--- a/ExcelTool/LubanTools/DataTables/Datas/NpcData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/NpcData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F697BCEB-A8AD-4969-ACC6-71615E93C82D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF5CD6EC-DA16-4408-836E-DC3FA27EF4B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3330" yWindow="3460" windowWidth="41500" windowHeight="15380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6690" yWindow="3010" windowWidth="38610" windowHeight="16040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="25">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -61,9 +61,6 @@
     <t>名称</t>
   </si>
   <si>
-    <t>缩小图</t>
-  </si>
-  <si>
     <t>立绘</t>
   </si>
   <si>
@@ -89,6 +86,33 @@
   </si>
   <si>
     <t>TbLocalzationKeyData#sep=+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>名字</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SceneSpinePath</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>立绘(后期换为Spine)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ShangDianXiaoMei</t>
+  </si>
+  <si>
+    <t>商店小妹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ShangDianXiaoMei</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CharacterNames+ShangDianXiaoMei</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -187,7 +211,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -214,6 +238,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -496,15 +523,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="3" width="8.6640625" style="1"/>
-    <col min="4" max="4" width="35.58203125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="18.9140625" style="9" customWidth="1"/>
+    <col min="4" max="5" width="35.58203125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="23" style="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="15.5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -517,11 +544,14 @@
       <c r="D1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1" s="8" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -529,16 +559,19 @@
         <v>7</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -549,49 +582,72 @@
         <v>9</v>
       </c>
       <c r="D3" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="6" t="s">
-        <v>11</v>
-      </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B4" s="6">
         <v>10000</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>16</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="E4" s="10"/>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B5" s="6">
         <v>10001</v>
       </c>
       <c r="C5" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>14</v>
-      </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B6" s="6">
         <v>10002</v>
       </c>
       <c r="C6" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>14</v>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B7" s="1">
+        <v>10003</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/ExcelTool/LubanTools/DataTables/Datas/NpcData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/NpcData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF5CD6EC-DA16-4408-836E-DC3FA27EF4B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B042BAA8-7713-42B0-A93D-316AA8500448}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6690" yWindow="3010" windowWidth="38610" windowHeight="16040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8520" yWindow="3250" windowWidth="38610" windowHeight="15710" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="41">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -113,6 +113,67 @@
   </si>
   <si>
     <t>CharacterNames+ShangDianXiaoMei</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>对话|送礼|布料店</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>无</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>功能组</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FunctionGroup</t>
+  </si>
+  <si>
+    <t>FunctionType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>点击对话</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(list#sep=+),long</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PointerDialogue</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>日常对话</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DailyDialogue</t>
+  </si>
+  <si>
+    <t>剧情对话</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PlotDialogue</t>
+  </si>
+  <si>
+    <t>场景列表</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ShowRule</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CharacterData</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>绑定真实ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -176,15 +237,33 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF258"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4E83FD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -207,11 +286,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFDEE0E3"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFDEE0E3"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -240,7 +330,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -523,15 +625,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="3" width="8.6640625" style="1"/>
-    <col min="4" max="5" width="35.58203125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="23" style="9" customWidth="1"/>
+    <col min="4" max="6" width="35.58203125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="23" style="9" customWidth="1"/>
+    <col min="8" max="8" width="23.75" customWidth="1"/>
+    <col min="9" max="9" width="23.25" customWidth="1"/>
+    <col min="10" max="10" width="21.4140625" customWidth="1"/>
+    <col min="11" max="11" width="16.58203125" customWidth="1"/>
+    <col min="12" max="12" width="27.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" ht="15.5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -545,13 +652,31 @@
         <v>5</v>
       </c>
       <c r="E1" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="F1" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="G1" s="8" t="s">
         <v>6</v>
       </c>
+      <c r="H1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="J1" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1" s="14" t="s">
+        <v>38</v>
+      </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -565,13 +690,31 @@
         <v>17</v>
       </c>
       <c r="E2" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>14</v>
       </c>
+      <c r="H2" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="L2" s="5" t="s">
+        <v>31</v>
+      </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -585,13 +728,31 @@
         <v>18</v>
       </c>
       <c r="E3" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="F3" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="G3" s="6" t="s">
         <v>10</v>
       </c>
+      <c r="H3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>37</v>
+      </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B4" s="6">
         <v>10000</v>
       </c>
@@ -601,9 +762,23 @@
       <c r="D4" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="10"/>
+      <c r="E4" s="6">
+        <v>10000</v>
+      </c>
+      <c r="F4" s="10"/>
+      <c r="H4" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="I4" s="12">
+        <v>10000</v>
+      </c>
+      <c r="J4" s="13">
+        <v>10100</v>
+      </c>
+      <c r="K4" s="1"/>
+      <c r="L4" s="6"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B5" s="6">
         <v>10001</v>
       </c>
@@ -613,12 +788,27 @@
       <c r="D5" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6" t="s">
+      <c r="E5" s="6">
+        <v>10000</v>
+      </c>
+      <c r="F5" s="6"/>
+      <c r="G5" s="6" t="s">
         <v>13</v>
       </c>
+      <c r="H5" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="I5" s="12">
+        <v>10000</v>
+      </c>
+      <c r="J5" s="13">
+        <v>10101</v>
+      </c>
+      <c r="L5" s="1">
+        <v>100001</v>
+      </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B6" s="6">
         <v>10002</v>
       </c>
@@ -628,12 +818,15 @@
       <c r="D6" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="E6" s="6"/>
-      <c r="F6" s="6" t="s">
+      <c r="E6" s="6">
+        <v>10000</v>
+      </c>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B7" s="1">
         <v>10003</v>
       </c>
@@ -643,10 +836,13 @@
       <c r="D7" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="E7" s="6">
+        <v>10000</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F7" s="6" t="s">
+      <c r="G7" s="6" t="s">
         <v>21</v>
       </c>
     </row>

--- a/ExcelTool/LubanTools/DataTables/Datas/NpcData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/NpcData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B042BAA8-7713-42B0-A93D-316AA8500448}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFAB14F7-66A6-406B-B88C-6CC5F10B1FF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8520" yWindow="3250" windowWidth="38610" windowHeight="15710" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="3710" windowWidth="38610" windowHeight="16040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="52">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -116,10 +116,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>对话|送礼|布料店</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>无</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -161,20 +157,65 @@
     <t>PlotDialogue</t>
   </si>
   <si>
-    <t>场景列表</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ShowRule</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>CharacterData</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>绑定真实ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>对话|送礼|布料店|超市</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0,0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>All</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>出现位置</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>出现时间段</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>出现周天</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>vector2#sep=+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ShowRuleTimeType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ShowRuleWeekType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ScenePosition</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AppearanceTime</t>
+  </si>
+  <si>
+    <t>WeekType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0,1</t>
+  </si>
+  <si>
+    <t>0,2</t>
   </si>
 </sst>
 </file>
@@ -237,7 +278,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -262,8 +303,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -286,17 +339,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFDEE0E3"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFDEE0E3"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -330,9 +372,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -342,7 +381,10 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -625,7 +667,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="3" width="8.6640625" style="1"/>
@@ -635,10 +677,12 @@
     <col min="9" max="9" width="23.25" customWidth="1"/>
     <col min="10" max="10" width="21.4140625" customWidth="1"/>
     <col min="11" max="11" width="16.58203125" customWidth="1"/>
-    <col min="12" max="12" width="27.25" customWidth="1"/>
+    <col min="12" max="12" width="19.1640625" style="9" customWidth="1"/>
+    <col min="13" max="13" width="17.75" customWidth="1"/>
+    <col min="14" max="14" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15.5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="15.5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -652,7 +696,7 @@
         <v>5</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F1" s="5" t="s">
         <v>19</v>
@@ -661,22 +705,28 @@
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I1" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J1" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K1" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="L1" s="14" t="s">
-        <v>38</v>
+        <v>35</v>
+      </c>
+      <c r="L1" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="M1" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="N1" s="6" t="s">
+        <v>47</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -698,23 +748,29 @@
       <c r="G2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H2" s="11" t="s">
-        <v>28</v>
+      <c r="H2" s="10" t="s">
+        <v>27</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="L2" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
+      </c>
+      <c r="L2" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="M2" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>44</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -728,7 +784,7 @@
         <v>18</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="F3" s="5" t="s">
         <v>20</v>
@@ -737,22 +793,28 @@
         <v>10</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
+      </c>
+      <c r="L3" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>41</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B4" s="6">
         <v>10000</v>
       </c>
@@ -765,20 +827,30 @@
       <c r="E4" s="6">
         <v>10000</v>
       </c>
-      <c r="F4" s="10"/>
-      <c r="H4" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="I4" s="12">
+      <c r="F4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H4" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="I4" s="11">
         <v>10000</v>
       </c>
-      <c r="J4" s="13">
+      <c r="J4" s="12">
         <v>10100</v>
       </c>
       <c r="K4" s="1"/>
-      <c r="L4" s="6"/>
+      <c r="L4" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="M4" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>39</v>
+      </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B5" s="6">
         <v>10001</v>
       </c>
@@ -791,24 +863,32 @@
       <c r="E5" s="6">
         <v>10000</v>
       </c>
-      <c r="F5" s="6"/>
+      <c r="F5" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="G5" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="H5" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="I5" s="12">
+      <c r="H5" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="I5" s="11">
         <v>10000</v>
       </c>
-      <c r="J5" s="13">
+      <c r="J5" s="12">
         <v>10101</v>
       </c>
-      <c r="L5" s="1">
-        <v>100001</v>
+      <c r="L5" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="M5" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>39</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B6" s="6">
         <v>10002</v>
       </c>
@@ -821,12 +901,23 @@
       <c r="E6" s="6">
         <v>10000</v>
       </c>
-      <c r="F6" s="6"/>
+      <c r="F6" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="G6" s="6" t="s">
         <v>13</v>
       </c>
+      <c r="L6" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="M6" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>50</v>
+      </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B7" s="1">
         <v>10003</v>
       </c>
@@ -844,6 +935,15 @@
       </c>
       <c r="G7" s="6" t="s">
         <v>21</v>
+      </c>
+      <c r="L7" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="M7" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>51</v>
       </c>
     </row>
   </sheetData>

--- a/ExcelTool/LubanTools/DataTables/Datas/NpcData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/NpcData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFAB14F7-66A6-406B-B88C-6CC5F10B1FF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CF9F4AB-C44E-438A-A4DF-14B3B2D59386}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="3710" windowWidth="38610" windowHeight="16040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="4840" windowWidth="38610" windowHeight="16040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="51">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -77,145 +77,134 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>TbLocalzationKeyData#sep=+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>名字</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SceneSpinePath</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>立绘(后期换为Spine)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ShangDianXiaoMei</t>
+  </si>
+  <si>
+    <t>功能组</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FunctionGroup</t>
+  </si>
+  <si>
+    <t>FunctionType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>点击对话</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(list#sep=+),long</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PointerDialogue</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>日常对话</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DailyDialogue</t>
+  </si>
+  <si>
+    <t>剧情对话</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PlotDialogue</t>
+  </si>
+  <si>
+    <t>CharacterData</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>绑定真实ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>出现位置</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>出现时间段</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>出现周天</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>vector2#sep=+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ShowRuleTimeType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ShowRuleWeekType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ScenePosition</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AppearanceTime</t>
+  </si>
+  <si>
+    <t>WeekType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>CharacterNames+Machi</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>无</t>
+  </si>
+  <si>
+    <t>All</t>
+  </si>
+  <si>
+    <t>对话|送礼|布料店</t>
   </si>
   <si>
     <t>CharacterNames+LiZhi</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TbLocalzationKeyData#sep=+</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>名字</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SceneSpinePath</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>立绘(后期换为Spine)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ShangDianXiaoMei</t>
   </si>
   <si>
     <t>商店小妹</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ShangDianXiaoMei</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>CharacterNames+ShangDianXiaoMei</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>无</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>功能组</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>FunctionGroup</t>
-  </si>
-  <si>
-    <t>FunctionType</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>点击对话</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(list#sep=+),long</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PointerDialogue</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>日常对话</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DailyDialogue</t>
-  </si>
-  <si>
-    <t>剧情对话</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PlotDialogue</t>
-  </si>
-  <si>
-    <t>CharacterData</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>绑定真实ID</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>对话|送礼|布料店|超市</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0,0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>All</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>出现位置</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>出现时间段</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>出现周天</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>vector2#sep=+</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ShowRuleTimeType</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ShowRuleWeekType</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ScenePosition</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>AppearanceTime</t>
-  </si>
-  <si>
-    <t>WeekType</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0,1</t>
-  </si>
-  <si>
-    <t>0,2</t>
+  </si>
+  <si>
+    <t>0+0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0+1</t>
+  </si>
+  <si>
+    <t>0+2</t>
   </si>
 </sst>
 </file>
@@ -696,34 +685,34 @@
         <v>5</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G1" s="8" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="I1" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="J1" s="6" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="K1" s="6" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="L1" s="9" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="M1" s="6" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="N1" s="6" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
@@ -737,7 +726,7 @@
         <v>14</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>7</v>
@@ -749,25 +738,25 @@
         <v>14</v>
       </c>
       <c r="H2" s="10" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="L2" s="14" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="M2" s="13" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
@@ -781,37 +770,37 @@
         <v>9</v>
       </c>
       <c r="D3" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="F3" s="5" t="s">
         <v>18</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>20</v>
       </c>
       <c r="G3" s="6" t="s">
         <v>10</v>
       </c>
       <c r="H3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J3" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="I3" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="J3" s="1" t="s">
+      <c r="K3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L3" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="N3" s="1" t="s">
         <v>32</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="L3" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
@@ -822,16 +811,13 @@
         <v>11</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="E4" s="6">
         <v>10000</v>
       </c>
-      <c r="F4" s="1" t="s">
-        <v>23</v>
-      </c>
       <c r="H4" s="10" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="I4" s="11">
         <v>10000</v>
@@ -840,14 +826,14 @@
         <v>10100</v>
       </c>
       <c r="K4" s="1"/>
-      <c r="L4" s="14" t="s">
-        <v>40</v>
+      <c r="L4" s="13" t="s">
+        <v>43</v>
       </c>
       <c r="M4" s="13" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
@@ -858,19 +844,16 @@
         <v>12</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="E5" s="6">
         <v>10000</v>
       </c>
-      <c r="F5" s="1" t="s">
-        <v>23</v>
-      </c>
       <c r="G5" s="6" t="s">
         <v>13</v>
       </c>
       <c r="H5" s="10" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="I5" s="11">
         <v>10000</v>
@@ -878,14 +861,14 @@
       <c r="J5" s="12">
         <v>10101</v>
       </c>
-      <c r="L5" s="14" t="s">
-        <v>40</v>
+      <c r="L5" s="13" t="s">
+        <v>43</v>
       </c>
       <c r="M5" s="13" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
@@ -896,25 +879,22 @@
         <v>12</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="E6" s="6">
         <v>10000</v>
       </c>
-      <c r="F6" s="1" t="s">
-        <v>23</v>
-      </c>
       <c r="G6" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="L6" s="14" t="s">
-        <v>40</v>
+      <c r="L6" s="13" t="s">
+        <v>43</v>
       </c>
       <c r="M6" s="13" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
@@ -922,28 +902,28 @@
         <v>10003</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="E7" s="6">
         <v>10000</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="L7" s="14" t="s">
-        <v>40</v>
+        <v>19</v>
+      </c>
+      <c r="L7" s="13" t="s">
+        <v>43</v>
       </c>
       <c r="M7" s="13" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>

--- a/ExcelTool/LubanTools/DataTables/Datas/NpcData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/NpcData.xlsx
@@ -1,31 +1,42 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CF9F4AB-C44E-438A-A4DF-14B3B2D59386}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75252433-3F8A-4FA2-8F7F-FF9B50F7FA6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="4840" windowWidth="38610" windowHeight="16040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="4920" windowWidth="38610" windowHeight="15960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="52">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -153,10 +164,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>vector2#sep=+</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>ShowRuleTimeType</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -197,14 +204,21 @@
     <t>CharacterNames+ShangDianXiaoMei</t>
   </si>
   <si>
-    <t>0+0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0+1</t>
-  </si>
-  <si>
-    <t>0+2</t>
+    <t>0,0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0,1</t>
+  </si>
+  <si>
+    <t>0,2</t>
+  </si>
+  <si>
+    <t>0,3</t>
+  </si>
+  <si>
+    <t>vector2#sep=,</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -706,13 +720,13 @@
         <v>29</v>
       </c>
       <c r="L1" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="M1" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="N1" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
@@ -750,13 +764,13 @@
         <v>24</v>
       </c>
       <c r="L2" s="14" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M2" s="13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
@@ -811,13 +825,13 @@
         <v>11</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E4" s="6">
         <v>10000</v>
       </c>
       <c r="H4" s="10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I4" s="11">
         <v>10000</v>
@@ -827,13 +841,13 @@
       </c>
       <c r="K4" s="1"/>
       <c r="L4" s="13" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M4" s="13" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
@@ -844,7 +858,7 @@
         <v>12</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E5" s="6">
         <v>10000</v>
@@ -853,7 +867,7 @@
         <v>13</v>
       </c>
       <c r="H5" s="10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I5" s="11">
         <v>10000</v>
@@ -862,10 +876,10 @@
         <v>10101</v>
       </c>
       <c r="L5" s="13" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M5" s="13" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="N5" s="1" t="s">
         <v>48</v>
@@ -879,7 +893,7 @@
         <v>12</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E6" s="6">
         <v>10000</v>
@@ -888,10 +902,10 @@
         <v>13</v>
       </c>
       <c r="L6" s="13" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M6" s="13" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="N6" s="1" t="s">
         <v>49</v>
@@ -902,10 +916,10 @@
         <v>10003</v>
       </c>
       <c r="C7" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D7" s="6" t="s">
         <v>46</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>47</v>
       </c>
       <c r="E7" s="6">
         <v>10000</v>
@@ -917,10 +931,10 @@
         <v>19</v>
       </c>
       <c r="L7" s="13" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M7" s="13" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="N7" s="1" t="s">
         <v>50</v>

--- a/ExcelTool/LubanTools/DataTables/Datas/NpcData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/NpcData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75252433-3F8A-4FA2-8F7F-FF9B50F7FA6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FF89AF7-32C5-466F-A959-DBC31FB8355D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="4920" windowWidth="38610" windowHeight="15960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="2800" windowWidth="42470" windowHeight="16040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="52">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -830,6 +830,12 @@
       <c r="E4" s="6">
         <v>10000</v>
       </c>
+      <c r="F4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>13</v>
+      </c>
       <c r="H4" s="10" t="s">
         <v>41</v>
       </c>
@@ -863,6 +869,9 @@
       <c r="E5" s="6">
         <v>10000</v>
       </c>
+      <c r="F5" s="1" t="s">
+        <v>19</v>
+      </c>
       <c r="G5" s="6" t="s">
         <v>13</v>
       </c>
@@ -897,6 +906,9 @@
       </c>
       <c r="E6" s="6">
         <v>10000</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="G6" s="6" t="s">
         <v>13</v>

--- a/ExcelTool/LubanTools/DataTables/Datas/NpcData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/NpcData.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="128">
   <si>
     <t>##var</t>
   </si>
@@ -143,46 +143,274 @@
     <t>男主</t>
   </si>
   <si>
-    <t>CharacterNames+Machi</t>
+    <t>CharacterNames+Character_NPC_01</t>
+  </si>
+  <si>
+    <t>0.0+0.0</t>
+  </si>
+  <si>
+    <t>马吉（女主）（卧室）</t>
+  </si>
+  <si>
+    <t>CharacterNames+Character_NPC_02</t>
+  </si>
+  <si>
+    <t>Machi</t>
+  </si>
+  <si>
+    <t>对话|好感|送礼</t>
+  </si>
+  <si>
+    <t>10000+10100</t>
+  </si>
+  <si>
+    <t>全部</t>
+  </si>
+  <si>
+    <t>半夜</t>
+  </si>
+  <si>
+    <t>中午</t>
+  </si>
+  <si>
+    <t>马吉（女主）（客厅）</t>
+  </si>
+  <si>
+    <t>周一|周二|周三|周四|周五</t>
+  </si>
+  <si>
+    <t>傍晚</t>
+  </si>
+  <si>
+    <t>马吉（女主）（酒吧）</t>
+  </si>
+  <si>
+    <t>周六|周日</t>
+  </si>
+  <si>
+    <t>马吉（女主）（女办公室）</t>
+  </si>
+  <si>
+    <t>对话|好感|送礼|催稿</t>
+  </si>
+  <si>
+    <t>早上</t>
+  </si>
+  <si>
+    <t>紅院 栗花（女二）（展会）</t>
+  </si>
+  <si>
+    <t>CharacterNames+Character_NPC_03</t>
+  </si>
+  <si>
+    <t>单人_女二@2x</t>
+  </si>
+  <si>
+    <t>女二@2x</t>
+  </si>
+  <si>
+    <t>周日</t>
+  </si>
+  <si>
+    <t>紅院 栗花（女二）（男主客厅）</t>
+  </si>
+  <si>
+    <t>紅院 栗花（女二）（咖啡店厅）</t>
+  </si>
+  <si>
+    <t>周一|周二|周三|周四|周五|周六</t>
+  </si>
+  <si>
+    <t>紅院 栗花（女二）（酒吧）</t>
+  </si>
+  <si>
+    <t>对话|好感|送礼|激情一下</t>
+  </si>
+  <si>
+    <t>紅院 栗花（女二）（女二公寓）</t>
+  </si>
+  <si>
+    <t>紗夜（女仆）（咖啡店）</t>
+  </si>
+  <si>
+    <t>CharacterNames+Character_NPC_04</t>
+  </si>
+  <si>
+    <t>单人_女仆@2x</t>
+  </si>
+  <si>
+    <t>女三女仆@2x</t>
+  </si>
+  <si>
+    <t>早上|中午</t>
+  </si>
+  <si>
+    <t>紗夜（女仆）（漫展）</t>
+  </si>
+  <si>
+    <t>紗夜（女仆）（男主客厅）</t>
+  </si>
+  <si>
+    <t>紫苑（情趣用品店）（摄影）</t>
+  </si>
+  <si>
+    <t>CharacterNames+Character_NPC_05</t>
+  </si>
+  <si>
+    <t>单人_女四@2x</t>
+  </si>
+  <si>
+    <t>女四@2x</t>
+  </si>
+  <si>
+    <t>对话|好感|送礼|摄影店|激情一下</t>
+  </si>
+  <si>
+    <t>周三|周四|周五|周六|周日</t>
+  </si>
+  <si>
+    <t>中午|傍晚</t>
+  </si>
+  <si>
+    <t>紫苑（情趣用品店）（情趣）</t>
+  </si>
+  <si>
+    <t>对话|好感|送礼|情趣用品店|激情一下</t>
+  </si>
+  <si>
+    <t>紫苑（情趣用品店）（咖啡）</t>
+  </si>
+  <si>
+    <t>周一|周二</t>
+  </si>
+  <si>
+    <t>紫苑（情趣用品店）（酒吧）</t>
+  </si>
+  <si>
+    <t>傍晚|半夜</t>
+  </si>
+  <si>
+    <t>友莉（超市小妹）(超市)</t>
+  </si>
+  <si>
+    <t>CharacterNames+Character_NPC_06</t>
   </si>
   <si>
     <t>ShangDianXiaoMei</t>
   </si>
   <si>
-    <t>Machi</t>
-  </si>
-  <si>
-    <t>无</t>
-  </si>
-  <si>
-    <t>All</t>
-  </si>
-  <si>
-    <t>0,0</t>
-  </si>
-  <si>
-    <t>马吉</t>
-  </si>
-  <si>
-    <t>对话|送礼|布料店</t>
-  </si>
-  <si>
-    <t>0,1</t>
-  </si>
-  <si>
-    <t>CharacterNames+LiZhi</t>
-  </si>
-  <si>
-    <t>0,2</t>
-  </si>
-  <si>
-    <t>商店小妹</t>
-  </si>
-  <si>
-    <t>CharacterNames+ShangDianXiaoMei</t>
-  </si>
-  <si>
-    <t>0,3</t>
+    <t>对话|好感|送礼|超市|激情一下</t>
+  </si>
+  <si>
+    <t>早上|中午|傍晚</t>
+  </si>
+  <si>
+    <t>友莉（超市小妹）(公园)</t>
+  </si>
+  <si>
+    <t>友莉（超市小妹）(小河)</t>
+  </si>
+  <si>
+    <t>对话|好感|送礼|鱼饵店|激情一下</t>
+  </si>
+  <si>
+    <t>桃（酒吧）</t>
+  </si>
+  <si>
+    <t>CharacterNames+Character_NPC_07</t>
+  </si>
+  <si>
+    <t>单人_酒保@2x</t>
+  </si>
+  <si>
+    <t>酒保@2x</t>
+  </si>
+  <si>
+    <t>对话|好感|送礼|去赌场</t>
+  </si>
+  <si>
+    <t>中午|傍晚|半夜</t>
+  </si>
+  <si>
+    <t>桃（赌场）</t>
+  </si>
+  <si>
+    <t>对话|好感|送礼|游戏币商店|激情一下</t>
+  </si>
+  <si>
+    <t>千织（工厂）</t>
+  </si>
+  <si>
+    <t>CharacterNames+Character_NPC_08</t>
+  </si>
+  <si>
+    <t>单人_经理@2x</t>
+  </si>
+  <si>
+    <t>PlantManager</t>
+  </si>
+  <si>
+    <t>对话|好感|送礼|周边工厂|激情一下</t>
+  </si>
+  <si>
+    <t>紬（服装店）</t>
+  </si>
+  <si>
+    <t>CharacterNames+Character_NPC_09</t>
+  </si>
+  <si>
+    <t>单人_布料店@2x</t>
+  </si>
+  <si>
+    <t>布料店@2x</t>
+  </si>
+  <si>
+    <t>对话|好感|送礼|布料店|激情一下</t>
+  </si>
+  <si>
+    <t>巧蜜（摄影店）</t>
+  </si>
+  <si>
+    <t>CharacterNames+Character_NPC_10</t>
+  </si>
+  <si>
+    <t>单人_摄影小妹@2x</t>
+  </si>
+  <si>
+    <t>摄影小妹@2x</t>
+  </si>
+  <si>
+    <t>对话|好感|送礼|摄影|激情一下</t>
+  </si>
+  <si>
+    <t>一郎（果蔬店）</t>
+  </si>
+  <si>
+    <t>CharacterNames+Character_NPC_11</t>
+  </si>
+  <si>
+    <t>单人_果蔬大叔@2x</t>
+  </si>
+  <si>
+    <t>果蔬店大叔@2x</t>
+  </si>
+  <si>
+    <t>对话|好感|送礼|果蔬店</t>
+  </si>
+  <si>
+    <t>二爺（钓鱼大爷）</t>
+  </si>
+  <si>
+    <t>CharacterNames+Character_NPC_12</t>
+  </si>
+  <si>
+    <t>单人_渔夫@2x</t>
+  </si>
+  <si>
+    <t>钓鱼老人@2x</t>
+  </si>
+  <si>
+    <t>对话|好感|送礼|鱼饵店</t>
   </si>
 </sst>
 </file>
@@ -195,42 +423,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="26">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF1F2329"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -241,9 +434,20 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="微软雅黑"/>
       <charset val="134"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1F2329"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -390,7 +594,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="38">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -399,6 +603,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -417,18 +627,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF258"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4E83FD"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -483,12 +681,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -598,18 +790,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -738,19 +918,31 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -759,173 +951,155 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1246,44 +1420,46 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="6"/>
+  <dimension ref="A1:N33"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="3" width="8.66666666666667" style="1"/>
-    <col min="4" max="6" width="35.5833333333333" style="1" customWidth="1"/>
-    <col min="7" max="7" width="23" style="2" customWidth="1"/>
-    <col min="8" max="8" width="23.75" customWidth="1"/>
-    <col min="9" max="9" width="23.25" customWidth="1"/>
-    <col min="10" max="10" width="21.4166666666667" customWidth="1"/>
-    <col min="11" max="11" width="16.5833333333333" customWidth="1"/>
-    <col min="12" max="12" width="19.1666666666667" style="2" customWidth="1"/>
-    <col min="13" max="13" width="17.75" customWidth="1"/>
-    <col min="14" max="14" width="22" customWidth="1"/>
+    <col min="1" max="2" width="8.66666666666667" style="2"/>
+    <col min="3" max="3" width="25.8333333333333" style="2" customWidth="1"/>
+    <col min="4" max="6" width="35.5833333333333" style="2" customWidth="1"/>
+    <col min="7" max="7" width="23" style="3" customWidth="1"/>
+    <col min="8" max="8" width="33.5833333333333" style="2" customWidth="1"/>
+    <col min="9" max="9" width="23.25" style="2" customWidth="1"/>
+    <col min="10" max="10" width="21.4166666666667" style="2" customWidth="1"/>
+    <col min="11" max="11" width="16.5833333333333" style="2" customWidth="1"/>
+    <col min="12" max="12" width="28" style="3" customWidth="1"/>
+    <col min="13" max="13" width="17.75" style="2" customWidth="1"/>
+    <col min="14" max="14" width="22" style="2" customWidth="1"/>
+    <col min="15" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.5" spans="1:14">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:14">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="7" t="s">
@@ -1295,7 +1471,7 @@
       <c r="K1" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="3" t="s">
         <v>11</v>
       </c>
       <c r="M1" s="7" t="s">
@@ -1306,227 +1482,1132 @@
       </c>
     </row>
     <row r="2" spans="1:14">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="D2" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="E2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="F2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="H2" s="9" t="s">
+      <c r="H2" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="I2" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="J2" s="5" t="s">
+      <c r="J2" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="K2" s="5" t="s">
+      <c r="K2" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="L2" s="10" t="s">
+      <c r="L2" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="M2" s="11" t="s">
+      <c r="M2" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="N2" s="2" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:14">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="6" t="s">
         <v>28</v>
       </c>
       <c r="G3" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="H3" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="I3" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="J3" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="K3" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="L3" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="M3" s="1" t="s">
+      <c r="M3" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="N3" s="1" t="s">
+      <c r="N3" s="2" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:14">
-      <c r="B4" s="7">
+    <row r="4" s="1" customFormat="1" spans="1:14">
+      <c r="B4" s="11">
         <v>10000</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="E4" s="7">
+      <c r="E4" s="11">
         <v>10000</v>
       </c>
-      <c r="F4" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="G4" s="7" t="s">
+      <c r="F4" s="1"/>
+      <c r="G4" s="12"/>
+      <c r="N4" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" spans="1:14">
+      <c r="B5" s="11">
+        <v>10001</v>
+      </c>
+      <c r="C5" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="H4" s="9" t="s">
+      <c r="D5" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="I4" s="13">
-        <v>10000</v>
-      </c>
-      <c r="J4" s="14">
-        <v>10100</v>
-      </c>
-      <c r="K4" s="1"/>
-      <c r="L4" s="11" t="s">
+      <c r="E5" s="11">
+        <v>10001</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="M4" s="11" t="s">
+      <c r="G5" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="N4" s="1" t="s">
+      <c r="H5" s="1" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="5" spans="1:14">
-      <c r="B5" s="7">
+      <c r="I5" s="1"/>
+      <c r="J5" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="K5" s="1"/>
+      <c r="L5" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" spans="1:14">
+      <c r="B6" s="11">
+        <v>10002</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="E6" s="11">
         <v>10001</v>
       </c>
-      <c r="C5" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="E5" s="7">
-        <v>10000</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="H5" s="9" t="s">
+      <c r="F6" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G6" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="L6" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="I5" s="13">
-        <v>10000</v>
-      </c>
-      <c r="J5" s="14">
-        <v>10101</v>
-      </c>
-      <c r="L5" s="11" t="s">
+      <c r="M6" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" spans="1:14">
+      <c r="B7" s="11">
+        <v>10003</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="E7" s="11">
+        <v>10001</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="M5" s="11" t="s">
+      <c r="G7" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="N5" s="1" t="s">
+      <c r="H7" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="K7" s="1"/>
+      <c r="L7" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" spans="1:14">
+      <c r="B8" s="11">
+        <v>10004</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="E8" s="11">
+        <v>10001</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G8" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="L8" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" spans="1:14">
+      <c r="B9" s="11">
+        <v>10005</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="E9" s="11">
+        <v>10001</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G9" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="K9" s="1"/>
+      <c r="L9" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" spans="1:14">
+      <c r="B10" s="11">
+        <v>10006</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="E10" s="11">
+        <v>10002</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G10" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="I10" s="1"/>
+      <c r="J10" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="K10" s="1"/>
+      <c r="L10" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" spans="1:14">
+      <c r="B11" s="11">
+        <v>10007</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="E11" s="11">
+        <v>10002</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G11" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="L11" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="M11" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="N11" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" spans="1:14">
+      <c r="B12" s="11">
+        <v>10008</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="E12" s="11">
+        <v>10002</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G12" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="L12" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="N12" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" spans="1:14">
+      <c r="B13" s="11">
+        <v>10009</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="E13" s="11">
+        <v>10002</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G13" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="L13" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="M13" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="N13" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" spans="1:14">
+      <c r="B14" s="11">
+        <v>10010</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="D14" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="E14" s="11">
+        <v>10002</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G14" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="L14" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="M14" s="1" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="6" spans="1:14">
-      <c r="B6" s="7">
-        <v>10002</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="D6" s="7" t="s">
+      <c r="N14" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" spans="1:14">
+      <c r="B15" s="11">
+        <v>10011</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="D15" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="E15" s="12">
+        <v>10003</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G15" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="I15" s="1"/>
+      <c r="J15" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="K15" s="1"/>
+      <c r="L15" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="M15" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="N15" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="16" s="1" customFormat="1" spans="1:14">
+      <c r="B16" s="11">
+        <v>10012</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="D16" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="E16" s="12">
+        <v>10003</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G16" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="L16" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="M16" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="N16" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" spans="2:14">
+      <c r="B17" s="11">
+        <v>10013</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="D17" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="E17" s="12">
+        <v>10003</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G17" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="L17" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="M17" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="N17" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="18" s="1" customFormat="1" spans="2:14">
+      <c r="B18" s="11">
+        <v>10014</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="D18" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="E18" s="12">
+        <v>10003</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G18" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="L18" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="M18" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="N18" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="19" s="1" customFormat="1" spans="2:14">
+      <c r="B19" s="11">
+        <v>10015</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="D19" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E19" s="11">
+        <v>10004</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G19" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="I19" s="1"/>
+      <c r="J19" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="K19" s="1"/>
+      <c r="L19" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="M19" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="N19" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="20" s="1" customFormat="1" spans="2:14">
+      <c r="B20" s="11">
+        <v>10016</v>
+      </c>
+      <c r="C20" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="D20" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E20" s="11">
+        <v>10004</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G20" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="L20" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="M20" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="N20" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="21" s="1" customFormat="1" spans="2:14">
+      <c r="B21" s="11">
+        <v>10017</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="D21" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E21" s="11">
+        <v>10004</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G21" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="L21" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="M21" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="E6" s="7">
-        <v>10000</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="L6" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="M6" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="N6" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
-      <c r="B7" s="1">
-        <v>10003</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="E7" s="7">
-        <v>10000</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="L7" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="M7" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="N7" s="1" t="s">
-        <v>51</v>
-      </c>
+      <c r="N21" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="22" s="1" customFormat="1" spans="2:14">
+      <c r="B22" s="11">
+        <v>10018</v>
+      </c>
+      <c r="C22" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="D22" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E22" s="11">
+        <v>10004</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G22" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="L22" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="M22" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="N22" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="23" s="1" customFormat="1" spans="2:14">
+      <c r="B23" s="11">
+        <v>10019</v>
+      </c>
+      <c r="C23" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="D23" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="E23" s="11">
+        <v>10005</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="G23" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="I23" s="1"/>
+      <c r="J23" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="K23" s="1"/>
+      <c r="L23" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="M23" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="N23" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="24" s="1" customFormat="1" spans="2:14">
+      <c r="B24" s="11">
+        <v>10020</v>
+      </c>
+      <c r="C24" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="D24" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="E24" s="11">
+        <v>10005</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="G24" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="L24" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="M24" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="N24" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="25" s="1" customFormat="1" spans="2:14">
+      <c r="B25" s="11">
+        <v>10021</v>
+      </c>
+      <c r="C25" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="D25" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="E25" s="11">
+        <v>10005</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="G25" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="L25" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="M25" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="N25" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="26" s="1" customFormat="1" spans="2:14">
+      <c r="B26" s="11">
+        <v>10022</v>
+      </c>
+      <c r="C26" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="D26" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E26" s="11">
+        <v>10006</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="G26" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="I26" s="1"/>
+      <c r="J26" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="K26" s="1"/>
+      <c r="L26" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="M26" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="N26" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="27" s="1" customFormat="1" spans="2:14">
+      <c r="B27" s="11">
+        <v>10023</v>
+      </c>
+      <c r="C27" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="D27" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E27" s="11">
+        <v>10006</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="G27" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="J27" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="L27" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="M27" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="N27" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="28" s="1" customFormat="1" spans="2:14">
+      <c r="B28" s="11">
+        <v>10024</v>
+      </c>
+      <c r="C28" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="D28" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="E28" s="12">
+        <v>10007</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="G28" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="I28" s="1"/>
+      <c r="J28" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="K28" s="1"/>
+      <c r="L28" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="M28" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="N28" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="29" s="1" customFormat="1" spans="2:14">
+      <c r="B29" s="11">
+        <v>10025</v>
+      </c>
+      <c r="C29" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="D29" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="E29" s="11">
+        <v>10008</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="G29" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="I29" s="1"/>
+      <c r="J29" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="K29" s="1"/>
+      <c r="L29" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="M29" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="N29" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="30" s="1" customFormat="1" spans="2:14">
+      <c r="B30" s="11">
+        <v>10026</v>
+      </c>
+      <c r="C30" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="D30" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="E30" s="11">
+        <v>10009</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="G30" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="I30" s="1"/>
+      <c r="J30" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="K30" s="1"/>
+      <c r="L30" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="M30" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="N30" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="31" s="1" customFormat="1" spans="2:14">
+      <c r="B31" s="11">
+        <v>10027</v>
+      </c>
+      <c r="C31" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="D31" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="E31" s="11">
+        <v>10010</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="G31" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="I31" s="1"/>
+      <c r="J31" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="K31" s="1"/>
+      <c r="L31" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="M31" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="N31" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="32" s="1" customFormat="1" spans="2:14">
+      <c r="B32" s="11">
+        <v>10028</v>
+      </c>
+      <c r="C32" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="D32" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="E32" s="12">
+        <v>10011</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="G32" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="I32" s="1"/>
+      <c r="J32" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="K32" s="1"/>
+      <c r="L32" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="M32" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="N32" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="33" customFormat="1" spans="1:14">
+      <c r="A33" s="2"/>
+      <c r="B33" s="2"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2"/>
+      <c r="E33" s="2"/>
+      <c r="F33" s="2"/>
+      <c r="G33" s="3"/>
+      <c r="H33" s="2"/>
+      <c r="I33" s="2"/>
+      <c r="J33" s="2"/>
+      <c r="K33" s="2"/>
+      <c r="L33" s="3"/>
+      <c r="N33" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ExcelTool/LubanTools/DataTables/Datas/NpcData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/NpcData.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{929B92B0-65F5-4FA2-988B-69903AAE8C8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView xWindow="11250" yWindow="2100" windowWidth="42470" windowHeight="16040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="角色表" sheetId="1" r:id="rId1"/>
@@ -27,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="156">
   <si>
     <t>##var</t>
   </si>
@@ -95,9 +101,6 @@
     <t>ShowRuleTimeType</t>
   </si>
   <si>
-    <t>vector2#sep=+</t>
-  </si>
-  <si>
     <t>##</t>
   </si>
   <si>
@@ -146,9 +149,6 @@
     <t>CharacterNames+Character_NPC_01</t>
   </si>
   <si>
-    <t>0.0+0.0</t>
-  </si>
-  <si>
     <t>马吉（女主）（卧室）</t>
   </si>
   <si>
@@ -350,9 +350,6 @@
     <t>PlantManager</t>
   </si>
   <si>
-    <t>对话|好感|送礼|周边工厂|激情一下</t>
-  </si>
-  <si>
     <t>紬（服装店）</t>
   </si>
   <si>
@@ -411,19 +408,109 @@
   </si>
   <si>
     <t>对话|好感|送礼|鱼饵店</t>
+  </si>
+  <si>
+    <t>vector2#sep=,</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0,0.0</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0,0.1</t>
+  </si>
+  <si>
+    <t>0.0,0.2</t>
+  </si>
+  <si>
+    <t>0.0,0.3</t>
+  </si>
+  <si>
+    <t>0.0,0.4</t>
+  </si>
+  <si>
+    <t>0.0,0.5</t>
+  </si>
+  <si>
+    <t>0.0,0.6</t>
+  </si>
+  <si>
+    <t>0.0,0.7</t>
+  </si>
+  <si>
+    <t>0.0,0.8</t>
+  </si>
+  <si>
+    <t>0.0,0.9</t>
+  </si>
+  <si>
+    <t>0.0,0.10</t>
+  </si>
+  <si>
+    <t>0.0,0.11</t>
+  </si>
+  <si>
+    <t>0.0,0.12</t>
+  </si>
+  <si>
+    <t>0.0,0.13</t>
+  </si>
+  <si>
+    <t>0.0,0.14</t>
+  </si>
+  <si>
+    <t>0.0,0.15</t>
+  </si>
+  <si>
+    <t>0.0,0.16</t>
+  </si>
+  <si>
+    <t>0.0,0.17</t>
+  </si>
+  <si>
+    <t>0.0,0.18</t>
+  </si>
+  <si>
+    <t>0.0,0.19</t>
+  </si>
+  <si>
+    <t>0.0,0.20</t>
+  </si>
+  <si>
+    <t>0.0,0.21</t>
+  </si>
+  <si>
+    <t>0.0,0.22</t>
+  </si>
+  <si>
+    <t>0.0,0.23</t>
+  </si>
+  <si>
+    <t>0.0,0.24</t>
+  </si>
+  <si>
+    <t>0.0,0.25</t>
+  </si>
+  <si>
+    <t>0.0,0.26</t>
+  </si>
+  <si>
+    <t>0.0,0.27</t>
+  </si>
+  <si>
+    <t>0.0,0.28</t>
+  </si>
+  <si>
+    <t>对话|好感|送礼|激情一下</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="23">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -435,166 +522,29 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="微软雅黑"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF1F2329"/>
       <name val="微软雅黑"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <sz val="9"/>
       <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="34">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -609,192 +559,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.39994506668294322"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -817,251 +599,9 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
   <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1102,61 +642,17 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1414,30 +910,30 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N33"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="2" width="8.66666666666667" style="2"/>
-    <col min="3" max="3" width="25.8333333333333" style="2" customWidth="1"/>
-    <col min="4" max="6" width="35.5833333333333" style="2" customWidth="1"/>
+    <col min="1" max="2" width="8.6640625" style="2"/>
+    <col min="3" max="3" width="25.83203125" style="2" customWidth="1"/>
+    <col min="4" max="6" width="35.58203125" style="2" customWidth="1"/>
     <col min="7" max="7" width="23" style="3" customWidth="1"/>
-    <col min="8" max="8" width="33.5833333333333" style="2" customWidth="1"/>
+    <col min="8" max="8" width="33.58203125" style="2" customWidth="1"/>
     <col min="9" max="9" width="23.25" style="2" customWidth="1"/>
-    <col min="10" max="10" width="21.4166666666667" style="2" customWidth="1"/>
-    <col min="11" max="11" width="16.5833333333333" style="2" customWidth="1"/>
+    <col min="10" max="10" width="21.4140625" style="2" customWidth="1"/>
+    <col min="11" max="11" width="16.58203125" style="2" customWidth="1"/>
     <col min="12" max="12" width="28" style="3" customWidth="1"/>
     <col min="13" max="13" width="17.75" style="2" customWidth="1"/>
     <col min="14" max="14" width="22" style="2" customWidth="1"/>
     <col min="15" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1481,7 +977,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>14</v>
       </c>
@@ -1522,1079 +1018,1052 @@
         <v>21</v>
       </c>
       <c r="N2" s="2" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A3" s="2" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="3" spans="1:14">
-      <c r="A3" s="2" t="s">
+      <c r="B3" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="C3" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="D3" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="E3" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="F3" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="G3" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="H3" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="I3" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="J3" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="K3" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="L3" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="M3" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="M3" s="2" t="s">
+      <c r="N3" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="N3" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="4" s="1" customFormat="1" spans="1:14">
+    </row>
+    <row r="4" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B4" s="11">
         <v>10000</v>
       </c>
       <c r="C4" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="D4" s="12" t="s">
         <v>37</v>
-      </c>
-      <c r="D4" s="12" t="s">
-        <v>38</v>
       </c>
       <c r="E4" s="11">
         <v>10000</v>
       </c>
-      <c r="F4" s="1"/>
       <c r="G4" s="12"/>
       <c r="N4" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="5" s="1" customFormat="1" spans="1:14">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B5" s="11">
         <v>10001</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E5" s="11">
         <v>10001</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G5" s="12" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H5" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="L5" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1" t="s">
+      <c r="M5" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="K5" s="1"/>
-      <c r="L5" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="M5" s="1" t="s">
-        <v>46</v>
-      </c>
       <c r="N5" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="6" s="1" customFormat="1" spans="1:14">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B6" s="11">
         <v>10002</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E6" s="11">
         <v>10001</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G6" s="12" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H6" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="L6" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="J6" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="L6" s="12" t="s">
+      <c r="M6" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="M6" s="1" t="s">
-        <v>47</v>
-      </c>
       <c r="N6" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="7" s="1" customFormat="1" spans="1:14">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B7" s="11">
         <v>10003</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E7" s="11">
         <v>10001</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="I7" s="1"/>
+        <v>41</v>
+      </c>
       <c r="J7" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="K7" s="1"/>
+        <v>42</v>
+      </c>
       <c r="L7" s="12" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="8" s="1" customFormat="1" spans="1:14">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B8" s="11">
         <v>10004</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E8" s="11">
         <v>10001</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G8" s="12" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="L8" s="12" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="9" s="1" customFormat="1" spans="1:14">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B9" s="11">
         <v>10005</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E9" s="11">
         <v>10001</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G9" s="12" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="I9" s="1"/>
+        <v>52</v>
+      </c>
       <c r="J9" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="K9" s="1"/>
+        <v>42</v>
+      </c>
       <c r="L9" s="12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="10" s="1" customFormat="1" spans="1:14">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B10" s="11">
         <v>10006</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E10" s="11">
         <v>10002</v>
       </c>
       <c r="F10" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="G10" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="L10" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="G10" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="I10" s="1"/>
-      <c r="J10" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="K10" s="1"/>
-      <c r="L10" s="12" t="s">
-        <v>60</v>
-      </c>
       <c r="M10" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="11" s="1" customFormat="1" spans="1:14">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B11" s="11">
         <v>10007</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E11" s="11">
         <v>10002</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G11" s="12" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="H11" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="L11" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="J11" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="L11" s="12" t="s">
+      <c r="M11" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="M11" s="1" t="s">
-        <v>47</v>
-      </c>
       <c r="N11" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="12" s="1" customFormat="1" spans="1:14">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B12" s="11">
         <v>10008</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E12" s="11">
         <v>10002</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G12" s="12" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="L12" s="12" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="13" s="1" customFormat="1" spans="1:14">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B13" s="11">
         <v>10009</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E13" s="11">
         <v>10002</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G13" s="12" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="L13" s="12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="14" s="1" customFormat="1" spans="1:14">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B14" s="11">
         <v>10010</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E14" s="11">
         <v>10002</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G14" s="12" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="J14" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="L14" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="M14" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="L14" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="M14" s="1" t="s">
-        <v>46</v>
-      </c>
       <c r="N14" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="15" s="1" customFormat="1" spans="1:14">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B15" s="11">
         <v>10011</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E15" s="12">
         <v>10003</v>
       </c>
       <c r="F15" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="G15" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="L15" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="M15" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="G15" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="H15" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="I15" s="1"/>
-      <c r="J15" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="K15" s="1"/>
-      <c r="L15" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="M15" s="1" t="s">
-        <v>71</v>
-      </c>
       <c r="N15" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="16" s="1" customFormat="1" spans="1:14">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B16" s="11">
         <v>10012</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E16" s="12">
         <v>10003</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G16" s="12" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="L16" s="12" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="17" s="1" customFormat="1" spans="2:14">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="17" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B17" s="11">
         <v>10013</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E17" s="12">
         <v>10003</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G17" s="12" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="L17" s="12" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="18" s="1" customFormat="1" spans="2:14">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="18" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B18" s="11">
         <v>10014</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E18" s="12">
         <v>10003</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G18" s="12" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="L18" s="12" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="19" s="1" customFormat="1" spans="2:14">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="19" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B19" s="11">
         <v>10015</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E19" s="11">
         <v>10004</v>
       </c>
       <c r="F19" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G19" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="H19" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="G19" s="12" t="s">
+      <c r="J19" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="L19" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="H19" s="1" t="s">
+      <c r="M19" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="I19" s="1"/>
-      <c r="J19" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="K19" s="1"/>
-      <c r="L19" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="M19" s="1" t="s">
-        <v>80</v>
-      </c>
       <c r="N19" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="20" s="1" customFormat="1" spans="2:14">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="20" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B20" s="11">
         <v>10016</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E20" s="11">
         <v>10004</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G20" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="L20" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="H20" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="J20" s="1" t="s">
+      <c r="M20" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="L20" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="M20" s="1" t="s">
-        <v>46</v>
-      </c>
       <c r="N20" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="21" s="1" customFormat="1" spans="2:14">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="21" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B21" s="11">
         <v>10017</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E21" s="11">
         <v>10004</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G21" s="12" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="L21" s="12" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="22" s="1" customFormat="1" spans="2:14">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="22" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B22" s="11">
         <v>10018</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E22" s="11">
         <v>10004</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G22" s="12" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="L22" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="M22" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="M22" s="1" t="s">
-        <v>86</v>
-      </c>
       <c r="N22" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="23" s="1" customFormat="1" spans="2:14">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="23" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B23" s="11">
         <v>10019</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E23" s="11">
         <v>10005</v>
       </c>
       <c r="F23" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="G23" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="L23" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="M23" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="G23" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="H23" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="I23" s="1"/>
-      <c r="J23" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="K23" s="1"/>
-      <c r="L23" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="M23" s="1" t="s">
-        <v>91</v>
-      </c>
       <c r="N23" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="24" s="1" customFormat="1" spans="2:14">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="24" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B24" s="11">
         <v>10020</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E24" s="11">
         <v>10005</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G24" s="12" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="L24" s="12" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="25" s="1" customFormat="1" spans="2:14">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="25" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B25" s="11">
         <v>10021</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E25" s="11">
         <v>10005</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G25" s="12" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="L25" s="12" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="M25" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="26" s="1" customFormat="1" spans="2:14">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="26" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B26" s="11">
         <v>10022</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E26" s="11">
         <v>10006</v>
       </c>
       <c r="F26" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="G26" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="H26" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="G26" s="12" t="s">
+      <c r="J26" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="L26" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="M26" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="H26" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="I26" s="1"/>
-      <c r="J26" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="K26" s="1"/>
-      <c r="L26" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="M26" s="1" t="s">
-        <v>100</v>
-      </c>
       <c r="N26" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="27" s="1" customFormat="1" spans="2:14">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="27" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B27" s="11">
         <v>10023</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E27" s="11">
         <v>10006</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G27" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="J27" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="L27" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="M27" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="H27" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="J27" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="L27" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="M27" s="1" t="s">
-        <v>100</v>
-      </c>
       <c r="N27" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="28" s="1" customFormat="1" spans="2:14">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="28" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B28" s="11">
         <v>10024</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E28" s="12">
         <v>10007</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="G28" s="12" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="I28" s="1"/>
+        <v>155</v>
+      </c>
       <c r="J28" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="K28" s="1"/>
+        <v>42</v>
+      </c>
       <c r="L28" s="12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="N28" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="29" s="1" customFormat="1" spans="2:14">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="29" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B29" s="11">
         <v>10025</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E29" s="11">
         <v>10008</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="G29" s="12" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="I29" s="1"/>
+        <v>109</v>
+      </c>
       <c r="J29" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="K29" s="1"/>
+        <v>42</v>
+      </c>
       <c r="L29" s="12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="M29" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="N29" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="30" s="1" customFormat="1" spans="2:14">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="30" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B30" s="11">
         <v>10026</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E30" s="11">
         <v>10009</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="G30" s="12" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="I30" s="1"/>
+        <v>114</v>
+      </c>
       <c r="J30" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="K30" s="1"/>
+        <v>42</v>
+      </c>
       <c r="L30" s="12" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="M30" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="N30" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="31" s="1" customFormat="1" spans="2:14">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="31" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B31" s="11">
         <v>10027</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="E31" s="11">
         <v>10010</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="G31" s="12" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="I31" s="1"/>
+        <v>119</v>
+      </c>
       <c r="J31" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="K31" s="1"/>
+        <v>42</v>
+      </c>
       <c r="L31" s="12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="M31" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="N31" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="32" s="1" customFormat="1" spans="2:14">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="32" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B32" s="11">
         <v>10028</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D32" s="12" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="E32" s="12">
         <v>10011</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="G32" s="12" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="I32" s="1"/>
+        <v>124</v>
+      </c>
       <c r="J32" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="K32" s="1"/>
+        <v>42</v>
+      </c>
       <c r="L32" s="12" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="M32" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N32" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="33" customFormat="1" spans="1:14">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
@@ -2610,7 +2079,7 @@
       <c r="N33" s="2"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/ExcelTool/LubanTools/DataTables/Datas/NpcData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/NpcData.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{929B92B0-65F5-4FA2-988B-69903AAE8C8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11250" yWindow="2100" windowWidth="42470" windowHeight="16040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="角色表" sheetId="1" r:id="rId1"/>
@@ -33,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="127">
   <si>
     <t>##var</t>
   </si>
@@ -101,6 +95,9 @@
     <t>ShowRuleTimeType</t>
   </si>
   <si>
+    <t>vector2#sep=,</t>
+  </si>
+  <si>
     <t>##</t>
   </si>
   <si>
@@ -149,6 +146,9 @@
     <t>CharacterNames+Character_NPC_01</t>
   </si>
   <si>
+    <t>0.0,0.0</t>
+  </si>
+  <si>
     <t>马吉（女主）（卧室）</t>
   </si>
   <si>
@@ -408,109 +408,19 @@
   </si>
   <si>
     <t>对话|好感|送礼|鱼饵店</t>
-  </si>
-  <si>
-    <t>vector2#sep=,</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.0,0.0</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.0,0.1</t>
-  </si>
-  <si>
-    <t>0.0,0.2</t>
-  </si>
-  <si>
-    <t>0.0,0.3</t>
-  </si>
-  <si>
-    <t>0.0,0.4</t>
-  </si>
-  <si>
-    <t>0.0,0.5</t>
-  </si>
-  <si>
-    <t>0.0,0.6</t>
-  </si>
-  <si>
-    <t>0.0,0.7</t>
-  </si>
-  <si>
-    <t>0.0,0.8</t>
-  </si>
-  <si>
-    <t>0.0,0.9</t>
-  </si>
-  <si>
-    <t>0.0,0.10</t>
-  </si>
-  <si>
-    <t>0.0,0.11</t>
-  </si>
-  <si>
-    <t>0.0,0.12</t>
-  </si>
-  <si>
-    <t>0.0,0.13</t>
-  </si>
-  <si>
-    <t>0.0,0.14</t>
-  </si>
-  <si>
-    <t>0.0,0.15</t>
-  </si>
-  <si>
-    <t>0.0,0.16</t>
-  </si>
-  <si>
-    <t>0.0,0.17</t>
-  </si>
-  <si>
-    <t>0.0,0.18</t>
-  </si>
-  <si>
-    <t>0.0,0.19</t>
-  </si>
-  <si>
-    <t>0.0,0.20</t>
-  </si>
-  <si>
-    <t>0.0,0.21</t>
-  </si>
-  <si>
-    <t>0.0,0.22</t>
-  </si>
-  <si>
-    <t>0.0,0.23</t>
-  </si>
-  <si>
-    <t>0.0,0.24</t>
-  </si>
-  <si>
-    <t>0.0,0.25</t>
-  </si>
-  <si>
-    <t>0.0,0.26</t>
-  </si>
-  <si>
-    <t>0.0,0.27</t>
-  </si>
-  <si>
-    <t>0.0,0.28</t>
-  </si>
-  <si>
-    <t>对话|好感|送礼|激情一下</t>
-    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -522,29 +432,166 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF1F2329"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="等线"/>
-      <family val="3"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -559,24 +606,198 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.39994506668294322"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399945066682943"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -599,9 +820,251 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -642,17 +1105,61 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -910,30 +1417,30 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:N33"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="2" width="8.6640625" style="2"/>
-    <col min="3" max="3" width="25.83203125" style="2" customWidth="1"/>
-    <col min="4" max="6" width="35.58203125" style="2" customWidth="1"/>
+    <col min="1" max="2" width="8.66666666666667" style="2"/>
+    <col min="3" max="3" width="25.8333333333333" style="2" customWidth="1"/>
+    <col min="4" max="6" width="35.5833333333333" style="2" customWidth="1"/>
     <col min="7" max="7" width="23" style="3" customWidth="1"/>
-    <col min="8" max="8" width="33.58203125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="33.5833333333333" style="2" customWidth="1"/>
     <col min="9" max="9" width="23.25" style="2" customWidth="1"/>
-    <col min="10" max="10" width="21.4140625" style="2" customWidth="1"/>
-    <col min="11" max="11" width="16.58203125" style="2" customWidth="1"/>
+    <col min="10" max="10" width="21.4166666666667" style="2" customWidth="1"/>
+    <col min="11" max="11" width="16.5833333333333" style="2" customWidth="1"/>
     <col min="12" max="12" width="28" style="3" customWidth="1"/>
     <col min="13" max="13" width="17.75" style="2" customWidth="1"/>
     <col min="14" max="14" width="22" style="2" customWidth="1"/>
     <col min="15" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -977,7 +1484,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:14">
       <c r="A2" s="2" t="s">
         <v>14</v>
       </c>
@@ -1018,1052 +1525,1052 @@
         <v>21</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.45">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" spans="1:14">
       <c r="B4" s="11">
         <v>10000</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E4" s="11">
         <v>10000</v>
       </c>
       <c r="G4" s="12"/>
       <c r="N4" s="1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" spans="1:14">
       <c r="B5" s="11">
         <v>10001</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E5" s="11">
         <v>10001</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G5" s="12" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="L5" s="12" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" spans="1:14">
       <c r="B6" s="11">
         <v>10002</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E6" s="11">
         <v>10001</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G6" s="12" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="L6" s="12" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" spans="1:14">
       <c r="B7" s="11">
         <v>10003</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E7" s="11">
         <v>10001</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="L7" s="12" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" spans="1:14">
       <c r="B8" s="11">
         <v>10004</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E8" s="11">
         <v>10001</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G8" s="12" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="L8" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="M8" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="M8" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="N8" s="1" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" spans="1:14">
       <c r="B9" s="11">
         <v>10005</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E9" s="11">
         <v>10001</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G9" s="12" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="L9" s="12" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" spans="1:14">
       <c r="B10" s="11">
         <v>10006</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E10" s="11">
         <v>10002</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G10" s="12" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="L10" s="12" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" spans="1:14">
       <c r="B11" s="11">
         <v>10007</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E11" s="11">
         <v>10002</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G11" s="12" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="L11" s="12" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" spans="1:14">
       <c r="B12" s="11">
         <v>10008</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E12" s="11">
         <v>10002</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G12" s="12" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="L12" s="12" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" spans="1:14">
       <c r="B13" s="11">
         <v>10009</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E13" s="11">
         <v>10002</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G13" s="12" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="L13" s="12" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" spans="1:14">
       <c r="B14" s="11">
         <v>10010</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E14" s="11">
         <v>10002</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G14" s="12" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="L14" s="12" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" spans="1:14">
       <c r="B15" s="11">
         <v>10011</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E15" s="12">
         <v>10003</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G15" s="12" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="L15" s="12" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="16" s="1" customFormat="1" spans="1:14">
       <c r="B16" s="11">
         <v>10012</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E16" s="12">
         <v>10003</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G16" s="12" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="L16" s="12" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="17" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" spans="2:14">
       <c r="B17" s="11">
         <v>10013</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E17" s="12">
         <v>10003</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G17" s="12" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="L17" s="12" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="18" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="18" s="1" customFormat="1" spans="2:14">
       <c r="B18" s="11">
         <v>10014</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E18" s="12">
         <v>10003</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G18" s="12" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="L18" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="M18" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="M18" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="N18" s="1" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="19" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="19" s="1" customFormat="1" spans="2:14">
       <c r="B19" s="11">
         <v>10015</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E19" s="11">
         <v>10004</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G19" s="12" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="L19" s="12" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="20" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="20" s="1" customFormat="1" spans="2:14">
       <c r="B20" s="11">
         <v>10016</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E20" s="11">
         <v>10004</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G20" s="12" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="L20" s="12" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="21" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="21" s="1" customFormat="1" spans="2:14">
       <c r="B21" s="11">
         <v>10017</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E21" s="11">
         <v>10004</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G21" s="12" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="L21" s="12" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="22" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="22" s="1" customFormat="1" spans="2:14">
       <c r="B22" s="11">
         <v>10018</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E22" s="11">
         <v>10004</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G22" s="12" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="L22" s="12" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="23" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="23" s="1" customFormat="1" spans="2:14">
       <c r="B23" s="11">
         <v>10019</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E23" s="11">
         <v>10005</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G23" s="12" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="L23" s="12" t="s">
-        <v>77</v>
+        <v>45</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="24" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="24" s="1" customFormat="1" spans="2:14">
       <c r="B24" s="11">
         <v>10020</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E24" s="11">
         <v>10005</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G24" s="12" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="L24" s="12" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="25" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="25" s="1" customFormat="1" spans="2:14">
       <c r="B25" s="11">
         <v>10021</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E25" s="11">
         <v>10005</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G25" s="12" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="L25" s="12" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="M25" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="26" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="26" s="1" customFormat="1" spans="2:14">
       <c r="B26" s="11">
         <v>10022</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E26" s="11">
         <v>10006</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G26" s="12" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="L26" s="12" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="27" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="27" s="1" customFormat="1" spans="2:14">
       <c r="B27" s="11">
         <v>10023</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E27" s="11">
         <v>10006</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G27" s="12" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="H27" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="J27" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="L27" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="M27" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="J27" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="L27" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="M27" s="1" t="s">
-        <v>98</v>
-      </c>
       <c r="N27" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="28" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="28" s="1" customFormat="1" spans="2:14">
       <c r="B28" s="11">
         <v>10024</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E28" s="12">
         <v>10007</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="G28" s="12" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>155</v>
+        <v>65</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="L28" s="12" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="N28" s="1" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="29" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="29" s="1" customFormat="1" spans="2:14">
       <c r="B29" s="11">
         <v>10025</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E29" s="11">
         <v>10008</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="G29" s="12" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="L29" s="12" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="M29" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="N29" s="1" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="30" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="30" s="1" customFormat="1" spans="2:14">
       <c r="B30" s="11">
         <v>10026</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E30" s="11">
         <v>10009</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G30" s="12" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="L30" s="12" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="M30" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="N30" s="1" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="31" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="31" s="1" customFormat="1" spans="2:14">
       <c r="B31" s="11">
         <v>10027</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E31" s="11">
         <v>10010</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="G31" s="12" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="L31" s="12" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="M31" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="N31" s="1" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="32" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="32" s="1" customFormat="1" spans="2:14">
       <c r="B32" s="11">
         <v>10028</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D32" s="12" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E32" s="12">
         <v>10011</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="G32" s="12" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="L32" s="12" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="M32" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="N32" s="1" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="33" spans="1:14" customFormat="1" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="33" customFormat="1" spans="1:14">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
@@ -2079,7 +2586,7 @@
       <c r="N33" s="2"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/ExcelTool/LubanTools/DataTables/Datas/NpcData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/NpcData.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B30F420-C439-4EBB-8C83-12E8FC3930EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView xWindow="0" yWindow="4840" windowWidth="42470" windowHeight="16040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="角色表" sheetId="1" r:id="rId1"/>
@@ -27,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="128">
   <si>
     <t>##var</t>
   </si>
@@ -408,19 +414,17 @@
   </si>
   <si>
     <t>对话|好感|送礼|鱼饵店</t>
+  </si>
+  <si>
+    <t>0.0,0.0</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="23">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -432,166 +436,29 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="微软雅黑"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF1F2329"/>
       <name val="微软雅黑"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <sz val="9"/>
       <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="35">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -606,198 +473,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399945066682943"/>
+        <fgColor theme="9" tint="0.39991454817346722"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -820,251 +513,9 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
   <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1105,61 +556,17 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1417,30 +824,30 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N33"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="2" width="8.66666666666667" style="2"/>
-    <col min="3" max="3" width="25.8333333333333" style="2" customWidth="1"/>
-    <col min="4" max="6" width="35.5833333333333" style="2" customWidth="1"/>
+    <col min="1" max="2" width="8.6640625" style="2"/>
+    <col min="3" max="3" width="25.83203125" style="2" customWidth="1"/>
+    <col min="4" max="6" width="35.58203125" style="2" customWidth="1"/>
     <col min="7" max="7" width="23" style="3" customWidth="1"/>
-    <col min="8" max="8" width="33.5833333333333" style="2" customWidth="1"/>
+    <col min="8" max="8" width="33.58203125" style="2" customWidth="1"/>
     <col min="9" max="9" width="23.25" style="2" customWidth="1"/>
-    <col min="10" max="10" width="21.4166666666667" style="2" customWidth="1"/>
-    <col min="11" max="11" width="16.5833333333333" style="2" customWidth="1"/>
+    <col min="10" max="10" width="21.4140625" style="2" customWidth="1"/>
+    <col min="11" max="11" width="16.58203125" style="2" customWidth="1"/>
     <col min="12" max="12" width="28" style="3" customWidth="1"/>
     <col min="13" max="13" width="17.75" style="2" customWidth="1"/>
     <col min="14" max="14" width="22" style="2" customWidth="1"/>
     <col min="15" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1484,7 +891,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>14</v>
       </c>
@@ -1528,7 +935,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>23</v>
       </c>
@@ -1572,7 +979,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" spans="1:14">
+    <row r="4" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B4" s="11">
         <v>10000</v>
       </c>
@@ -1590,7 +997,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" spans="1:14">
+    <row r="5" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B5" s="11">
         <v>10001</v>
       </c>
@@ -1625,7 +1032,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" spans="1:14">
+    <row r="6" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B6" s="11">
         <v>10002</v>
       </c>
@@ -1660,7 +1067,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" spans="1:14">
+    <row r="7" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B7" s="11">
         <v>10003</v>
       </c>
@@ -1695,7 +1102,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" spans="1:14">
+    <row r="8" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B8" s="11">
         <v>10004</v>
       </c>
@@ -1730,7 +1137,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" spans="1:14">
+    <row r="9" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B9" s="11">
         <v>10005</v>
       </c>
@@ -1765,7 +1172,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" spans="1:14">
+    <row r="10" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B10" s="11">
         <v>10006</v>
       </c>
@@ -1800,7 +1207,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="11" s="1" customFormat="1" spans="1:14">
+    <row r="11" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B11" s="11">
         <v>10007</v>
       </c>
@@ -1835,7 +1242,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" spans="1:14">
+    <row r="12" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B12" s="11">
         <v>10008</v>
       </c>
@@ -1870,7 +1277,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" spans="1:14">
+    <row r="13" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B13" s="11">
         <v>10009</v>
       </c>
@@ -1905,7 +1312,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="14" s="1" customFormat="1" spans="1:14">
+    <row r="14" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B14" s="11">
         <v>10010</v>
       </c>
@@ -1940,7 +1347,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="15" s="1" customFormat="1" spans="1:14">
+    <row r="15" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B15" s="11">
         <v>10011</v>
       </c>
@@ -1975,7 +1382,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="16" s="1" customFormat="1" spans="1:14">
+    <row r="16" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B16" s="11">
         <v>10012</v>
       </c>
@@ -2010,7 +1417,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="17" s="1" customFormat="1" spans="2:14">
+    <row r="17" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B17" s="11">
         <v>10013</v>
       </c>
@@ -2045,7 +1452,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="18" s="1" customFormat="1" spans="2:14">
+    <row r="18" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B18" s="11">
         <v>10014</v>
       </c>
@@ -2080,7 +1487,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="19" s="1" customFormat="1" spans="2:14">
+    <row r="19" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B19" s="11">
         <v>10015</v>
       </c>
@@ -2115,7 +1522,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="20" s="1" customFormat="1" spans="2:14">
+    <row r="20" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B20" s="11">
         <v>10016</v>
       </c>
@@ -2150,7 +1557,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="21" s="1" customFormat="1" spans="2:14">
+    <row r="21" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B21" s="11">
         <v>10017</v>
       </c>
@@ -2185,7 +1592,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="22" s="1" customFormat="1" spans="2:14">
+    <row r="22" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B22" s="11">
         <v>10018</v>
       </c>
@@ -2220,7 +1627,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="23" s="1" customFormat="1" spans="2:14">
+    <row r="23" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B23" s="11">
         <v>10019</v>
       </c>
@@ -2242,8 +1649,8 @@
       <c r="H23" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="J23" s="1" t="s">
-        <v>44</v>
+      <c r="J23" s="1">
+        <v>10100</v>
       </c>
       <c r="L23" s="12" t="s">
         <v>45</v>
@@ -2252,10 +1659,10 @@
         <v>91</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="24" s="1" customFormat="1" spans="2:14">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="24" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B24" s="11">
         <v>10020</v>
       </c>
@@ -2290,7 +1697,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="25" s="1" customFormat="1" spans="2:14">
+    <row r="25" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B25" s="11">
         <v>10021</v>
       </c>
@@ -2325,7 +1732,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="26" s="1" customFormat="1" spans="2:14">
+    <row r="26" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B26" s="11">
         <v>10022</v>
       </c>
@@ -2360,7 +1767,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="27" s="1" customFormat="1" spans="2:14">
+    <row r="27" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B27" s="11">
         <v>10023</v>
       </c>
@@ -2395,7 +1802,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="28" s="1" customFormat="1" spans="2:14">
+    <row r="28" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B28" s="11">
         <v>10024</v>
       </c>
@@ -2430,7 +1837,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="29" s="1" customFormat="1" spans="2:14">
+    <row r="29" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B29" s="11">
         <v>10025</v>
       </c>
@@ -2465,7 +1872,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="30" s="1" customFormat="1" spans="2:14">
+    <row r="30" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B30" s="11">
         <v>10026</v>
       </c>
@@ -2500,7 +1907,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="31" s="1" customFormat="1" spans="2:14">
+    <row r="31" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B31" s="11">
         <v>10027</v>
       </c>
@@ -2535,7 +1942,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="32" s="1" customFormat="1" spans="2:14">
+    <row r="32" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B32" s="11">
         <v>10028</v>
       </c>
@@ -2570,7 +1977,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="33" customFormat="1" spans="1:14">
+    <row r="33" spans="1:14" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
@@ -2586,7 +1993,7 @@
       <c r="N33" s="2"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/ExcelTool/LubanTools/DataTables/Datas/NpcData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/NpcData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B30F420-C439-4EBB-8C83-12E8FC3930EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DB80E3A-962E-4622-9978-1F4BDE87EC7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="4840" windowWidth="42470" windowHeight="16040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-9460" yWindow="8300" windowWidth="42470" windowHeight="19850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="角色表" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="129">
   <si>
     <t>##var</t>
   </si>
@@ -417,6 +417,10 @@
   </si>
   <si>
     <t>0.0,0.0</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>CustomShowWeek</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -517,7 +521,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -554,6 +558,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -830,7 +837,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N33"/>
+  <dimension ref="A1:O33"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="2" width="8.6640625" style="2"/>
@@ -843,11 +850,12 @@
     <col min="11" max="11" width="16.58203125" style="2" customWidth="1"/>
     <col min="12" max="12" width="28" style="3" customWidth="1"/>
     <col min="13" max="13" width="17.75" style="2" customWidth="1"/>
-    <col min="14" max="14" width="22" style="2" customWidth="1"/>
-    <col min="15" max="16384" width="9" style="2"/>
+    <col min="14" max="14" width="17.33203125" style="2" customWidth="1"/>
+    <col min="15" max="15" width="18.9140625" style="2" customWidth="1"/>
+    <col min="16" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -890,8 +898,11 @@
       <c r="N1" s="7" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="O1" s="13" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>14</v>
       </c>
@@ -935,7 +946,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>23</v>
       </c>
@@ -979,7 +990,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B4" s="11">
         <v>10000</v>
       </c>
@@ -997,7 +1008,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B5" s="11">
         <v>10001</v>
       </c>
@@ -1032,7 +1043,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="6" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B6" s="11">
         <v>10002</v>
       </c>
@@ -1067,7 +1078,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="7" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B7" s="11">
         <v>10003</v>
       </c>
@@ -1102,7 +1113,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="8" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B8" s="11">
         <v>10004</v>
       </c>
@@ -1137,7 +1148,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="9" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B9" s="11">
         <v>10005</v>
       </c>
@@ -1172,7 +1183,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="10" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B10" s="11">
         <v>10006</v>
       </c>
@@ -1207,7 +1218,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="11" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B11" s="11">
         <v>10007</v>
       </c>
@@ -1242,7 +1253,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="12" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B12" s="11">
         <v>10008</v>
       </c>
@@ -1277,7 +1288,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="13" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B13" s="11">
         <v>10009</v>
       </c>
@@ -1312,7 +1323,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="14" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B14" s="11">
         <v>10010</v>
       </c>
@@ -1347,7 +1358,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="15" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B15" s="11">
         <v>10011</v>
       </c>
@@ -1382,7 +1393,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="16" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B16" s="11">
         <v>10012</v>
       </c>

--- a/ExcelTool/LubanTools/DataTables/Datas/NpcData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/NpcData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DB80E3A-962E-4622-9978-1F4BDE87EC7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48D93C51-F21F-4D37-9019-66D50A79903F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-9460" yWindow="8300" windowWidth="42470" windowHeight="19850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-17630" yWindow="7250" windowWidth="63710" windowHeight="21860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="角色表" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="128">
   <si>
     <t>##var</t>
   </si>
@@ -417,10 +417,6 @@
   </si>
   <si>
     <t>0.0,0.0</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>CustomShowWeek</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -521,7 +517,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -558,9 +554,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -837,7 +830,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O33"/>
+  <dimension ref="A1:N33"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="2" width="8.6640625" style="2"/>
@@ -851,11 +844,10 @@
     <col min="12" max="12" width="28" style="3" customWidth="1"/>
     <col min="13" max="13" width="17.75" style="2" customWidth="1"/>
     <col min="14" max="14" width="17.33203125" style="2" customWidth="1"/>
-    <col min="15" max="15" width="18.9140625" style="2" customWidth="1"/>
-    <col min="16" max="16384" width="9" style="2"/>
+    <col min="15" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -898,11 +890,8 @@
       <c r="N1" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="13" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.45">
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>14</v>
       </c>
@@ -946,7 +935,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>23</v>
       </c>
@@ -990,7 +979,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B4" s="11">
         <v>10000</v>
       </c>
@@ -1008,7 +997,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B5" s="11">
         <v>10001</v>
       </c>
@@ -1043,7 +1032,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="6" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B6" s="11">
         <v>10002</v>
       </c>
@@ -1078,7 +1067,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="7" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B7" s="11">
         <v>10003</v>
       </c>
@@ -1113,7 +1102,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="8" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B8" s="11">
         <v>10004</v>
       </c>
@@ -1148,7 +1137,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="9" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B9" s="11">
         <v>10005</v>
       </c>
@@ -1183,7 +1172,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="10" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B10" s="11">
         <v>10006</v>
       </c>
@@ -1218,7 +1207,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="11" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B11" s="11">
         <v>10007</v>
       </c>
@@ -1253,7 +1242,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="12" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B12" s="11">
         <v>10008</v>
       </c>
@@ -1288,7 +1277,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="13" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B13" s="11">
         <v>10009</v>
       </c>
@@ -1323,7 +1312,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="14" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B14" s="11">
         <v>10010</v>
       </c>
@@ -1358,7 +1347,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="15" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B15" s="11">
         <v>10011</v>
       </c>
@@ -1393,7 +1382,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="16" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B16" s="11">
         <v>10012</v>
       </c>

--- a/ExcelTool/LubanTools/DataTables/Datas/NpcData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/NpcData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48D93C51-F21F-4D37-9019-66D50A79903F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D6BA4BB-0F7C-4287-911C-F9B4F41280EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-17630" yWindow="7250" windowWidth="63710" windowHeight="21860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="43155" yWindow="9810" windowWidth="42465" windowHeight="19845" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="角色表" sheetId="1" r:id="rId1"/>
@@ -296,127 +296,128 @@
     <t>傍晚|半夜</t>
   </si>
   <si>
+    <t>CharacterNames+Character_NPC_06</t>
+  </si>
+  <si>
+    <t>ShangDianXiaoMei</t>
+  </si>
+  <si>
+    <t>对话|好感|送礼|超市|激情一下</t>
+  </si>
+  <si>
+    <t>早上|中午|傍晚</t>
+  </si>
+  <si>
+    <t>友莉（超市小妹）(公园)</t>
+  </si>
+  <si>
+    <t>友莉（超市小妹）(小河)</t>
+  </si>
+  <si>
+    <t>对话|好感|送礼|鱼饵店|激情一下</t>
+  </si>
+  <si>
+    <t>桃（酒吧）</t>
+  </si>
+  <si>
+    <t>CharacterNames+Character_NPC_07</t>
+  </si>
+  <si>
+    <t>单人_酒保@2x</t>
+  </si>
+  <si>
+    <t>酒保@2x</t>
+  </si>
+  <si>
+    <t>对话|好感|送礼|去赌场</t>
+  </si>
+  <si>
+    <t>中午|傍晚|半夜</t>
+  </si>
+  <si>
+    <t>桃（赌场）</t>
+  </si>
+  <si>
+    <t>对话|好感|送礼|游戏币商店|激情一下</t>
+  </si>
+  <si>
+    <t>千织（工厂）</t>
+  </si>
+  <si>
+    <t>CharacterNames+Character_NPC_08</t>
+  </si>
+  <si>
+    <t>单人_经理@2x</t>
+  </si>
+  <si>
+    <t>PlantManager</t>
+  </si>
+  <si>
+    <t>紬（服装店）</t>
+  </si>
+  <si>
+    <t>CharacterNames+Character_NPC_09</t>
+  </si>
+  <si>
+    <t>单人_布料店@2x</t>
+  </si>
+  <si>
+    <t>布料店@2x</t>
+  </si>
+  <si>
+    <t>对话|好感|送礼|布料店|激情一下</t>
+  </si>
+  <si>
+    <t>巧蜜（摄影店）</t>
+  </si>
+  <si>
+    <t>CharacterNames+Character_NPC_10</t>
+  </si>
+  <si>
+    <t>单人_摄影小妹@2x</t>
+  </si>
+  <si>
+    <t>摄影小妹@2x</t>
+  </si>
+  <si>
+    <t>对话|好感|送礼|摄影|激情一下</t>
+  </si>
+  <si>
+    <t>一郎（果蔬店）</t>
+  </si>
+  <si>
+    <t>CharacterNames+Character_NPC_11</t>
+  </si>
+  <si>
+    <t>单人_果蔬大叔@2x</t>
+  </si>
+  <si>
+    <t>果蔬店大叔@2x</t>
+  </si>
+  <si>
+    <t>对话|好感|送礼|果蔬店</t>
+  </si>
+  <si>
+    <t>二爺（钓鱼大爷）</t>
+  </si>
+  <si>
+    <t>CharacterNames+Character_NPC_12</t>
+  </si>
+  <si>
+    <t>单人_渔夫@2x</t>
+  </si>
+  <si>
+    <t>钓鱼老人@2x</t>
+  </si>
+  <si>
+    <t>对话|好感|送礼|鱼饵店</t>
+  </si>
+  <si>
+    <t>0.0,0.0</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
     <t>友莉（超市小妹）(超市)</t>
-  </si>
-  <si>
-    <t>CharacterNames+Character_NPC_06</t>
-  </si>
-  <si>
-    <t>ShangDianXiaoMei</t>
-  </si>
-  <si>
-    <t>对话|好感|送礼|超市|激情一下</t>
-  </si>
-  <si>
-    <t>早上|中午|傍晚</t>
-  </si>
-  <si>
-    <t>友莉（超市小妹）(公园)</t>
-  </si>
-  <si>
-    <t>友莉（超市小妹）(小河)</t>
-  </si>
-  <si>
-    <t>对话|好感|送礼|鱼饵店|激情一下</t>
-  </si>
-  <si>
-    <t>桃（酒吧）</t>
-  </si>
-  <si>
-    <t>CharacterNames+Character_NPC_07</t>
-  </si>
-  <si>
-    <t>单人_酒保@2x</t>
-  </si>
-  <si>
-    <t>酒保@2x</t>
-  </si>
-  <si>
-    <t>对话|好感|送礼|去赌场</t>
-  </si>
-  <si>
-    <t>中午|傍晚|半夜</t>
-  </si>
-  <si>
-    <t>桃（赌场）</t>
-  </si>
-  <si>
-    <t>对话|好感|送礼|游戏币商店|激情一下</t>
-  </si>
-  <si>
-    <t>千织（工厂）</t>
-  </si>
-  <si>
-    <t>CharacterNames+Character_NPC_08</t>
-  </si>
-  <si>
-    <t>单人_经理@2x</t>
-  </si>
-  <si>
-    <t>PlantManager</t>
-  </si>
-  <si>
-    <t>紬（服装店）</t>
-  </si>
-  <si>
-    <t>CharacterNames+Character_NPC_09</t>
-  </si>
-  <si>
-    <t>单人_布料店@2x</t>
-  </si>
-  <si>
-    <t>布料店@2x</t>
-  </si>
-  <si>
-    <t>对话|好感|送礼|布料店|激情一下</t>
-  </si>
-  <si>
-    <t>巧蜜（摄影店）</t>
-  </si>
-  <si>
-    <t>CharacterNames+Character_NPC_10</t>
-  </si>
-  <si>
-    <t>单人_摄影小妹@2x</t>
-  </si>
-  <si>
-    <t>摄影小妹@2x</t>
-  </si>
-  <si>
-    <t>对话|好感|送礼|摄影|激情一下</t>
-  </si>
-  <si>
-    <t>一郎（果蔬店）</t>
-  </si>
-  <si>
-    <t>CharacterNames+Character_NPC_11</t>
-  </si>
-  <si>
-    <t>单人_果蔬大叔@2x</t>
-  </si>
-  <si>
-    <t>果蔬店大叔@2x</t>
-  </si>
-  <si>
-    <t>对话|好感|送礼|果蔬店</t>
-  </si>
-  <si>
-    <t>二爺（钓鱼大爷）</t>
-  </si>
-  <si>
-    <t>CharacterNames+Character_NPC_12</t>
-  </si>
-  <si>
-    <t>单人_渔夫@2x</t>
-  </si>
-  <si>
-    <t>钓鱼老人@2x</t>
-  </si>
-  <si>
-    <t>对话|好感|送礼|鱼饵店</t>
-  </si>
-  <si>
-    <t>0.0,0.0</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -1632,22 +1633,22 @@
         <v>10019</v>
       </c>
       <c r="C23" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="D23" s="12" t="s">
         <v>87</v>
-      </c>
-      <c r="D23" s="12" t="s">
-        <v>88</v>
       </c>
       <c r="E23" s="11">
         <v>10005</v>
       </c>
       <c r="F23" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="G23" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="H23" s="1" t="s">
         <v>89</v>
-      </c>
-      <c r="G23" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="H23" s="1" t="s">
-        <v>90</v>
       </c>
       <c r="J23" s="1">
         <v>10100</v>
@@ -1656,10 +1657,10 @@
         <v>45</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="24" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
@@ -1667,19 +1668,19 @@
         <v>10020</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E24" s="11">
         <v>10005</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G24" s="12" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H24" s="1" t="s">
         <v>65</v>
@@ -1702,22 +1703,22 @@
         <v>10021</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E25" s="11">
         <v>10005</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G25" s="12" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J25" s="1" t="s">
         <v>44</v>
@@ -1737,22 +1738,22 @@
         <v>10022</v>
       </c>
       <c r="C26" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="D26" s="12" t="s">
         <v>95</v>
-      </c>
-      <c r="D26" s="12" t="s">
-        <v>96</v>
       </c>
       <c r="E26" s="11">
         <v>10006</v>
       </c>
       <c r="F26" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="G26" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="G26" s="12" t="s">
+      <c r="H26" s="1" t="s">
         <v>98</v>
-      </c>
-      <c r="H26" s="1" t="s">
-        <v>99</v>
       </c>
       <c r="J26" s="1" t="s">
         <v>44</v>
@@ -1761,7 +1762,7 @@
         <v>45</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="N26" s="1" t="s">
         <v>39</v>
@@ -1772,22 +1773,22 @@
         <v>10023</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E27" s="11">
         <v>10006</v>
       </c>
       <c r="F27" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="G27" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="G27" s="12" t="s">
-        <v>98</v>
-      </c>
       <c r="H27" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="J27" s="1" t="s">
         <v>44</v>
@@ -1796,7 +1797,7 @@
         <v>45</v>
       </c>
       <c r="M27" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="N27" s="1" t="s">
         <v>39</v>
@@ -1807,19 +1808,19 @@
         <v>10024</v>
       </c>
       <c r="C28" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="D28" s="12" t="s">
         <v>103</v>
-      </c>
-      <c r="D28" s="12" t="s">
-        <v>104</v>
       </c>
       <c r="E28" s="12">
         <v>10007</v>
       </c>
       <c r="F28" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="G28" s="12" t="s">
         <v>105</v>
-      </c>
-      <c r="G28" s="12" t="s">
-        <v>106</v>
       </c>
       <c r="H28" s="1" t="s">
         <v>65</v>
@@ -1831,7 +1832,7 @@
         <v>45</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="N28" s="1" t="s">
         <v>39</v>
@@ -1842,22 +1843,22 @@
         <v>10025</v>
       </c>
       <c r="C29" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="D29" s="12" t="s">
         <v>107</v>
-      </c>
-      <c r="D29" s="12" t="s">
-        <v>108</v>
       </c>
       <c r="E29" s="11">
         <v>10008</v>
       </c>
       <c r="F29" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="G29" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="G29" s="12" t="s">
+      <c r="H29" s="1" t="s">
         <v>110</v>
-      </c>
-      <c r="H29" s="1" t="s">
-        <v>111</v>
       </c>
       <c r="J29" s="1" t="s">
         <v>44</v>
@@ -1866,7 +1867,7 @@
         <v>45</v>
       </c>
       <c r="M29" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="N29" s="1" t="s">
         <v>39</v>
@@ -1877,22 +1878,22 @@
         <v>10026</v>
       </c>
       <c r="C30" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="D30" s="12" t="s">
         <v>112</v>
-      </c>
-      <c r="D30" s="12" t="s">
-        <v>113</v>
       </c>
       <c r="E30" s="11">
         <v>10009</v>
       </c>
       <c r="F30" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="G30" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="G30" s="12" t="s">
+      <c r="H30" s="1" t="s">
         <v>115</v>
-      </c>
-      <c r="H30" s="1" t="s">
-        <v>116</v>
       </c>
       <c r="J30" s="1" t="s">
         <v>44</v>
@@ -1901,7 +1902,7 @@
         <v>79</v>
       </c>
       <c r="M30" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="N30" s="1" t="s">
         <v>39</v>
@@ -1912,22 +1913,22 @@
         <v>10027</v>
       </c>
       <c r="C31" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="D31" s="12" t="s">
         <v>117</v>
-      </c>
-      <c r="D31" s="12" t="s">
-        <v>118</v>
       </c>
       <c r="E31" s="11">
         <v>10010</v>
       </c>
       <c r="F31" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="G31" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="G31" s="12" t="s">
+      <c r="H31" s="1" t="s">
         <v>120</v>
-      </c>
-      <c r="H31" s="1" t="s">
-        <v>121</v>
       </c>
       <c r="J31" s="1" t="s">
         <v>44</v>
@@ -1936,7 +1937,7 @@
         <v>45</v>
       </c>
       <c r="M31" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="N31" s="1" t="s">
         <v>39</v>
@@ -1947,22 +1948,22 @@
         <v>10028</v>
       </c>
       <c r="C32" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="D32" s="12" t="s">
         <v>122</v>
-      </c>
-      <c r="D32" s="12" t="s">
-        <v>123</v>
       </c>
       <c r="E32" s="12">
         <v>10011</v>
       </c>
       <c r="F32" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="G32" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="G32" s="12" t="s">
+      <c r="H32" s="1" t="s">
         <v>125</v>
-      </c>
-      <c r="H32" s="1" t="s">
-        <v>126</v>
       </c>
       <c r="J32" s="1" t="s">
         <v>44</v>

--- a/ExcelTool/LubanTools/DataTables/Datas/NpcData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/NpcData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D6BA4BB-0F7C-4287-911C-F9B4F41280EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1D42405-2FED-46B7-8060-99B5B1D5CD68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="43155" yWindow="9810" windowWidth="42465" windowHeight="19845" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="1660" windowWidth="38610" windowHeight="19220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="角色表" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="130">
   <si>
     <t>##var</t>
   </si>
@@ -408,9 +408,6 @@
   </si>
   <si>
     <t>钓鱼老人@2x</t>
-  </si>
-  <si>
-    <t>对话|好感|送礼|鱼饵店</t>
   </si>
   <si>
     <t>0.0,0.0</t>
@@ -418,6 +415,18 @@
   </si>
   <si>
     <t>友莉（超市小妹）(超市)</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>友莉(男主客厅)</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>对话|好感|送礼|鱼饵店</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>对话</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -1633,7 +1642,7 @@
         <v>10019</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D23" s="12" t="s">
         <v>87</v>
@@ -1660,7 +1669,7 @@
         <v>90</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="24" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
@@ -1963,7 +1972,7 @@
         <v>124</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="J32" s="1" t="s">
         <v>44</v>
@@ -1980,18 +1989,41 @@
     </row>
     <row r="33" spans="1:14" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A33" s="2"/>
-      <c r="B33" s="2"/>
-      <c r="C33" s="2"/>
-      <c r="D33" s="2"/>
-      <c r="E33" s="2"/>
-      <c r="F33" s="2"/>
-      <c r="G33" s="3"/>
-      <c r="H33" s="2"/>
+      <c r="B33" s="11">
+        <v>10029</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="D33" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="E33" s="11">
+        <v>10005</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="G33" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>129</v>
+      </c>
       <c r="I33" s="2"/>
-      <c r="J33" s="2"/>
+      <c r="J33" s="1" t="s">
+        <v>44</v>
+      </c>
       <c r="K33" s="2"/>
-      <c r="L33" s="3"/>
-      <c r="N33" s="2"/>
+      <c r="L33" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="M33" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="N33" s="1" t="s">
+        <v>39</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>

--- a/ExcelTool/LubanTools/DataTables/Datas/NpcData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/NpcData.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1D42405-2FED-46B7-8060-99B5B1D5CD68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1660" windowWidth="38610" windowHeight="19220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="角色表" sheetId="1" r:id="rId1"/>
@@ -33,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="127">
   <si>
     <t>##var</t>
   </si>
@@ -296,6 +290,9 @@
     <t>傍晚|半夜</t>
   </si>
   <si>
+    <t>友莉（超市小妹）(超市)</t>
+  </si>
+  <si>
     <t>CharacterNames+Character_NPC_06</t>
   </si>
   <si>
@@ -410,31 +407,20 @@
     <t>钓鱼老人@2x</t>
   </si>
   <si>
-    <t>0.0,0.0</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>友莉（超市小妹）(超市)</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>友莉(男主客厅)</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>对话|好感|送礼|鱼饵店</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>对话</t>
-    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -446,29 +432,166 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF1F2329"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="等线"/>
-      <family val="3"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -483,24 +606,210 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.39991454817346722"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399914548173467"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -523,9 +832,251 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -566,17 +1117,61 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -834,30 +1429,30 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N33"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:N32"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="2" width="8.6640625" style="2"/>
-    <col min="3" max="3" width="25.83203125" style="2" customWidth="1"/>
-    <col min="4" max="6" width="35.58203125" style="2" customWidth="1"/>
+    <col min="1" max="2" width="8.66666666666667" style="2"/>
+    <col min="3" max="3" width="25.8333333333333" style="2" customWidth="1"/>
+    <col min="4" max="6" width="35.5833333333333" style="2" customWidth="1"/>
     <col min="7" max="7" width="23" style="3" customWidth="1"/>
-    <col min="8" max="8" width="33.58203125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="33.5833333333333" style="2" customWidth="1"/>
     <col min="9" max="9" width="23.25" style="2" customWidth="1"/>
-    <col min="10" max="10" width="21.4140625" style="2" customWidth="1"/>
-    <col min="11" max="11" width="16.58203125" style="2" customWidth="1"/>
+    <col min="10" max="10" width="21.4166666666667" style="2" customWidth="1"/>
+    <col min="11" max="11" width="16.5833333333333" style="2" customWidth="1"/>
     <col min="12" max="12" width="28" style="3" customWidth="1"/>
     <col min="13" max="13" width="17.75" style="2" customWidth="1"/>
-    <col min="14" max="14" width="17.33203125" style="2" customWidth="1"/>
+    <col min="14" max="14" width="17.3333333333333" style="2" customWidth="1"/>
     <col min="15" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -901,7 +1496,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:14">
       <c r="A2" s="2" t="s">
         <v>14</v>
       </c>
@@ -945,7 +1540,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:14">
       <c r="A3" s="2" t="s">
         <v>23</v>
       </c>
@@ -989,7 +1584,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="4" s="1" customFormat="1" spans="1:14">
       <c r="B4" s="11">
         <v>10000</v>
       </c>
@@ -1007,7 +1602,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="5" s="1" customFormat="1" spans="1:14">
       <c r="B5" s="11">
         <v>10001</v>
       </c>
@@ -1042,7 +1637,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="6" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="6" s="1" customFormat="1" spans="1:14">
       <c r="B6" s="11">
         <v>10002</v>
       </c>
@@ -1077,7 +1672,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="7" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="7" s="1" customFormat="1" spans="1:14">
       <c r="B7" s="11">
         <v>10003</v>
       </c>
@@ -1112,7 +1707,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="8" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="8" s="1" customFormat="1" spans="1:14">
       <c r="B8" s="11">
         <v>10004</v>
       </c>
@@ -1147,7 +1742,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="9" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="9" s="1" customFormat="1" spans="1:14">
       <c r="B9" s="11">
         <v>10005</v>
       </c>
@@ -1182,7 +1777,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="10" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="10" s="1" customFormat="1" spans="1:14">
       <c r="B10" s="11">
         <v>10006</v>
       </c>
@@ -1217,7 +1812,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="11" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="11" s="1" customFormat="1" spans="1:14">
       <c r="B11" s="11">
         <v>10007</v>
       </c>
@@ -1252,7 +1847,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="12" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="12" s="1" customFormat="1" spans="1:14">
       <c r="B12" s="11">
         <v>10008</v>
       </c>
@@ -1287,7 +1882,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="13" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="13" s="1" customFormat="1" spans="1:14">
       <c r="B13" s="11">
         <v>10009</v>
       </c>
@@ -1322,7 +1917,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="14" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="14" s="1" customFormat="1" spans="1:14">
       <c r="B14" s="11">
         <v>10010</v>
       </c>
@@ -1357,7 +1952,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="15" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="15" s="1" customFormat="1" spans="1:14">
       <c r="B15" s="11">
         <v>10011</v>
       </c>
@@ -1392,7 +1987,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="16" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="16" s="1" customFormat="1" spans="1:14">
       <c r="B16" s="11">
         <v>10012</v>
       </c>
@@ -1427,7 +2022,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="17" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="17" s="1" customFormat="1" spans="2:14">
       <c r="B17" s="11">
         <v>10013</v>
       </c>
@@ -1462,7 +2057,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="18" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="18" s="1" customFormat="1" spans="2:14">
       <c r="B18" s="11">
         <v>10014</v>
       </c>
@@ -1497,7 +2092,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="19" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="19" s="1" customFormat="1" spans="2:14">
       <c r="B19" s="11">
         <v>10015</v>
       </c>
@@ -1532,7 +2127,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="20" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="20" s="1" customFormat="1" spans="2:14">
       <c r="B20" s="11">
         <v>10016</v>
       </c>
@@ -1567,7 +2162,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="21" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="21" s="1" customFormat="1" spans="2:14">
       <c r="B21" s="11">
         <v>10017</v>
       </c>
@@ -1602,7 +2197,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="22" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="22" s="1" customFormat="1" spans="2:14">
       <c r="B22" s="11">
         <v>10018</v>
       </c>
@@ -1637,27 +2232,27 @@
         <v>39</v>
       </c>
     </row>
-    <row r="23" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="23" s="1" customFormat="1" spans="2:14">
       <c r="B23" s="11">
         <v>10019</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>126</v>
+        <v>87</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E23" s="11">
         <v>10005</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G23" s="12" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J23" s="1">
         <v>10100</v>
@@ -1666,30 +2261,30 @@
         <v>45</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="24" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="24" s="1" customFormat="1" spans="2:14">
       <c r="B24" s="11">
         <v>10020</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E24" s="11">
         <v>10005</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G24" s="12" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H24" s="1" t="s">
         <v>65</v>
@@ -1707,27 +2302,27 @@
         <v>39</v>
       </c>
     </row>
-    <row r="25" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="25" s="1" customFormat="1" spans="2:14">
       <c r="B25" s="11">
         <v>10021</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E25" s="11">
         <v>10005</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G25" s="12" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J25" s="1" t="s">
         <v>44</v>
@@ -1742,27 +2337,27 @@
         <v>39</v>
       </c>
     </row>
-    <row r="26" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="26" s="1" customFormat="1" spans="2:14">
       <c r="B26" s="11">
         <v>10022</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E26" s="11">
         <v>10006</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G26" s="12" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="J26" s="1" t="s">
         <v>44</v>
@@ -1771,33 +2366,33 @@
         <v>45</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="N26" s="1" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="27" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="27" s="1" customFormat="1" spans="2:14">
       <c r="B27" s="11">
         <v>10023</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E27" s="11">
         <v>10006</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G27" s="12" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="J27" s="1" t="s">
         <v>44</v>
@@ -1806,30 +2401,30 @@
         <v>45</v>
       </c>
       <c r="M27" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="N27" s="1" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="28" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="28" s="1" customFormat="1" spans="2:14">
       <c r="B28" s="11">
         <v>10024</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E28" s="12">
         <v>10007</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G28" s="12" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H28" s="1" t="s">
         <v>65</v>
@@ -1841,33 +2436,33 @@
         <v>45</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="N28" s="1" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="29" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="29" s="1" customFormat="1" spans="2:14">
       <c r="B29" s="11">
         <v>10025</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E29" s="11">
         <v>10008</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G29" s="12" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="J29" s="1" t="s">
         <v>44</v>
@@ -1876,33 +2471,33 @@
         <v>45</v>
       </c>
       <c r="M29" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="N29" s="1" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="30" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="30" s="1" customFormat="1" spans="2:14">
       <c r="B30" s="11">
         <v>10026</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E30" s="11">
         <v>10009</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G30" s="12" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J30" s="1" t="s">
         <v>44</v>
@@ -1911,33 +2506,33 @@
         <v>79</v>
       </c>
       <c r="M30" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="N30" s="1" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="31" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="31" s="1" customFormat="1" spans="2:14">
       <c r="B31" s="11">
         <v>10027</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E31" s="11">
         <v>10010</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G31" s="12" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="J31" s="1" t="s">
         <v>44</v>
@@ -1946,33 +2541,33 @@
         <v>45</v>
       </c>
       <c r="M31" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="N31" s="1" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="32" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="32" s="1" customFormat="1" spans="2:14">
       <c r="B32" s="11">
         <v>10028</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D32" s="12" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E32" s="12">
         <v>10011</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G32" s="12" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="J32" s="1" t="s">
         <v>44</v>
@@ -1987,46 +2582,8 @@
         <v>39</v>
       </c>
     </row>
-    <row r="33" spans="1:14" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A33" s="2"/>
-      <c r="B33" s="11">
-        <v>10029</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="D33" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="E33" s="11">
-        <v>10005</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="G33" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="H33" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="I33" s="2"/>
-      <c r="J33" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="K33" s="2"/>
-      <c r="L33" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="M33" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="N33" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/ExcelTool/LubanTools/DataTables/Datas/NpcData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/NpcData.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="128">
   <si>
     <t>##var</t>
   </si>
@@ -348,6 +348,9 @@
   </si>
   <si>
     <t>PlantManager</t>
+  </si>
+  <si>
+    <t>对话|好感|送礼|激情一下|工厂制作</t>
   </si>
   <si>
     <t>紬（服装店）</t>
@@ -591,7 +594,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="37">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -678,12 +681,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -793,12 +790,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1011,70 +1002,70 @@
     <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2427,7 +2418,7 @@
         <v>106</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>65</v>
+        <v>107</v>
       </c>
       <c r="J28" s="1" t="s">
         <v>44</v>
@@ -2447,22 +2438,22 @@
         <v>10025</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E29" s="11">
         <v>10008</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G29" s="12" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="J29" s="1" t="s">
         <v>44</v>
@@ -2482,22 +2473,22 @@
         <v>10026</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E30" s="11">
         <v>10009</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G30" s="12" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="J30" s="1" t="s">
         <v>44</v>
@@ -2517,22 +2508,22 @@
         <v>10027</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E31" s="11">
         <v>10010</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G31" s="12" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="J31" s="1" t="s">
         <v>44</v>
@@ -2552,22 +2543,22 @@
         <v>10028</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D32" s="12" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E32" s="12">
         <v>10011</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G32" s="12" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J32" s="1" t="s">
         <v>44</v>

--- a/ExcelTool/LubanTools/DataTables/Datas/NpcData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/NpcData.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="129">
   <si>
     <t>##var</t>
   </si>
@@ -176,6 +176,9 @@
     <t>马吉（女主）（客厅）</t>
   </si>
   <si>
+    <t>对话|好感|送礼|厨房</t>
+  </si>
+  <si>
     <t>周一|周二|周三|周四|周五</t>
   </si>
   <si>
@@ -335,7 +338,7 @@
     <t>桃（赌场）</t>
   </si>
   <si>
-    <t>对话|好感|送礼|游戏币商店|激情一下</t>
+    <t>对话|好感|送礼|游戏币商店|激情一下|娃娃机|爆点游戏|女巫毒药</t>
   </si>
   <si>
     <t>千织（工厂）</t>
@@ -410,7 +413,7 @@
     <t>钓鱼老人@2x</t>
   </si>
   <si>
-    <t>对话|好感|送礼|鱼饵店</t>
+    <t>对话|好感|送礼|鱼饵店|钓鱼</t>
   </si>
 </sst>
 </file>
@@ -1683,16 +1686,16 @@
         <v>42</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="J7" s="1" t="s">
         <v>44</v>
       </c>
       <c r="L7" s="12" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="N7" s="1" t="s">
         <v>39</v>
@@ -1703,7 +1706,7 @@
         <v>10004</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D8" s="12" t="s">
         <v>41</v>
@@ -1724,10 +1727,10 @@
         <v>44</v>
       </c>
       <c r="L8" s="12" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="N8" s="1" t="s">
         <v>39</v>
@@ -1738,7 +1741,7 @@
         <v>10005</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D9" s="12" t="s">
         <v>41</v>
@@ -1753,7 +1756,7 @@
         <v>42</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J9" s="1" t="s">
         <v>44</v>
@@ -1762,7 +1765,7 @@
         <v>45</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="N9" s="1" t="s">
         <v>39</v>
@@ -1773,19 +1776,19 @@
         <v>10006</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E10" s="11">
         <v>10002</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G10" s="12" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>43</v>
@@ -1794,10 +1797,10 @@
         <v>44</v>
       </c>
       <c r="L10" s="12" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="N10" s="1" t="s">
         <v>39</v>
@@ -1808,19 +1811,19 @@
         <v>10007</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E11" s="11">
         <v>10002</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G11" s="12" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>43</v>
@@ -1843,19 +1846,19 @@
         <v>10008</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E12" s="11">
         <v>10002</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G12" s="12" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>43</v>
@@ -1864,10 +1867,10 @@
         <v>44</v>
       </c>
       <c r="L12" s="12" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="N12" s="1" t="s">
         <v>39</v>
@@ -1878,22 +1881,22 @@
         <v>10009</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E13" s="11">
         <v>10002</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G13" s="12" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J13" s="1" t="s">
         <v>44</v>
@@ -1902,7 +1905,7 @@
         <v>45</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="N13" s="1" t="s">
         <v>39</v>
@@ -1913,22 +1916,22 @@
         <v>10010</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E14" s="11">
         <v>10002</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G14" s="12" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J14" s="1" t="s">
         <v>44</v>
@@ -1948,19 +1951,19 @@
         <v>10011</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E15" s="12">
         <v>10003</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G15" s="12" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H15" s="1" t="s">
         <v>43</v>
@@ -1969,10 +1972,10 @@
         <v>44</v>
       </c>
       <c r="L15" s="12" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="N15" s="1" t="s">
         <v>39</v>
@@ -1983,31 +1986,31 @@
         <v>10012</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E16" s="12">
         <v>10003</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G16" s="12" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J16" s="1" t="s">
         <v>44</v>
       </c>
       <c r="L16" s="12" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="N16" s="1" t="s">
         <v>39</v>
@@ -2018,19 +2021,19 @@
         <v>10013</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E17" s="12">
         <v>10003</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G17" s="12" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>43</v>
@@ -2039,10 +2042,10 @@
         <v>44</v>
       </c>
       <c r="L17" s="12" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="N17" s="1" t="s">
         <v>39</v>
@@ -2053,31 +2056,31 @@
         <v>10014</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E18" s="12">
         <v>10003</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G18" s="12" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J18" s="1" t="s">
         <v>44</v>
       </c>
       <c r="L18" s="12" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="N18" s="1" t="s">
         <v>39</v>
@@ -2088,31 +2091,31 @@
         <v>10015</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E19" s="11">
         <v>10004</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G19" s="12" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J19" s="1" t="s">
         <v>44</v>
       </c>
       <c r="L19" s="12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="N19" s="1" t="s">
         <v>39</v>
@@ -2123,28 +2126,28 @@
         <v>10016</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E20" s="11">
         <v>10004</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G20" s="12" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J20" s="1" t="s">
         <v>44</v>
       </c>
       <c r="L20" s="12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M20" s="1" t="s">
         <v>46</v>
@@ -2158,19 +2161,19 @@
         <v>10017</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E21" s="11">
         <v>10004</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G21" s="12" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H21" s="1" t="s">
         <v>43</v>
@@ -2179,7 +2182,7 @@
         <v>44</v>
       </c>
       <c r="L21" s="12" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M21" s="1" t="s">
         <v>47</v>
@@ -2193,19 +2196,19 @@
         <v>10018</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E22" s="11">
         <v>10004</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G22" s="12" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H22" s="1" t="s">
         <v>43</v>
@@ -2214,10 +2217,10 @@
         <v>44</v>
       </c>
       <c r="L22" s="12" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="N22" s="1" t="s">
         <v>39</v>
@@ -2228,22 +2231,22 @@
         <v>10019</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E23" s="11">
         <v>10005</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G23" s="12" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J23" s="1">
         <v>10100</v>
@@ -2252,7 +2255,7 @@
         <v>45</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N23" s="1" t="s">
         <v>39</v>
@@ -2263,31 +2266,31 @@
         <v>10020</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E24" s="11">
         <v>10005</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G24" s="12" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J24" s="1" t="s">
         <v>44</v>
       </c>
       <c r="L24" s="12" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="N24" s="1" t="s">
         <v>39</v>
@@ -2298,28 +2301,28 @@
         <v>10021</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E25" s="11">
         <v>10005</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G25" s="12" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J25" s="1" t="s">
         <v>44</v>
       </c>
       <c r="L25" s="12" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M25" s="1" t="s">
         <v>47</v>
@@ -2333,22 +2336,22 @@
         <v>10022</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E26" s="11">
         <v>10006</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G26" s="12" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="J26" s="1" t="s">
         <v>44</v>
@@ -2357,7 +2360,7 @@
         <v>45</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N26" s="1" t="s">
         <v>39</v>
@@ -2368,22 +2371,22 @@
         <v>10023</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E27" s="11">
         <v>10006</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G27" s="12" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="J27" s="1" t="s">
         <v>44</v>
@@ -2392,7 +2395,7 @@
         <v>45</v>
       </c>
       <c r="M27" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N27" s="1" t="s">
         <v>39</v>
@@ -2403,22 +2406,22 @@
         <v>10024</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E28" s="12">
         <v>10007</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G28" s="12" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="J28" s="1" t="s">
         <v>44</v>
@@ -2427,7 +2430,7 @@
         <v>45</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N28" s="1" t="s">
         <v>39</v>
@@ -2438,22 +2441,22 @@
         <v>10025</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E29" s="11">
         <v>10008</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G29" s="12" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J29" s="1" t="s">
         <v>44</v>
@@ -2462,7 +2465,7 @@
         <v>45</v>
       </c>
       <c r="M29" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N29" s="1" t="s">
         <v>39</v>
@@ -2473,31 +2476,31 @@
         <v>10026</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E30" s="11">
         <v>10009</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G30" s="12" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="J30" s="1" t="s">
         <v>44</v>
       </c>
       <c r="L30" s="12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M30" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N30" s="1" t="s">
         <v>39</v>
@@ -2508,22 +2511,22 @@
         <v>10027</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E31" s="11">
         <v>10010</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G31" s="12" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="J31" s="1" t="s">
         <v>44</v>
@@ -2532,7 +2535,7 @@
         <v>45</v>
       </c>
       <c r="M31" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N31" s="1" t="s">
         <v>39</v>
@@ -2543,28 +2546,28 @@
         <v>10028</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D32" s="12" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E32" s="12">
         <v>10011</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G32" s="12" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="J32" s="1" t="s">
         <v>44</v>
       </c>
       <c r="L32" s="12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M32" s="1" t="s">
         <v>47</v>

--- a/ExcelTool/LubanTools/DataTables/Datas/NpcData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/NpcData.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="142">
   <si>
     <t>##var</t>
   </si>
@@ -158,18 +158,18 @@
     <t>Machi</t>
   </si>
   <si>
+    <t>10000+10100</t>
+  </si>
+  <si>
+    <t>全部</t>
+  </si>
+  <si>
+    <t>半夜</t>
+  </si>
+  <si>
     <t>对话|好感|送礼</t>
   </si>
   <si>
-    <t>10000+10100</t>
-  </si>
-  <si>
-    <t>全部</t>
-  </si>
-  <si>
-    <t>半夜</t>
-  </si>
-  <si>
     <t>中午</t>
   </si>
   <si>
@@ -338,7 +338,10 @@
     <t>桃（赌场）</t>
   </si>
   <si>
-    <t>对话|好感|送礼|游戏币商店|激情一下|娃娃机|爆点游戏|女巫毒药</t>
+    <t>对话|好感|送礼|游戏币商店|激情一下</t>
+  </si>
+  <si>
+    <t>3.5,-2.0</t>
   </si>
   <si>
     <t>千织（工厂）</t>
@@ -414,6 +417,42 @@
   </si>
   <si>
     <t>对话|好感|送礼|鱼饵店|钓鱼</t>
+  </si>
+  <si>
+    <t>赌场(娃娃机)</t>
+  </si>
+  <si>
+    <t>CharacterNames+Character_NPC_13</t>
+  </si>
+  <si>
+    <t>娃娃机</t>
+  </si>
+  <si>
+    <t>0.25,-2.0</t>
+  </si>
+  <si>
+    <t>赌场(毒药)</t>
+  </si>
+  <si>
+    <t>CharacterNames+Character_NPC_14</t>
+  </si>
+  <si>
+    <t>爆点游戏</t>
+  </si>
+  <si>
+    <t>-2.75,-2.0</t>
+  </si>
+  <si>
+    <t>赌场(爆点)</t>
+  </si>
+  <si>
+    <t>CharacterNames+Character_NPC_15</t>
+  </si>
+  <si>
+    <t>女巫毒药</t>
+  </si>
+  <si>
+    <t>-6.5,-2.0</t>
   </si>
 </sst>
 </file>
@@ -426,7 +465,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -437,6 +476,11 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -597,7 +641,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -607,6 +651,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.15"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -942,55 +992,52 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1005,97 +1052,106 @@
     <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1104,11 +1160,26 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1429,820 +1500,818 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N32"/>
+  <dimension ref="A1:N35"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="2" width="8.66666666666667" style="2"/>
-    <col min="3" max="3" width="25.8333333333333" style="2" customWidth="1"/>
-    <col min="4" max="6" width="35.5833333333333" style="2" customWidth="1"/>
-    <col min="7" max="7" width="23" style="3" customWidth="1"/>
-    <col min="8" max="8" width="33.5833333333333" style="2" customWidth="1"/>
-    <col min="9" max="9" width="23.25" style="2" customWidth="1"/>
-    <col min="10" max="10" width="21.4166666666667" style="2" customWidth="1"/>
-    <col min="11" max="11" width="16.5833333333333" style="2" customWidth="1"/>
-    <col min="12" max="12" width="28" style="3" customWidth="1"/>
-    <col min="13" max="13" width="17.75" style="2" customWidth="1"/>
-    <col min="14" max="14" width="17.3333333333333" style="2" customWidth="1"/>
-    <col min="15" max="16384" width="9" style="2"/>
+    <col min="1" max="2" width="8.66666666666667" style="3"/>
+    <col min="3" max="3" width="25.8333333333333" style="3" customWidth="1"/>
+    <col min="4" max="6" width="35.5833333333333" style="3" customWidth="1"/>
+    <col min="7" max="7" width="23" style="4" customWidth="1"/>
+    <col min="8" max="8" width="33.5833333333333" style="3" customWidth="1"/>
+    <col min="9" max="9" width="23.25" style="3" customWidth="1"/>
+    <col min="10" max="10" width="21.4166666666667" style="3" customWidth="1"/>
+    <col min="11" max="11" width="16.5833333333333" style="3" customWidth="1"/>
+    <col min="12" max="12" width="28" style="4" customWidth="1"/>
+    <col min="13" max="13" width="17.75" style="3" customWidth="1"/>
+    <col min="14" max="14" width="17.3333333333333" style="5" customWidth="1"/>
+    <col min="15" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="J1" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="K1" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="7" t="s">
+      <c r="M1" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="7" t="s">
+      <c r="N1" s="10" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:14">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="H2" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="I2" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="J2" s="6" t="s">
+      <c r="J2" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="K2" s="6" t="s">
+      <c r="K2" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="L2" s="9" t="s">
+      <c r="L2" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="M2" s="10" t="s">
+      <c r="M2" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="N2" s="5" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:14">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="G3" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="J3" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="K3" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="L3" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="M3" s="2" t="s">
+      <c r="M3" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="N3" s="5" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" spans="1:14">
-      <c r="B4" s="11">
+      <c r="B4" s="14">
         <v>10000</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="E4" s="11">
+      <c r="E4" s="14">
         <v>10000</v>
       </c>
-      <c r="G4" s="12"/>
-      <c r="N4" s="1" t="s">
+      <c r="G4" s="15"/>
+      <c r="N4" s="16" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" spans="1:14">
-      <c r="B5" s="11">
+      <c r="B5" s="14">
         <v>10001</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="E5" s="11">
+      <c r="E5" s="14">
         <v>10001</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G5" s="12" t="s">
+      <c r="G5" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="H5" s="1" t="s">
-        <v>43</v>
-      </c>
+      <c r="H5" s="1"/>
       <c r="J5" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="L5" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="L5" s="12" t="s">
+      <c r="M5" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="M5" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="N5" s="1" t="s">
+      <c r="N5" s="16" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" spans="1:14">
-      <c r="B6" s="11">
+      <c r="B6" s="14">
         <v>10002</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="E6" s="11">
+      <c r="E6" s="14">
         <v>10001</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G6" s="12" t="s">
+      <c r="G6" s="15" t="s">
         <v>42</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="J6" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="L6" s="15" t="s">
         <v>44</v>
-      </c>
-      <c r="L6" s="12" t="s">
-        <v>45</v>
       </c>
       <c r="M6" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="N6" s="1" t="s">
+      <c r="N6" s="16" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" spans="1:14">
-      <c r="B7" s="11">
+      <c r="B7" s="14">
         <v>10003</v>
       </c>
-      <c r="C7" s="12" t="s">
+      <c r="C7" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="D7" s="12" t="s">
+      <c r="D7" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="E7" s="11">
+      <c r="E7" s="14">
         <v>10001</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G7" s="12" t="s">
+      <c r="G7" s="15" t="s">
         <v>42</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>49</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="L7" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="L7" s="15" t="s">
         <v>50</v>
       </c>
       <c r="M7" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="N7" s="1" t="s">
+      <c r="N7" s="16" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" spans="1:14">
-      <c r="B8" s="11">
+      <c r="B8" s="14">
         <v>10004</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="C8" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="D8" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="E8" s="11">
+      <c r="E8" s="14">
         <v>10001</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G8" s="12" t="s">
+      <c r="G8" s="15" t="s">
         <v>42</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="L8" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="L8" s="15" t="s">
         <v>53</v>
       </c>
       <c r="M8" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="N8" s="1" t="s">
+      <c r="N8" s="16" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" spans="1:14">
-      <c r="B9" s="11">
+      <c r="B9" s="14">
         <v>10005</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="C9" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="D9" s="12" t="s">
+      <c r="D9" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="E9" s="11">
+      <c r="E9" s="14">
         <v>10001</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G9" s="12" t="s">
+      <c r="G9" s="15" t="s">
         <v>42</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>55</v>
       </c>
       <c r="J9" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="L9" s="15" t="s">
         <v>44</v>
-      </c>
-      <c r="L9" s="12" t="s">
-        <v>45</v>
       </c>
       <c r="M9" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="N9" s="1" t="s">
+      <c r="N9" s="16" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" spans="1:14">
-      <c r="B10" s="11">
+      <c r="B10" s="14">
         <v>10006</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="C10" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="D10" s="12" t="s">
+      <c r="D10" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="E10" s="11">
+      <c r="E10" s="14">
         <v>10002</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="G10" s="12" t="s">
+      <c r="G10" s="15" t="s">
         <v>60</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="L10" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="L10" s="15" t="s">
         <v>61</v>
       </c>
       <c r="M10" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="N10" s="1" t="s">
+      <c r="N10" s="16" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" spans="1:14">
-      <c r="B11" s="11">
+      <c r="B11" s="14">
         <v>10007</v>
       </c>
-      <c r="C11" s="12" t="s">
+      <c r="C11" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="D11" s="12" t="s">
+      <c r="D11" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="E11" s="11">
+      <c r="E11" s="14">
         <v>10002</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="G11" s="12" t="s">
+      <c r="G11" s="15" t="s">
         <v>60</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="J11" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="L11" s="15" t="s">
         <v>44</v>
-      </c>
-      <c r="L11" s="12" t="s">
-        <v>45</v>
       </c>
       <c r="M11" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="N11" s="1" t="s">
+      <c r="N11" s="16" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" spans="1:14">
-      <c r="B12" s="11">
+      <c r="B12" s="14">
         <v>10008</v>
       </c>
-      <c r="C12" s="12" t="s">
+      <c r="C12" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="D12" s="12" t="s">
+      <c r="D12" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="E12" s="11">
+      <c r="E12" s="14">
         <v>10002</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="G12" s="12" t="s">
+      <c r="G12" s="15" t="s">
         <v>60</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="L12" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="L12" s="15" t="s">
         <v>64</v>
       </c>
       <c r="M12" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="N12" s="1" t="s">
+      <c r="N12" s="16" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" spans="1:14">
-      <c r="B13" s="11">
+      <c r="B13" s="14">
         <v>10009</v>
       </c>
-      <c r="C13" s="12" t="s">
+      <c r="C13" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="D13" s="12" t="s">
+      <c r="D13" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="E13" s="11">
+      <c r="E13" s="14">
         <v>10002</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="G13" s="12" t="s">
+      <c r="G13" s="15" t="s">
         <v>60</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>66</v>
       </c>
       <c r="J13" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="L13" s="15" t="s">
         <v>44</v>
-      </c>
-      <c r="L13" s="12" t="s">
-        <v>45</v>
       </c>
       <c r="M13" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="N13" s="1" t="s">
+      <c r="N13" s="16" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" spans="1:14">
-      <c r="B14" s="11">
+      <c r="B14" s="14">
         <v>10010</v>
       </c>
-      <c r="C14" s="12" t="s">
+      <c r="C14" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="D14" s="12" t="s">
+      <c r="D14" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="E14" s="11">
+      <c r="E14" s="14">
         <v>10002</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="G14" s="12" t="s">
+      <c r="G14" s="15" t="s">
         <v>60</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>66</v>
       </c>
       <c r="J14" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="L14" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="L14" s="12" t="s">
+      <c r="M14" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="M14" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="N14" s="1" t="s">
+      <c r="N14" s="16" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" spans="1:14">
-      <c r="B15" s="11">
+      <c r="B15" s="14">
         <v>10011</v>
       </c>
-      <c r="C15" s="12" t="s">
+      <c r="C15" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="D15" s="12" t="s">
+      <c r="D15" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="E15" s="12">
+      <c r="E15" s="15">
         <v>10003</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="G15" s="12" t="s">
+      <c r="G15" s="15" t="s">
         <v>71</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="L15" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="L15" s="15" t="s">
         <v>64</v>
       </c>
       <c r="M15" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="N15" s="1" t="s">
+      <c r="N15" s="16" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" spans="1:14">
-      <c r="B16" s="11">
+      <c r="B16" s="14">
         <v>10012</v>
       </c>
-      <c r="C16" s="12" t="s">
+      <c r="C16" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="D16" s="12" t="s">
+      <c r="D16" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="E16" s="12">
+      <c r="E16" s="15">
         <v>10003</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="G16" s="12" t="s">
+      <c r="G16" s="15" t="s">
         <v>71</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>66</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="L16" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="L16" s="15" t="s">
         <v>50</v>
       </c>
       <c r="M16" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="N16" s="1" t="s">
+      <c r="N16" s="16" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" spans="2:14">
-      <c r="B17" s="11">
+      <c r="B17" s="14">
         <v>10013</v>
       </c>
-      <c r="C17" s="12" t="s">
+      <c r="C17" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="D17" s="12" t="s">
+      <c r="D17" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="E17" s="12">
+      <c r="E17" s="15">
         <v>10003</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="G17" s="12" t="s">
+      <c r="G17" s="15" t="s">
         <v>71</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="L17" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="L17" s="15" t="s">
         <v>61</v>
       </c>
       <c r="M17" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="N17" s="1" t="s">
+      <c r="N17" s="16" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" spans="2:14">
-      <c r="B18" s="11">
+      <c r="B18" s="14">
         <v>10014</v>
       </c>
-      <c r="C18" s="12" t="s">
+      <c r="C18" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="D18" s="12" t="s">
+      <c r="D18" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="E18" s="12">
+      <c r="E18" s="15">
         <v>10003</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="G18" s="12" t="s">
+      <c r="G18" s="15" t="s">
         <v>71</v>
       </c>
       <c r="H18" s="1" t="s">
         <v>66</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="L18" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="L18" s="15" t="s">
         <v>53</v>
       </c>
       <c r="M18" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="N18" s="1" t="s">
+      <c r="N18" s="16" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" spans="2:14">
-      <c r="B19" s="11">
+      <c r="B19" s="14">
         <v>10015</v>
       </c>
-      <c r="C19" s="12" t="s">
+      <c r="C19" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="D19" s="12" t="s">
+      <c r="D19" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="E19" s="11">
+      <c r="E19" s="14">
         <v>10004</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="G19" s="12" t="s">
+      <c r="G19" s="15" t="s">
         <v>78</v>
       </c>
       <c r="H19" s="1" t="s">
         <v>79</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="L19" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="L19" s="15" t="s">
         <v>80</v>
       </c>
       <c r="M19" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="N19" s="1" t="s">
+      <c r="N19" s="16" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" spans="2:14">
-      <c r="B20" s="11">
+      <c r="B20" s="14">
         <v>10016</v>
       </c>
-      <c r="C20" s="12" t="s">
+      <c r="C20" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="D20" s="12" t="s">
+      <c r="D20" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="E20" s="11">
+      <c r="E20" s="14">
         <v>10004</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="G20" s="12" t="s">
+      <c r="G20" s="15" t="s">
         <v>78</v>
       </c>
       <c r="H20" s="1" t="s">
         <v>83</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="L20" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="L20" s="15" t="s">
         <v>80</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="N20" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="N20" s="16" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" spans="2:14">
-      <c r="B21" s="11">
+      <c r="B21" s="14">
         <v>10017</v>
       </c>
-      <c r="C21" s="12" t="s">
+      <c r="C21" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="D21" s="12" t="s">
+      <c r="D21" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="E21" s="11">
+      <c r="E21" s="14">
         <v>10004</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="G21" s="12" t="s">
+      <c r="G21" s="15" t="s">
         <v>78</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="L21" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="L21" s="15" t="s">
         <v>85</v>
       </c>
       <c r="M21" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="N21" s="1" t="s">
+      <c r="N21" s="16" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" spans="2:14">
-      <c r="B22" s="11">
+      <c r="B22" s="14">
         <v>10018</v>
       </c>
-      <c r="C22" s="12" t="s">
+      <c r="C22" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="D22" s="12" t="s">
+      <c r="D22" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="E22" s="11">
+      <c r="E22" s="14">
         <v>10004</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="G22" s="12" t="s">
+      <c r="G22" s="15" t="s">
         <v>78</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="L22" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="L22" s="15" t="s">
         <v>85</v>
       </c>
       <c r="M22" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="N22" s="1" t="s">
+      <c r="N22" s="16" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" spans="2:14">
-      <c r="B23" s="11">
+      <c r="B23" s="14">
         <v>10019</v>
       </c>
-      <c r="C23" s="12" t="s">
+      <c r="C23" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="D23" s="12" t="s">
+      <c r="D23" s="15" t="s">
         <v>89</v>
       </c>
-      <c r="E23" s="11">
+      <c r="E23" s="14">
         <v>10005</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="G23" s="12" t="s">
+      <c r="G23" s="15" t="s">
         <v>90</v>
       </c>
       <c r="H23" s="1" t="s">
@@ -2251,329 +2320,440 @@
       <c r="J23" s="1">
         <v>10100</v>
       </c>
-      <c r="L23" s="12" t="s">
-        <v>45</v>
+      <c r="L23" s="15" t="s">
+        <v>44</v>
       </c>
       <c r="M23" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="N23" s="1" t="s">
+      <c r="N23" s="16" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" spans="2:14">
-      <c r="B24" s="11">
+      <c r="B24" s="14">
         <v>10020</v>
       </c>
-      <c r="C24" s="12" t="s">
+      <c r="C24" s="15" t="s">
         <v>93</v>
       </c>
-      <c r="D24" s="12" t="s">
+      <c r="D24" s="15" t="s">
         <v>89</v>
       </c>
-      <c r="E24" s="11">
+      <c r="E24" s="14">
         <v>10005</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="G24" s="12" t="s">
+      <c r="G24" s="15" t="s">
         <v>90</v>
       </c>
       <c r="H24" s="1" t="s">
         <v>66</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="L24" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="L24" s="15" t="s">
         <v>85</v>
       </c>
       <c r="M24" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="N24" s="1" t="s">
+      <c r="N24" s="16" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" spans="2:14">
-      <c r="B25" s="11">
+      <c r="B25" s="14">
         <v>10021</v>
       </c>
-      <c r="C25" s="12" t="s">
+      <c r="C25" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="D25" s="12" t="s">
+      <c r="D25" s="15" t="s">
         <v>89</v>
       </c>
-      <c r="E25" s="11">
+      <c r="E25" s="14">
         <v>10005</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="G25" s="12" t="s">
+      <c r="G25" s="15" t="s">
         <v>90</v>
       </c>
       <c r="H25" s="1" t="s">
         <v>95</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="L25" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="L25" s="15" t="s">
         <v>85</v>
       </c>
       <c r="M25" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="N25" s="1" t="s">
+      <c r="N25" s="16" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" spans="2:14">
-      <c r="B26" s="11">
+      <c r="B26" s="14">
         <v>10022</v>
       </c>
-      <c r="C26" s="12" t="s">
+      <c r="C26" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="D26" s="12" t="s">
+      <c r="D26" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="E26" s="11">
+      <c r="E26" s="14">
         <v>10006</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="G26" s="12" t="s">
+      <c r="G26" s="15" t="s">
         <v>99</v>
       </c>
       <c r="H26" s="1" t="s">
         <v>100</v>
       </c>
       <c r="J26" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="L26" s="15" t="s">
         <v>44</v>
-      </c>
-      <c r="L26" s="12" t="s">
-        <v>45</v>
       </c>
       <c r="M26" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="N26" s="1" t="s">
+      <c r="N26" s="16" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" spans="2:14">
-      <c r="B27" s="11">
+      <c r="B27" s="14">
         <v>10023</v>
       </c>
-      <c r="C27" s="12" t="s">
+      <c r="C27" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="D27" s="12" t="s">
+      <c r="D27" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="E27" s="11">
+      <c r="E27" s="14">
         <v>10006</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="G27" s="12" t="s">
+      <c r="G27" s="15" t="s">
         <v>99</v>
       </c>
       <c r="H27" s="1" t="s">
         <v>103</v>
       </c>
       <c r="J27" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="L27" s="15" t="s">
         <v>44</v>
-      </c>
-      <c r="L27" s="12" t="s">
-        <v>45</v>
       </c>
       <c r="M27" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="N27" s="1" t="s">
-        <v>39</v>
+      <c r="N27" s="16" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" spans="2:14">
-      <c r="B28" s="11">
+      <c r="B28" s="14">
         <v>10024</v>
       </c>
-      <c r="C28" s="12" t="s">
-        <v>104</v>
-      </c>
-      <c r="D28" s="12" t="s">
+      <c r="C28" s="15" t="s">
         <v>105</v>
       </c>
-      <c r="E28" s="12">
+      <c r="D28" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="E28" s="15">
         <v>10007</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="G28" s="12" t="s">
         <v>107</v>
       </c>
+      <c r="G28" s="15" t="s">
+        <v>108</v>
+      </c>
       <c r="H28" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J28" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="L28" s="15" t="s">
         <v>44</v>
-      </c>
-      <c r="L28" s="12" t="s">
-        <v>45</v>
       </c>
       <c r="M28" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="N28" s="1" t="s">
+      <c r="N28" s="16" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" spans="2:14">
-      <c r="B29" s="11">
+      <c r="B29" s="14">
         <v>10025</v>
       </c>
-      <c r="C29" s="12" t="s">
-        <v>109</v>
-      </c>
-      <c r="D29" s="12" t="s">
+      <c r="C29" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="E29" s="11">
+      <c r="D29" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="E29" s="14">
         <v>10008</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="G29" s="12" t="s">
         <v>112</v>
       </c>
+      <c r="G29" s="15" t="s">
+        <v>113</v>
+      </c>
       <c r="H29" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="J29" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="L29" s="15" t="s">
         <v>44</v>
-      </c>
-      <c r="L29" s="12" t="s">
-        <v>45</v>
       </c>
       <c r="M29" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="N29" s="1" t="s">
+      <c r="N29" s="16" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" spans="2:14">
-      <c r="B30" s="11">
+      <c r="B30" s="14">
         <v>10026</v>
       </c>
-      <c r="C30" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="D30" s="12" t="s">
+      <c r="C30" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="E30" s="11">
+      <c r="D30" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="E30" s="14">
         <v>10009</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="G30" s="12" t="s">
         <v>117</v>
       </c>
+      <c r="G30" s="15" t="s">
+        <v>118</v>
+      </c>
       <c r="H30" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="L30" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="L30" s="15" t="s">
         <v>80</v>
       </c>
       <c r="M30" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="N30" s="1" t="s">
+      <c r="N30" s="16" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" spans="2:14">
-      <c r="B31" s="11">
+      <c r="B31" s="14">
         <v>10027</v>
       </c>
-      <c r="C31" s="12" t="s">
-        <v>119</v>
-      </c>
-      <c r="D31" s="12" t="s">
+      <c r="C31" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="E31" s="11">
+      <c r="D31" s="15" t="s">
+        <v>121</v>
+      </c>
+      <c r="E31" s="14">
         <v>10010</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="G31" s="12" t="s">
         <v>122</v>
       </c>
+      <c r="G31" s="15" t="s">
+        <v>123</v>
+      </c>
       <c r="H31" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="J31" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="L31" s="15" t="s">
         <v>44</v>
-      </c>
-      <c r="L31" s="12" t="s">
-        <v>45</v>
       </c>
       <c r="M31" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="N31" s="1" t="s">
+      <c r="N31" s="16" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" spans="2:14">
-      <c r="B32" s="11">
+      <c r="B32" s="14">
         <v>10028</v>
       </c>
-      <c r="C32" s="12" t="s">
-        <v>124</v>
-      </c>
-      <c r="D32" s="12" t="s">
+      <c r="C32" s="15" t="s">
         <v>125</v>
       </c>
-      <c r="E32" s="12">
+      <c r="D32" s="15" t="s">
+        <v>126</v>
+      </c>
+      <c r="E32" s="15">
         <v>10011</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="G32" s="12" t="s">
         <v>127</v>
       </c>
+      <c r="G32" s="15" t="s">
+        <v>128</v>
+      </c>
       <c r="H32" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="L32" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="L32" s="15" t="s">
         <v>80</v>
       </c>
       <c r="M32" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="N32" s="1" t="s">
+      <c r="N32" s="16" t="s">
         <v>39</v>
+      </c>
+    </row>
+    <row r="33" s="2" customFormat="1" spans="2:14">
+      <c r="B33" s="17">
+        <v>10029</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D33" s="18" t="s">
+        <v>131</v>
+      </c>
+      <c r="E33" s="18">
+        <v>10012</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="G33" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="I33" s="2"/>
+      <c r="J33" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K33" s="2"/>
+      <c r="L33" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="M33" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="N33" s="16" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="34" s="2" customFormat="1" spans="2:14">
+      <c r="B34" s="17">
+        <v>10030</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="D34" s="18" t="s">
+        <v>135</v>
+      </c>
+      <c r="E34" s="18">
+        <v>10013</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="G34" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="I34" s="2"/>
+      <c r="J34" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K34" s="2"/>
+      <c r="L34" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="M34" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="N34" s="19" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="35" s="2" customFormat="1" spans="2:14">
+      <c r="B35" s="17">
+        <v>10031</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D35" s="18" t="s">
+        <v>139</v>
+      </c>
+      <c r="E35" s="18">
+        <v>10014</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="G35" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="I35" s="2"/>
+      <c r="J35" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K35" s="2"/>
+      <c r="L35" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="M35" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="N35" s="19" t="s">
+        <v>141</v>
       </c>
     </row>
   </sheetData>

--- a/ExcelTool/LubanTools/DataTables/Datas/NpcData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/NpcData.xlsx
@@ -302,7 +302,7 @@
     <t>ShangDianXiaoMei</t>
   </si>
   <si>
-    <t>对话|好感|送礼|超市|激情一下</t>
+    <t>对话|好感|送礼|超市|商店帮忙|激情一下</t>
   </si>
   <si>
     <t>早上|中午|傍晚</t>

--- a/ExcelTool/LubanTools/DataTables/Datas/NpcData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/NpcData.xlsx
@@ -1,33 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4506"/>
+  <fileSharing readOnlyRecommended="0" userName="Lumino Game 03"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView activeTab="0" xWindow="240" yWindow="60" windowWidth="0" windowHeight="17680" tabRatio="500"/>
   </bookViews>
   <sheets>
-    <sheet name="角色表" sheetId="1" r:id="rId1"/>
+    <sheet name="角色表" sheetId="1" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
+    <ext uri="smNativeData">
+      <pm:revision xmlns:pm="smNativeData" day="1784688383" val="1234" rev="124" revOS="4" revMin="124" revMax="0"/>
+      <pm:docPrefs xmlns:pm="smNativeData" id="1784688383" fixedDigits="0" showNotice="1" showFrameBounds="1" autoChart="1" recalcOnPrint="1" recalcOnCopy="1" finalRounding="1" compatTextArt="1" tab="567" useDefinedPrintRange="1" printArea="currentSheet"/>
+      <pm:compatibility xmlns:pm="smNativeData" id="1784688383" overlapCells="1"/>
+      <pm:defCurrency xmlns:pm="smNativeData" id="1784688383"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="141">
   <si>
     <t>##var</t>
   </si>
@@ -410,10 +406,7 @@
     <t>CharacterNames+Character_NPC_12</t>
   </si>
   <si>
-    <t>单人_渔夫@2x</t>
-  </si>
-  <si>
-    <t>钓鱼老人@2x</t>
+    <t>OldFisherman</t>
   </si>
   <si>
     <t>对话|好感|送礼|鱼饵店|钓鱼</t>
@@ -458,408 +451,1573 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="14">
+    <numFmt numFmtId="5" formatCode="#,##0\ &quot;¥&quot;;\-#,##0\ &quot;¥&quot;"/>
+    <numFmt numFmtId="6" formatCode="#,##0\ &quot;¥&quot;;[Red]\-#,##0\ &quot;¥&quot;"/>
+    <numFmt numFmtId="7" formatCode="#,##0.00\ &quot;¥&quot;;\-#,##0.00\ &quot;¥&quot;"/>
+    <numFmt numFmtId="8" formatCode="#,##0.00\ &quot;¥&quot;;[Red]\-#,##0.00\ &quot;¥&quot;"/>
+    <numFmt numFmtId="42" formatCode="_-* #,##0\ &quot;¥&quot;_-;\-* #,##0\ &quot;¥&quot;_-;_-* &quot;-&quot;\ &quot;¥&quot;_-;_-@_-"/>
+    <numFmt numFmtId="41" formatCode="_-* #,##0\ _¥_-;\-* #,##0\ _¥_-;_-* &quot;-&quot;\ _¥_-;_-@_-"/>
+    <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;¥&quot;_-;\-* #,##0.00\ &quot;¥&quot;_-;_-* &quot;-&quot;??\ &quot;¥&quot;_-;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00\ _¥_-;\-* #,##0.00\ _¥_-;_-* &quot;-&quot;??\ _¥_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="165" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="166" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="167" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="9" formatCode="0%"/>
+    <numFmt numFmtId="49" formatCode="@"/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="22">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
-      <scheme val="minor"/>
+      <color rgb="FF000000"/>
+      <sz val="11"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1784688383" ulstyle="none" kern="1">
+            <pm:latin face="等线" sz="220" lang="default"/>
+            <pm:cs face="Times New Roman" sz="220" lang="default"/>
+            <pm:ea face="SimSun" sz="220" lang="default"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1784688383" ulstyle="none" kern="1">
+            <pm:latin face="Arial" sz="200" lang="default"/>
+            <pm:cs face="Times New Roman" sz="200" lang="default"/>
+            <pm:ea face="SimSun" sz="200" lang="default"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
+    </font>
+    <font>
       <name val="微软雅黑"/>
       <charset val="134"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+      <sz val="11"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1784688383" ulstyle="none" kern="1">
+            <pm:latin face="微软雅黑" sz="220" lang="default"/>
+            <pm:cs face="Times New Roman" sz="220" lang="default"/>
+            <pm:ea face="SimSun" sz="220" lang="default"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
     <font>
-      <sz val="11"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
+      <family val="2"/>
+      <color rgb="FF1F2329"/>
+      <sz val="11"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1784688383" fgClr="1F2329" ulstyle="none" kern="1">
+            <pm:latin face="微软雅黑" sz="220" lang="default"/>
+            <pm:cs face="Times New Roman" sz="220" lang="default"/>
+            <pm:ea face="SimSun" sz="220" lang="default"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
     <font>
+      <name val="等线"/>
+      <charset val="134"/>
+      <color rgb="FF0000FF"/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
+      <u val="single"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1784688383" fgClr="0000FF" ulstyle="single" kern="1">
+            <pm:latin face="等线" sz="220" lang="default"/>
+            <pm:cs face="Times New Roman" sz="220" lang="default"/>
+            <pm:ea face="SimSun" sz="220" lang="default"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
     <font>
+      <name val="等线"/>
+      <charset val="134"/>
+      <color rgb="FF800080"/>
       <sz val="11"/>
-      <color rgb="FF1F2329"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
+      <u val="single"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1784688383" fgClr="800080" ulstyle="single" kern="1">
+            <pm:latin face="等线" sz="220" lang="default"/>
+            <pm:cs face="Times New Roman" sz="220" lang="default"/>
+            <pm:ea face="SimSun" sz="220" lang="default"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
     <font>
-      <u/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <color rgb="FFFF0000"/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1784688383" fgClr="FF0000" ulstyle="none" kern="1">
+            <pm:latin face="等线" sz="220" lang="default"/>
+            <pm:cs face="Times New Roman" sz="220" lang="default"/>
+            <pm:ea face="SimSun" sz="220" lang="default"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
       <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
+      <b/>
+      <color rgb="FF44546A"/>
+      <sz val="18"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1784688383" fgClr="44546A" ulstyle="none" kern="1">
+            <pm:latin face="等线" sz="360" lang="default" weight="bold"/>
+            <pm:cs face="Times New Roman" sz="360" lang="default" weight="bold"/>
+            <pm:ea face="SimSun" sz="360" lang="default" weight="bold"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
     <font>
+      <name val="等线"/>
+      <charset val="134"/>
+      <i/>
+      <color rgb="FF7F7F7F"/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1784688383" fgClr="7F7F7F" ulstyle="none" kern="1">
+            <pm:latin face="等线" sz="220" lang="default" i="1"/>
+            <pm:cs face="Times New Roman" sz="220" lang="default" i="1"/>
+            <pm:ea face="SimSun" sz="220" lang="default" i="1"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
       <name val="等线"/>
       <charset val="134"/>
-      <scheme val="minor"/>
+      <b/>
+      <color rgb="FF44546A"/>
+      <sz val="15"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1784688383" fgClr="44546A" ulstyle="none" kern="1">
+            <pm:latin face="等线" sz="300" lang="default" weight="bold"/>
+            <pm:cs face="Times New Roman" sz="300" lang="default" weight="bold"/>
+            <pm:ea face="SimSun" sz="300" lang="default" weight="bold"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
       <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
+      <b/>
+      <color rgb="FF44546A"/>
+      <sz val="13"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1784688383" fgClr="44546A" ulstyle="none" kern="1">
+            <pm:latin face="等线" sz="260" lang="default" weight="bold"/>
+            <pm:cs face="Times New Roman" sz="260" lang="default" weight="bold"/>
+            <pm:ea face="SimSun" sz="260" lang="default" weight="bold"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
       <name val="等线"/>
       <charset val="134"/>
-      <scheme val="minor"/>
+      <b/>
+      <color rgb="FF44546A"/>
+      <sz val="11"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1784688383" fgClr="44546A" ulstyle="none" kern="1">
+            <pm:latin face="等线" sz="220" lang="default" weight="bold"/>
+            <pm:cs face="Times New Roman" sz="220" lang="default" weight="bold"/>
+            <pm:ea face="SimSun" sz="220" lang="default" weight="bold"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
       <name val="等线"/>
       <charset val="134"/>
-      <scheme val="minor"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1784688383" fgClr="3F3F76" ulstyle="none" kern="1">
+            <pm:latin face="等线" sz="220" lang="default"/>
+            <pm:cs face="Times New Roman" sz="220" lang="default"/>
+            <pm:ea face="SimSun" sz="220" lang="default"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
       <name val="等线"/>
       <charset val="134"/>
-      <scheme val="minor"/>
+      <b/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1784688383" fgClr="3F3F3F" ulstyle="none" kern="1">
+            <pm:latin face="等线" sz="220" lang="default" weight="bold"/>
+            <pm:cs face="Times New Roman" sz="220" lang="default" weight="bold"/>
+            <pm:ea face="SimSun" sz="220" lang="default" weight="bold"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
     <font>
+      <name val="等线"/>
+      <charset val="134"/>
+      <b/>
+      <color rgb="FFFA7D00"/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1784688383" fgClr="FA7D00" ulstyle="none" kern="1">
+            <pm:latin face="等线" sz="220" lang="default" weight="bold"/>
+            <pm:cs face="Times New Roman" sz="220" lang="default" weight="bold"/>
+            <pm:ea face="SimSun" sz="220" lang="default" weight="bold"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
     <font>
+      <name val="等线"/>
+      <charset val="134"/>
       <b/>
+      <color rgb="FFFFFFFF"/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1784688383" fgClr="FFFFFF" ulstyle="none" kern="1">
+            <pm:latin face="等线" sz="220" lang="default" weight="bold"/>
+            <pm:cs face="Times New Roman" sz="220" lang="default" weight="bold"/>
+            <pm:ea face="SimSun" sz="220" lang="default" weight="bold"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
     <font>
-      <b/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <color rgb="FFFA7D00"/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1784688383" fgClr="FA7D00" ulstyle="none" kern="1">
+            <pm:latin face="等线" sz="220" lang="default"/>
+            <pm:cs face="Times New Roman" sz="220" lang="default"/>
+            <pm:ea face="SimSun" sz="220" lang="default"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
     <font>
+      <name val="等线"/>
+      <charset val="134"/>
       <b/>
+      <color rgb="FF000000"/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1784688383" ulstyle="none" kern="1">
+            <pm:latin face="等线" sz="220" lang="default" weight="bold"/>
+            <pm:cs face="Times New Roman" sz="220" lang="default" weight="bold"/>
+            <pm:ea face="SimSun" sz="220" lang="default" weight="bold"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
     <font>
+      <name val="等线"/>
+      <charset val="134"/>
+      <color rgb="FF006100"/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1784688383" fgClr="006100" ulstyle="none" kern="1">
+            <pm:latin face="等线" sz="220" lang="default"/>
+            <pm:cs face="Times New Roman" sz="220" lang="default"/>
+            <pm:ea face="SimSun" sz="220" lang="default"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
     <font>
-      <b/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <color rgb="FF9C0006"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1784688383" fgClr="9C0006" ulstyle="none" kern="1">
+            <pm:latin face="等线" sz="220" lang="default"/>
+            <pm:cs face="Times New Roman" sz="220" lang="default"/>
+            <pm:ea face="SimSun" sz="220" lang="default"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
     <font>
+      <name val="等线"/>
+      <charset val="134"/>
+      <color rgb="FF9C6500"/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1784688383" fgClr="9C6500" ulstyle="none" kern="1">
+            <pm:latin face="等线" sz="220" lang="default"/>
+            <pm:cs face="Times New Roman" sz="220" lang="default"/>
+            <pm:ea face="SimSun" sz="220" lang="default"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
     <font>
+      <name val="等线"/>
+      <charset val="134"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1784688383" fgClr="FFFFFF" ulstyle="none" kern="1">
+            <pm:latin face="等线" sz="220" lang="default"/>
+            <pm:cs face="Times New Roman" sz="220" lang="default"/>
+            <pm:ea face="SimSun" sz="220" lang="default"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="44">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.15"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399914548173467"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784688383" type="1" fgLvl="100" fgClr="00FFFFCC" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
       </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784688383" type="1" fgLvl="100" fgClr="00FFCC99" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784688383" type="1" fgLvl="100" fgClr="00F2F2F2" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784688383" type="1" fgLvl="100" fgClr="00F2F2F2" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784688383" type="1" fgLvl="100" fgClr="00A5A5A5" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
       </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784688383" type="1" fgLvl="100" fgClr="00C6EFCE" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784688383" type="1" fgLvl="100" fgClr="00FFC7CE" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784688383" type="1" fgLvl="100" fgClr="00FFEB9C" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FF5B9BD5"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784688383" type="1" fgLvl="100" fgClr="005B9BD5" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FFDDEBF7"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784688383" type="1" fgLvl="100" fgClr="00DDEBF7" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FFBDD7EE"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784688383" type="1" fgLvl="100" fgClr="00BDD7EE" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FF9BC2E6"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784688383" type="1" fgLvl="100" fgClr="009BC2E6" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FFED7D31"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784688383" type="1" fgLvl="100" fgClr="00ED7D31" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FFFBE3D5"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784688383" type="1" fgLvl="100" fgClr="00FBE3D5" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FFF8CAAB"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784688383" type="1" fgLvl="100" fgClr="00F8CAAB" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FFF4AF82"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784688383" type="1" fgLvl="100" fgClr="00F4AF82" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784688383" type="1" fgLvl="100" fgClr="00A5A5A5" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FFEBEBEB"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784688383" type="1" fgLvl="100" fgClr="00EBEBEB" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FFD9D9D9"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784688383" type="1" fgLvl="100" fgClr="00D9D9D9" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FFC7C7C7"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784688383" type="1" fgLvl="100" fgClr="00C7C7C7" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FFFFC000"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784688383" type="1" fgLvl="100" fgClr="00FFC000" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FFFFF2CA"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784688383" type="1" fgLvl="100" fgClr="00FFF2CA" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FFFFE697"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784688383" type="1" fgLvl="100" fgClr="00FFE697" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FFFFD964"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784688383" type="1" fgLvl="100" fgClr="00FFD964" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FF4472C4"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784688383" type="1" fgLvl="100" fgClr="004472C4" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FFD9E1F2"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784688383" type="1" fgLvl="100" fgClr="00D9E1F2" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FFB4C6E7"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784688383" type="1" fgLvl="100" fgClr="00B4C6E7" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FF8EA9DB"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784688383" type="1" fgLvl="100" fgClr="008EA9DB" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FF70AD47"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784688383" type="1" fgLvl="100" fgClr="0070AD47" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FFE1EFD8"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784688383" type="1" fgLvl="100" fgClr="00E1EFD8" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC5DFB3"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784688383" type="1" fgLvl="100" fgClr="00C5DFB3" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA8D08C"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784688383" type="1" fgLvl="100" fgClr="00A8D08C" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE7E6E6"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784688383" type="1" fgLvl="100" fgClr="00E7E6E6" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD8D8D8"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784688383" type="1" fgLvl="100" fgClr="00D8D8D8" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE7E6E6"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784688383" type="1" fgLvl="100" fgClr="00E7E6E6" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD8D8D8"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784688383" type="1" fgLvl="100" fgClr="00D8D8D8" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784688383" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="100" bgClr="00000000"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="10">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
+  <borders count="43">
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784688383"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784688383">
+            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="B2B2B2"/>
+            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="B2B2B2"/>
+            <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="B2B2B2"/>
+            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="B2B2B2"/>
+          </pm:border>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF5B9BD5"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784688383">
+            <pm:line position="bottom" type="1" style="0" width="30" dist="20" width2="20" rgb="5B9BD5"/>
+          </pm:border>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFACCCEA"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784688383">
+            <pm:line position="bottom" type="1" style="0" width="30" dist="20" width2="20" rgb="ACCCEA"/>
+          </pm:border>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784688383">
+            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="7F7F7F"/>
+            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="7F7F7F"/>
+            <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="7F7F7F"/>
+            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="7F7F7F"/>
+          </pm:border>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784688383">
+            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="3F3F3F"/>
+            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="3F3F3F"/>
+            <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="3F3F3F"/>
+            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="3F3F3F"/>
+          </pm:border>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784688383">
+            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="7F7F7F"/>
+            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="7F7F7F"/>
+            <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="7F7F7F"/>
+            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="7F7F7F"/>
+          </pm:border>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784688383">
+            <pm:line position="top" type="2" style="0" width="20" dist="20" width2="20" rgb="3F3F3F"/>
+            <pm:line position="bottom" type="2" style="0" width="20" dist="20" width2="20" rgb="3F3F3F"/>
+            <pm:line position="left" type="2" style="0" width="20" dist="20" width2="20" rgb="3F3F3F"/>
+            <pm:line position="right" type="2" style="0" width="20" dist="20" width2="20" rgb="3F3F3F"/>
+          </pm:border>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784688383">
+            <pm:line position="bottom" type="2" style="0" width="20" dist="20" width2="20" rgb="FF8001"/>
+          </pm:border>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF5B9BD5"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF5B9BD5"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784688383">
+            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="5B9BD5"/>
+            <pm:line position="bottom" type="2" style="0" width="20" dist="20" width2="20" rgb="5B9BD5"/>
+          </pm:border>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784688383"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784688383"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784688383"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784688383"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784688383"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784688383"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784688383"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784688383"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784688383"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784688383"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784688383"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784688383"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784688383"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784688383"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784688383"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784688383"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784688383"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784688383"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784688383"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784688383"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784688383"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784688383"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784688383"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784688383"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784688383"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784688383"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784688383"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784688383"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784688383"/>
+        </ext>
+      </extLst>
     </border>
     <border>
       <left style="thin">
@@ -874,369 +2032,538 @@
       <bottom style="thin">
         <color rgb="FFDEE0E3"/>
       </bottom>
-      <diagonal/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784688383">
+            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
+            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
+            <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
+            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
+          </pm:border>
+        </ext>
+      </extLst>
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FFDEE0E3"/>
       </left>
       <right style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FFDEE0E3"/>
       </right>
       <top style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FFDEE0E3"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
+        <color rgb="FFDEE0E3"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784688383">
+            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
+            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
+            <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
+            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
+          </pm:border>
+        </ext>
+      </extLst>
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FFDEE0E3"/>
       </left>
       <right style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FFDEE0E3"/>
       </right>
       <top style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FFDEE0E3"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
+        <color rgb="FFDEE0E3"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784688383">
+            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
+            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
+            <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
+            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
+          </pm:border>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784688383"/>
+        </ext>
+      </extLst>
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyFill="1" applyBorder="1" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="3" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="6" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="7" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="8" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="9" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="10" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="11" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="12" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="13" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="14" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="15" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="16" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="17" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="18" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="19" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="20" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="21" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="22" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="24" borderId="23" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="24" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="25" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="26" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="27" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="28" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="29" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="31" borderId="30" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="32" borderId="31" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="32" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="33" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="34" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="35" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="37" borderId="36" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="10">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="11">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="12">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="13">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="14">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="15">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" xfId="16">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" xfId="17">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="6" xfId="18">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="7" xfId="19">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="20">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="21">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="10" xfId="22">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="11" xfId="23">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="12" xfId="24">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="13" xfId="25">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="14" xfId="26">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="15" xfId="27">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="16" xfId="28">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="17" xfId="29">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="18" xfId="30">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="19" xfId="31">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="20" xfId="32">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="21" xfId="33">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="22" xfId="34">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="24" borderId="23" xfId="35">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="24" xfId="36">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="25" xfId="37">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="26" xfId="38">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="27" xfId="39">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="28" xfId="40">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="29" xfId="41">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="31" borderId="30" xfId="42">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="32" borderId="31" xfId="43">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="32" xfId="44">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="33" xfId="45">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="34" xfId="46">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="35" xfId="47">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="37" borderId="36" xfId="48">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="38" borderId="37" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="39" borderId="38" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="36" borderId="35" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="37" borderId="36" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="15" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="41" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="38" borderId="37" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="38" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="42" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="39" borderId="38" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="49" fontId="2" fillId="38" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" customBuiltin="1"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3" customBuiltin="1"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4" customBuiltin="1"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5" customBuiltin="1"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6" customBuiltin="1"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7" customBuiltin="1"/>
+    <cellStyle name="Hyperlink" xfId="6" builtinId="8" customBuiltin="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9" customBuiltin="1"/>
+    <cellStyle name="Note" xfId="8" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11" customBuiltin="1"/>
+    <cellStyle name="Title" xfId="10" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Input" xfId="16" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="Output" xfId="17" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="Total" xfId="21" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="Good" xfId="22" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28" customBuiltin="1"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29" customBuiltin="1"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32" customBuiltin="1"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33" customBuiltin="1"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34" customBuiltin="1"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36" customBuiltin="1"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37" customBuiltin="1"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38" customBuiltin="1"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39" customBuiltin="1"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40" customBuiltin="1"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41" customBuiltin="1"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43" customBuiltin="1"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44" customBuiltin="1"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45" customBuiltin="1"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46" customBuiltin="1"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47" customBuiltin="1"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48" customBuiltin="1"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49" customBuiltin="1"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50" customBuiltin="1"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51" customBuiltin="1"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52" customBuiltin="1"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0"/>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext uri="smNativeData">
+      <pm:charStyles xmlns:pm="smNativeData" id="1784688383" count="1">
+        <pm:charStyle name="普通" fontId="0" Id="1"/>
+      </pm:charStyles>
+      <pm:colors xmlns:pm="smNativeData" id="1784688383" count="46">
+        <pm:color name="颜色 24" rgb="1F2329"/>
+        <pm:color name="颜色 25" rgb="800080"/>
+        <pm:color name="颜色 26" rgb="44546A"/>
+        <pm:color name="颜色 27" rgb="3F3F76"/>
+        <pm:color name="颜色 28" rgb="3F3F3F"/>
+        <pm:color name="颜色 29" rgb="FA7D00"/>
+        <pm:color name="颜色 30" rgb="006100"/>
+        <pm:color name="颜色 31" rgb="9C0006"/>
+        <pm:color name="颜色 32" rgb="9C6500"/>
+        <pm:color name="颜色 33" rgb="E7E6E6"/>
+        <pm:color name="20% 灰色" rgb="000000"/>
+        <pm:color name="颜色 35" rgb="D8D8D8"/>
+        <pm:color name="颜色 36" rgb="C5DFB3"/>
+        <pm:color name="颜色 37" rgb="A8D08C"/>
+        <pm:color name="颜色 38" rgb="BDD7EE"/>
+        <pm:color name="颜色 39" rgb="FFFFCC"/>
+        <pm:color name="颜色 40" rgb="FFCC99"/>
+        <pm:color name="颜色 41" rgb="F2F2F2"/>
+        <pm:color name="颜色 42" rgb="A5A5A5"/>
+        <pm:color name="颜色 43" rgb="C6EFCE"/>
+        <pm:color name="颜色 44" rgb="FFC7CE"/>
+        <pm:color name="颜色 45" rgb="FFEB9C"/>
+        <pm:color name="颜色 46" rgb="5B9BD5"/>
+        <pm:color name="颜色 47" rgb="DDEBF7"/>
+        <pm:color name="颜色 48" rgb="9BC2E6"/>
+        <pm:color name="颜色 49" rgb="ED7D31"/>
+        <pm:color name="颜色 50" rgb="FBE3D5"/>
+        <pm:color name="颜色 51" rgb="F8CAAB"/>
+        <pm:color name="颜色 52" rgb="F4AF82"/>
+        <pm:color name="颜色 53" rgb="EBEBEB"/>
+        <pm:color name="颜色 54" rgb="D9D9D9"/>
+        <pm:color name="颜色 55" rgb="C7C7C7"/>
+        <pm:color name="颜色 56" rgb="FFC000"/>
+        <pm:color name="颜色 57" rgb="FFF2CA"/>
+        <pm:color name="颜色 58" rgb="FFE697"/>
+        <pm:color name="颜色 59" rgb="FFD964"/>
+        <pm:color name="颜色 60" rgb="4472C4"/>
+        <pm:color name="颜色 61" rgb="D9E1F2"/>
+        <pm:color name="颜色 62" rgb="B4C6E7"/>
+        <pm:color name="颜色 63" rgb="8EA9DB"/>
+        <pm:color name="颜色 64" rgb="70AD47"/>
+        <pm:color name="颜色 65" rgb="E1EFD8"/>
+        <pm:color name="颜色 66" rgb="DEE0E3"/>
+        <pm:color name="颜色 67" rgb="B2B2B2"/>
+        <pm:color name="颜色 68" rgb="ACCCEA"/>
+        <pm:color name="颜色 69" rgb="FF8001"/>
+      </pm:colors>
     </ext>
   </extLst>
 </styleSheet>
@@ -1253,106 +2580,46 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="EEECE1"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="1F497D"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="Yu Gothic Light"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="Yu Gothic"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:latin typeface="等线"/>
+        <a:ea typeface="SimSun"/>
+        <a:cs typeface="Times New Roman"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -1364,1400 +2631,1476 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr>
+        <a:prstTxWarp prst="textNoShape">
+          <a:avLst/>
+        </a:prstTxWarp>
+        <a:noAutofit/>
+      </a:bodyPr>
+      <a:lstStyle>
+        <a:defPPr>
+          <a:defRPr/>
+        </a:defPPr>
+      </a:lstStyle>
+      <a:style>
+        <a:lnRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
+  </a:objectDefaults>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <dimension ref="A1:N35"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.55"/>
   <cols>
-    <col min="1" max="2" width="8.66666666666667" style="3"/>
-    <col min="3" max="3" width="25.8333333333333" style="3" customWidth="1"/>
-    <col min="4" max="6" width="35.5833333333333" style="3" customWidth="1"/>
-    <col min="7" max="7" width="23" style="4" customWidth="1"/>
-    <col min="8" max="8" width="33.5833333333333" style="3" customWidth="1"/>
-    <col min="9" max="9" width="23.25" style="3" customWidth="1"/>
-    <col min="10" max="10" width="21.4166666666667" style="3" customWidth="1"/>
-    <col min="11" max="11" width="16.5833333333333" style="3" customWidth="1"/>
-    <col min="12" max="12" width="28" style="4" customWidth="1"/>
-    <col min="13" max="13" width="17.75" style="3" customWidth="1"/>
-    <col min="14" max="14" width="17.3333333333333" style="5" customWidth="1"/>
-    <col min="15" max="16384" width="9" style="3"/>
+    <col min="1" max="2" width="8.663793" customWidth="1" style="51"/>
+    <col min="3" max="3" width="25.836207" customWidth="1" style="51"/>
+    <col min="4" max="6" width="35.586207" customWidth="1" style="51"/>
+    <col min="7" max="7" width="23.000000" customWidth="1" style="52"/>
+    <col min="8" max="8" width="33.586207" customWidth="1" style="51"/>
+    <col min="9" max="9" width="23.250000" customWidth="1" style="51"/>
+    <col min="10" max="10" width="21.413793" customWidth="1" style="51"/>
+    <col min="11" max="11" width="16.586207" customWidth="1" style="51"/>
+    <col min="12" max="12" width="28.000000" customWidth="1" style="52"/>
+    <col min="13" max="13" width="17.750000" customWidth="1" style="51"/>
+    <col min="14" max="14" width="17.336207" customWidth="1" style="53"/>
+    <col min="15" max="16384" width="9.000000" style="51"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="51" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="54" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="55" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="56" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="56" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="54" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="51" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I1" s="54" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="J1" s="54" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="K1" s="54" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="L1" s="52" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="9" t="s">
+      <c r="M1" s="54" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="10" t="s">
+      <c r="N1" s="57" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:14">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="51" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="51" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="51" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="52" t="s">
         <v>17</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="52" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="52" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="51" t="s">
         <v>16</v>
       </c>
-      <c r="H2" s="11" t="s">
+      <c r="H2" s="58" t="s">
         <v>18</v>
       </c>
-      <c r="I2" s="8" t="s">
+      <c r="I2" s="56" t="s">
         <v>19</v>
       </c>
-      <c r="J2" s="8" t="s">
+      <c r="J2" s="56" t="s">
         <v>19</v>
       </c>
-      <c r="K2" s="8" t="s">
+      <c r="K2" s="56" t="s">
         <v>19</v>
       </c>
-      <c r="L2" s="12" t="s">
+      <c r="L2" s="59" t="s">
         <v>20</v>
       </c>
-      <c r="M2" s="13" t="s">
+      <c r="M2" s="60" t="s">
         <v>21</v>
       </c>
-      <c r="N2" s="5" t="s">
+      <c r="N2" s="53" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:14">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="51" t="s">
         <v>23</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="54" t="s">
         <v>24</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="56" t="s">
         <v>25</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="56" t="s">
         <v>26</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="56" t="s">
         <v>27</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="F3" s="56" t="s">
         <v>28</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="G3" s="54" t="s">
         <v>29</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="51" t="s">
         <v>30</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="51" t="s">
         <v>31</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" s="51" t="s">
         <v>32</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="K3" s="51" t="s">
         <v>33</v>
       </c>
-      <c r="L3" s="4" t="s">
+      <c r="L3" s="52" t="s">
         <v>34</v>
       </c>
-      <c r="M3" s="3" t="s">
+      <c r="M3" s="51" t="s">
         <v>35</v>
       </c>
-      <c r="N3" s="5" t="s">
+      <c r="N3" s="53" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" spans="1:14">
-      <c r="B4" s="14">
+    <row r="4" spans="2:14" s="49" customFormat="1">
+      <c r="B4" s="61" t="n">
         <v>10000</v>
       </c>
-      <c r="C4" s="15" t="s">
+      <c r="C4" s="62" t="s">
         <v>37</v>
       </c>
-      <c r="D4" s="15" t="s">
+      <c r="D4" s="62" t="s">
         <v>38</v>
       </c>
-      <c r="E4" s="14">
+      <c r="E4" s="61" t="n">
         <v>10000</v>
       </c>
-      <c r="G4" s="15"/>
-      <c r="N4" s="16" t="s">
+      <c r="G4" s="62"/>
+      <c r="N4" s="63" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" spans="1:14">
-      <c r="B5" s="14">
+    <row r="5" spans="2:14" s="49" customFormat="1">
+      <c r="B5" s="61" t="n">
         <v>10001</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="62" t="s">
         <v>40</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="D5" s="62" t="s">
         <v>41</v>
       </c>
-      <c r="E5" s="14">
+      <c r="E5" s="61" t="n">
         <v>10001</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="F5" s="49" t="s">
         <v>42</v>
       </c>
-      <c r="G5" s="15" t="s">
+      <c r="G5" s="62" t="s">
         <v>42</v>
       </c>
-      <c r="H5" s="1"/>
-      <c r="J5" s="1" t="s">
+      <c r="J5" s="49" t="s">
         <v>43</v>
       </c>
-      <c r="L5" s="15" t="s">
+      <c r="L5" s="62" t="s">
         <v>44</v>
       </c>
-      <c r="M5" s="1" t="s">
+      <c r="M5" s="49" t="s">
         <v>45</v>
       </c>
-      <c r="N5" s="16" t="s">
+      <c r="N5" s="63" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" spans="1:14">
-      <c r="B6" s="14">
+    <row r="6" spans="2:14" s="49" customFormat="1">
+      <c r="B6" s="61" t="n">
         <v>10002</v>
       </c>
-      <c r="C6" s="15" t="s">
+      <c r="C6" s="62" t="s">
         <v>40</v>
       </c>
-      <c r="D6" s="15" t="s">
+      <c r="D6" s="62" t="s">
         <v>41</v>
       </c>
-      <c r="E6" s="14">
+      <c r="E6" s="61" t="n">
         <v>10001</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="F6" s="49" t="s">
         <v>42</v>
       </c>
-      <c r="G6" s="15" t="s">
+      <c r="G6" s="62" t="s">
         <v>42</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="H6" s="49" t="s">
         <v>46</v>
       </c>
-      <c r="J6" s="1" t="s">
+      <c r="J6" s="49" t="s">
         <v>43</v>
       </c>
-      <c r="L6" s="15" t="s">
+      <c r="L6" s="62" t="s">
         <v>44</v>
       </c>
-      <c r="M6" s="1" t="s">
+      <c r="M6" s="49" t="s">
         <v>47</v>
       </c>
-      <c r="N6" s="16" t="s">
+      <c r="N6" s="63" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" spans="1:14">
-      <c r="B7" s="14">
+    <row r="7" spans="2:14" s="49" customFormat="1">
+      <c r="B7" s="61" t="n">
         <v>10003</v>
       </c>
-      <c r="C7" s="15" t="s">
+      <c r="C7" s="62" t="s">
         <v>48</v>
       </c>
-      <c r="D7" s="15" t="s">
+      <c r="D7" s="62" t="s">
         <v>41</v>
       </c>
-      <c r="E7" s="14">
+      <c r="E7" s="61" t="n">
         <v>10001</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="F7" s="49" t="s">
         <v>42</v>
       </c>
-      <c r="G7" s="15" t="s">
+      <c r="G7" s="62" t="s">
         <v>42</v>
       </c>
-      <c r="H7" s="1" t="s">
+      <c r="H7" s="49" t="s">
         <v>49</v>
       </c>
-      <c r="J7" s="1" t="s">
+      <c r="J7" s="49" t="s">
         <v>43</v>
       </c>
-      <c r="L7" s="15" t="s">
+      <c r="L7" s="62" t="s">
         <v>50</v>
       </c>
-      <c r="M7" s="1" t="s">
+      <c r="M7" s="49" t="s">
         <v>51</v>
       </c>
-      <c r="N7" s="16" t="s">
+      <c r="N7" s="63" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" spans="1:14">
-      <c r="B8" s="14">
+    <row r="8" spans="2:14" s="49" customFormat="1">
+      <c r="B8" s="61" t="n">
         <v>10004</v>
       </c>
-      <c r="C8" s="15" t="s">
+      <c r="C8" s="62" t="s">
         <v>52</v>
       </c>
-      <c r="D8" s="15" t="s">
+      <c r="D8" s="62" t="s">
         <v>41</v>
       </c>
-      <c r="E8" s="14">
+      <c r="E8" s="61" t="n">
         <v>10001</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="F8" s="49" t="s">
         <v>42</v>
       </c>
-      <c r="G8" s="15" t="s">
+      <c r="G8" s="62" t="s">
         <v>42</v>
       </c>
-      <c r="H8" s="1" t="s">
+      <c r="H8" s="49" t="s">
         <v>46</v>
       </c>
-      <c r="J8" s="1" t="s">
+      <c r="J8" s="49" t="s">
         <v>43</v>
       </c>
-      <c r="L8" s="15" t="s">
+      <c r="L8" s="62" t="s">
         <v>53</v>
       </c>
-      <c r="M8" s="1" t="s">
+      <c r="M8" s="49" t="s">
         <v>51</v>
       </c>
-      <c r="N8" s="16" t="s">
+      <c r="N8" s="63" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" spans="1:14">
-      <c r="B9" s="14">
+    <row r="9" spans="2:14" s="49" customFormat="1">
+      <c r="B9" s="61" t="n">
         <v>10005</v>
       </c>
-      <c r="C9" s="15" t="s">
+      <c r="C9" s="62" t="s">
         <v>54</v>
       </c>
-      <c r="D9" s="15" t="s">
+      <c r="D9" s="62" t="s">
         <v>41</v>
       </c>
-      <c r="E9" s="14">
+      <c r="E9" s="61" t="n">
         <v>10001</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="F9" s="49" t="s">
         <v>42</v>
       </c>
-      <c r="G9" s="15" t="s">
+      <c r="G9" s="62" t="s">
         <v>42</v>
       </c>
-      <c r="H9" s="1" t="s">
+      <c r="H9" s="49" t="s">
         <v>55</v>
       </c>
-      <c r="J9" s="1" t="s">
+      <c r="J9" s="49" t="s">
         <v>43</v>
       </c>
-      <c r="L9" s="15" t="s">
+      <c r="L9" s="62" t="s">
         <v>44</v>
       </c>
-      <c r="M9" s="1" t="s">
+      <c r="M9" s="49" t="s">
         <v>56</v>
       </c>
-      <c r="N9" s="16" t="s">
+      <c r="N9" s="63" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" spans="1:14">
-      <c r="B10" s="14">
+    <row r="10" spans="2:14" s="49" customFormat="1">
+      <c r="B10" s="61" t="n">
         <v>10006</v>
       </c>
-      <c r="C10" s="15" t="s">
+      <c r="C10" s="62" t="s">
         <v>57</v>
       </c>
-      <c r="D10" s="15" t="s">
+      <c r="D10" s="62" t="s">
         <v>58</v>
       </c>
-      <c r="E10" s="14">
+      <c r="E10" s="61" t="n">
         <v>10002</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="F10" s="49" t="s">
         <v>59</v>
       </c>
-      <c r="G10" s="15" t="s">
+      <c r="G10" s="62" t="s">
         <v>60</v>
       </c>
-      <c r="H10" s="1" t="s">
+      <c r="H10" s="49" t="s">
         <v>46</v>
       </c>
-      <c r="J10" s="1" t="s">
+      <c r="J10" s="49" t="s">
         <v>43</v>
       </c>
-      <c r="L10" s="15" t="s">
+      <c r="L10" s="62" t="s">
         <v>61</v>
       </c>
-      <c r="M10" s="1" t="s">
+      <c r="M10" s="49" t="s">
         <v>56</v>
       </c>
-      <c r="N10" s="16" t="s">
+      <c r="N10" s="63" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="11" s="1" customFormat="1" spans="1:14">
-      <c r="B11" s="14">
+    <row r="11" spans="2:14" s="49" customFormat="1">
+      <c r="B11" s="61" t="n">
         <v>10007</v>
       </c>
-      <c r="C11" s="15" t="s">
+      <c r="C11" s="62" t="s">
         <v>62</v>
       </c>
-      <c r="D11" s="15" t="s">
+      <c r="D11" s="62" t="s">
         <v>58</v>
       </c>
-      <c r="E11" s="14">
+      <c r="E11" s="61" t="n">
         <v>10002</v>
       </c>
-      <c r="F11" s="1" t="s">
+      <c r="F11" s="49" t="s">
         <v>59</v>
       </c>
-      <c r="G11" s="15" t="s">
+      <c r="G11" s="62" t="s">
         <v>60</v>
       </c>
-      <c r="H11" s="1" t="s">
+      <c r="H11" s="49" t="s">
         <v>46</v>
       </c>
-      <c r="J11" s="1" t="s">
+      <c r="J11" s="49" t="s">
         <v>43</v>
       </c>
-      <c r="L11" s="15" t="s">
+      <c r="L11" s="62" t="s">
         <v>44</v>
       </c>
-      <c r="M11" s="1" t="s">
+      <c r="M11" s="49" t="s">
         <v>47</v>
       </c>
-      <c r="N11" s="16" t="s">
+      <c r="N11" s="63" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" spans="1:14">
-      <c r="B12" s="14">
+    <row r="12" spans="2:14" s="49" customFormat="1">
+      <c r="B12" s="61" t="n">
         <v>10008</v>
       </c>
-      <c r="C12" s="15" t="s">
+      <c r="C12" s="62" t="s">
         <v>63</v>
       </c>
-      <c r="D12" s="15" t="s">
+      <c r="D12" s="62" t="s">
         <v>58</v>
       </c>
-      <c r="E12" s="14">
+      <c r="E12" s="61" t="n">
         <v>10002</v>
       </c>
-      <c r="F12" s="1" t="s">
+      <c r="F12" s="49" t="s">
         <v>59</v>
       </c>
-      <c r="G12" s="15" t="s">
+      <c r="G12" s="62" t="s">
         <v>60</v>
       </c>
-      <c r="H12" s="1" t="s">
+      <c r="H12" s="49" t="s">
         <v>46</v>
       </c>
-      <c r="J12" s="1" t="s">
+      <c r="J12" s="49" t="s">
         <v>43</v>
       </c>
-      <c r="L12" s="15" t="s">
+      <c r="L12" s="62" t="s">
         <v>64</v>
       </c>
-      <c r="M12" s="1" t="s">
+      <c r="M12" s="49" t="s">
         <v>56</v>
       </c>
-      <c r="N12" s="16" t="s">
+      <c r="N12" s="63" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" spans="1:14">
-      <c r="B13" s="14">
+    <row r="13" spans="2:14" s="49" customFormat="1">
+      <c r="B13" s="61" t="n">
         <v>10009</v>
       </c>
-      <c r="C13" s="15" t="s">
+      <c r="C13" s="62" t="s">
         <v>65</v>
       </c>
-      <c r="D13" s="15" t="s">
+      <c r="D13" s="62" t="s">
         <v>58</v>
       </c>
-      <c r="E13" s="14">
+      <c r="E13" s="61" t="n">
         <v>10002</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="F13" s="49" t="s">
         <v>59</v>
       </c>
-      <c r="G13" s="15" t="s">
+      <c r="G13" s="62" t="s">
         <v>60</v>
       </c>
-      <c r="H13" s="1" t="s">
+      <c r="H13" s="49" t="s">
         <v>66</v>
       </c>
-      <c r="J13" s="1" t="s">
+      <c r="J13" s="49" t="s">
         <v>43</v>
       </c>
-      <c r="L13" s="15" t="s">
+      <c r="L13" s="62" t="s">
         <v>44</v>
       </c>
-      <c r="M13" s="1" t="s">
+      <c r="M13" s="49" t="s">
         <v>51</v>
       </c>
-      <c r="N13" s="16" t="s">
+      <c r="N13" s="63" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="14" s="1" customFormat="1" spans="1:14">
-      <c r="B14" s="14">
+    <row r="14" spans="2:14" s="49" customFormat="1">
+      <c r="B14" s="61" t="n">
         <v>10010</v>
       </c>
-      <c r="C14" s="15" t="s">
+      <c r="C14" s="62" t="s">
         <v>67</v>
       </c>
-      <c r="D14" s="15" t="s">
+      <c r="D14" s="62" t="s">
         <v>58</v>
       </c>
-      <c r="E14" s="14">
+      <c r="E14" s="61" t="n">
         <v>10002</v>
       </c>
-      <c r="F14" s="1" t="s">
+      <c r="F14" s="49" t="s">
         <v>59</v>
       </c>
-      <c r="G14" s="15" t="s">
+      <c r="G14" s="62" t="s">
         <v>60</v>
       </c>
-      <c r="H14" s="1" t="s">
+      <c r="H14" s="49" t="s">
         <v>66</v>
       </c>
-      <c r="J14" s="1" t="s">
+      <c r="J14" s="49" t="s">
         <v>43</v>
       </c>
-      <c r="L14" s="15" t="s">
+      <c r="L14" s="62" t="s">
         <v>44</v>
       </c>
-      <c r="M14" s="1" t="s">
+      <c r="M14" s="49" t="s">
         <v>45</v>
       </c>
-      <c r="N14" s="16" t="s">
+      <c r="N14" s="63" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="15" s="1" customFormat="1" spans="1:14">
-      <c r="B15" s="14">
+    <row r="15" spans="2:14" s="49" customFormat="1">
+      <c r="B15" s="61" t="n">
         <v>10011</v>
       </c>
-      <c r="C15" s="15" t="s">
+      <c r="C15" s="62" t="s">
         <v>68</v>
       </c>
-      <c r="D15" s="15" t="s">
+      <c r="D15" s="62" t="s">
         <v>69</v>
       </c>
-      <c r="E15" s="15">
+      <c r="E15" s="62" t="n">
         <v>10003</v>
       </c>
-      <c r="F15" s="1" t="s">
+      <c r="F15" s="49" t="s">
         <v>70</v>
       </c>
-      <c r="G15" s="15" t="s">
+      <c r="G15" s="62" t="s">
         <v>71</v>
       </c>
-      <c r="H15" s="1" t="s">
+      <c r="H15" s="49" t="s">
         <v>46</v>
       </c>
-      <c r="J15" s="1" t="s">
+      <c r="J15" s="49" t="s">
         <v>43</v>
       </c>
-      <c r="L15" s="15" t="s">
+      <c r="L15" s="62" t="s">
         <v>64</v>
       </c>
-      <c r="M15" s="1" t="s">
+      <c r="M15" s="49" t="s">
         <v>72</v>
       </c>
-      <c r="N15" s="16" t="s">
+      <c r="N15" s="63" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="16" s="1" customFormat="1" spans="1:14">
-      <c r="B16" s="14">
+    <row r="16" spans="2:14" s="49" customFormat="1">
+      <c r="B16" s="61" t="n">
         <v>10012</v>
       </c>
-      <c r="C16" s="15" t="s">
+      <c r="C16" s="62" t="s">
         <v>68</v>
       </c>
-      <c r="D16" s="15" t="s">
+      <c r="D16" s="62" t="s">
         <v>69</v>
       </c>
-      <c r="E16" s="15">
+      <c r="E16" s="62" t="n">
         <v>10003</v>
       </c>
-      <c r="F16" s="1" t="s">
+      <c r="F16" s="49" t="s">
         <v>70</v>
       </c>
-      <c r="G16" s="15" t="s">
+      <c r="G16" s="62" t="s">
         <v>71</v>
       </c>
-      <c r="H16" s="1" t="s">
+      <c r="H16" s="49" t="s">
         <v>66</v>
       </c>
-      <c r="J16" s="1" t="s">
+      <c r="J16" s="49" t="s">
         <v>43</v>
       </c>
-      <c r="L16" s="15" t="s">
+      <c r="L16" s="62" t="s">
         <v>50</v>
       </c>
-      <c r="M16" s="1" t="s">
+      <c r="M16" s="49" t="s">
         <v>51</v>
       </c>
-      <c r="N16" s="16" t="s">
+      <c r="N16" s="63" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="17" s="1" customFormat="1" spans="2:14">
-      <c r="B17" s="14">
+    <row r="17" spans="2:14" s="49" customFormat="1">
+      <c r="B17" s="61" t="n">
         <v>10013</v>
       </c>
-      <c r="C17" s="15" t="s">
+      <c r="C17" s="62" t="s">
         <v>73</v>
       </c>
-      <c r="D17" s="15" t="s">
+      <c r="D17" s="62" t="s">
         <v>69</v>
       </c>
-      <c r="E17" s="15">
+      <c r="E17" s="62" t="n">
         <v>10003</v>
       </c>
-      <c r="F17" s="1" t="s">
+      <c r="F17" s="49" t="s">
         <v>70</v>
       </c>
-      <c r="G17" s="15" t="s">
+      <c r="G17" s="62" t="s">
         <v>71</v>
       </c>
-      <c r="H17" s="1" t="s">
+      <c r="H17" s="49" t="s">
         <v>46</v>
       </c>
-      <c r="J17" s="1" t="s">
+      <c r="J17" s="49" t="s">
         <v>43</v>
       </c>
-      <c r="L17" s="15" t="s">
+      <c r="L17" s="62" t="s">
         <v>61</v>
       </c>
-      <c r="M17" s="1" t="s">
+      <c r="M17" s="49" t="s">
         <v>56</v>
       </c>
-      <c r="N17" s="16" t="s">
+      <c r="N17" s="63" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="18" s="1" customFormat="1" spans="2:14">
-      <c r="B18" s="14">
+    <row r="18" spans="2:14" s="49" customFormat="1">
+      <c r="B18" s="61" t="n">
         <v>10014</v>
       </c>
-      <c r="C18" s="15" t="s">
+      <c r="C18" s="62" t="s">
         <v>74</v>
       </c>
-      <c r="D18" s="15" t="s">
+      <c r="D18" s="62" t="s">
         <v>69</v>
       </c>
-      <c r="E18" s="15">
+      <c r="E18" s="62" t="n">
         <v>10003</v>
       </c>
-      <c r="F18" s="1" t="s">
+      <c r="F18" s="49" t="s">
         <v>70</v>
       </c>
-      <c r="G18" s="15" t="s">
+      <c r="G18" s="62" t="s">
         <v>71</v>
       </c>
-      <c r="H18" s="1" t="s">
+      <c r="H18" s="49" t="s">
         <v>66</v>
       </c>
-      <c r="J18" s="1" t="s">
+      <c r="J18" s="49" t="s">
         <v>43</v>
       </c>
-      <c r="L18" s="15" t="s">
+      <c r="L18" s="62" t="s">
         <v>53</v>
       </c>
-      <c r="M18" s="1" t="s">
+      <c r="M18" s="49" t="s">
         <v>51</v>
       </c>
-      <c r="N18" s="16" t="s">
+      <c r="N18" s="63" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="19" s="1" customFormat="1" spans="2:14">
-      <c r="B19" s="14">
+    <row r="19" spans="2:14" s="49" customFormat="1">
+      <c r="B19" s="61" t="n">
         <v>10015</v>
       </c>
-      <c r="C19" s="15" t="s">
+      <c r="C19" s="62" t="s">
         <v>75</v>
       </c>
-      <c r="D19" s="15" t="s">
+      <c r="D19" s="62" t="s">
         <v>76</v>
       </c>
-      <c r="E19" s="14">
+      <c r="E19" s="61" t="n">
         <v>10004</v>
       </c>
-      <c r="F19" s="1" t="s">
+      <c r="F19" s="49" t="s">
         <v>77</v>
       </c>
-      <c r="G19" s="15" t="s">
+      <c r="G19" s="62" t="s">
         <v>78</v>
       </c>
-      <c r="H19" s="1" t="s">
+      <c r="H19" s="49" t="s">
         <v>79</v>
       </c>
-      <c r="J19" s="1" t="s">
+      <c r="J19" s="49" t="s">
         <v>43</v>
       </c>
-      <c r="L19" s="15" t="s">
+      <c r="L19" s="62" t="s">
         <v>80</v>
       </c>
-      <c r="M19" s="1" t="s">
+      <c r="M19" s="49" t="s">
         <v>81</v>
       </c>
-      <c r="N19" s="16" t="s">
+      <c r="N19" s="63" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="20" s="1" customFormat="1" spans="2:14">
-      <c r="B20" s="14">
+    <row r="20" spans="2:14" s="49" customFormat="1">
+      <c r="B20" s="61" t="n">
         <v>10016</v>
       </c>
-      <c r="C20" s="15" t="s">
+      <c r="C20" s="62" t="s">
         <v>82</v>
       </c>
-      <c r="D20" s="15" t="s">
+      <c r="D20" s="62" t="s">
         <v>76</v>
       </c>
-      <c r="E20" s="14">
+      <c r="E20" s="61" t="n">
         <v>10004</v>
       </c>
-      <c r="F20" s="1" t="s">
+      <c r="F20" s="49" t="s">
         <v>77</v>
       </c>
-      <c r="G20" s="15" t="s">
+      <c r="G20" s="62" t="s">
         <v>78</v>
       </c>
-      <c r="H20" s="1" t="s">
+      <c r="H20" s="49" t="s">
         <v>83</v>
       </c>
-      <c r="J20" s="1" t="s">
+      <c r="J20" s="49" t="s">
         <v>43</v>
       </c>
-      <c r="L20" s="15" t="s">
+      <c r="L20" s="62" t="s">
         <v>80</v>
       </c>
-      <c r="M20" s="1" t="s">
+      <c r="M20" s="49" t="s">
         <v>45</v>
       </c>
-      <c r="N20" s="16" t="s">
+      <c r="N20" s="63" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="21" s="1" customFormat="1" spans="2:14">
-      <c r="B21" s="14">
+    <row r="21" spans="2:14" s="49" customFormat="1">
+      <c r="B21" s="61" t="n">
         <v>10017</v>
       </c>
-      <c r="C21" s="15" t="s">
+      <c r="C21" s="62" t="s">
         <v>84</v>
       </c>
-      <c r="D21" s="15" t="s">
+      <c r="D21" s="62" t="s">
         <v>76</v>
       </c>
-      <c r="E21" s="14">
+      <c r="E21" s="61" t="n">
         <v>10004</v>
       </c>
-      <c r="F21" s="1" t="s">
+      <c r="F21" s="49" t="s">
         <v>77</v>
       </c>
-      <c r="G21" s="15" t="s">
+      <c r="G21" s="62" t="s">
         <v>78</v>
       </c>
-      <c r="H21" s="1" t="s">
+      <c r="H21" s="49" t="s">
         <v>46</v>
       </c>
-      <c r="J21" s="1" t="s">
+      <c r="J21" s="49" t="s">
         <v>43</v>
       </c>
-      <c r="L21" s="15" t="s">
+      <c r="L21" s="62" t="s">
         <v>85</v>
       </c>
-      <c r="M21" s="1" t="s">
+      <c r="M21" s="49" t="s">
         <v>47</v>
       </c>
-      <c r="N21" s="16" t="s">
+      <c r="N21" s="63" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="22" s="1" customFormat="1" spans="2:14">
-      <c r="B22" s="14">
+    <row r="22" spans="2:14" s="49" customFormat="1">
+      <c r="B22" s="61" t="n">
         <v>10018</v>
       </c>
-      <c r="C22" s="15" t="s">
+      <c r="C22" s="62" t="s">
         <v>86</v>
       </c>
-      <c r="D22" s="15" t="s">
+      <c r="D22" s="62" t="s">
         <v>76</v>
       </c>
-      <c r="E22" s="14">
+      <c r="E22" s="61" t="n">
         <v>10004</v>
       </c>
-      <c r="F22" s="1" t="s">
+      <c r="F22" s="49" t="s">
         <v>77</v>
       </c>
-      <c r="G22" s="15" t="s">
+      <c r="G22" s="62" t="s">
         <v>78</v>
       </c>
-      <c r="H22" s="1" t="s">
+      <c r="H22" s="49" t="s">
         <v>46</v>
       </c>
-      <c r="J22" s="1" t="s">
+      <c r="J22" s="49" t="s">
         <v>43</v>
       </c>
-      <c r="L22" s="15" t="s">
+      <c r="L22" s="62" t="s">
         <v>85</v>
       </c>
-      <c r="M22" s="1" t="s">
+      <c r="M22" s="49" t="s">
         <v>87</v>
       </c>
-      <c r="N22" s="16" t="s">
+      <c r="N22" s="63" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="23" s="1" customFormat="1" spans="2:14">
-      <c r="B23" s="14">
+    <row r="23" spans="2:14" s="49" customFormat="1">
+      <c r="B23" s="61" t="n">
         <v>10019</v>
       </c>
-      <c r="C23" s="15" t="s">
+      <c r="C23" s="62" t="s">
         <v>88</v>
       </c>
-      <c r="D23" s="15" t="s">
+      <c r="D23" s="62" t="s">
         <v>89</v>
       </c>
-      <c r="E23" s="14">
+      <c r="E23" s="61" t="n">
         <v>10005</v>
       </c>
-      <c r="F23" s="1" t="s">
+      <c r="F23" s="49" t="s">
         <v>90</v>
       </c>
-      <c r="G23" s="15" t="s">
+      <c r="G23" s="62" t="s">
         <v>90</v>
       </c>
-      <c r="H23" s="1" t="s">
+      <c r="H23" s="49" t="s">
         <v>91</v>
       </c>
-      <c r="J23" s="1">
+      <c r="J23" s="49" t="n">
         <v>10100</v>
       </c>
-      <c r="L23" s="15" t="s">
+      <c r="L23" s="62" t="s">
         <v>44</v>
       </c>
-      <c r="M23" s="1" t="s">
+      <c r="M23" s="49" t="s">
         <v>92</v>
       </c>
-      <c r="N23" s="16" t="s">
+      <c r="N23" s="63" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="24" s="1" customFormat="1" spans="2:14">
-      <c r="B24" s="14">
+    <row r="24" spans="2:14" s="49" customFormat="1">
+      <c r="B24" s="61" t="n">
         <v>10020</v>
       </c>
-      <c r="C24" s="15" t="s">
+      <c r="C24" s="62" t="s">
         <v>93</v>
       </c>
-      <c r="D24" s="15" t="s">
+      <c r="D24" s="62" t="s">
         <v>89</v>
       </c>
-      <c r="E24" s="14">
+      <c r="E24" s="61" t="n">
         <v>10005</v>
       </c>
-      <c r="F24" s="1" t="s">
+      <c r="F24" s="49" t="s">
         <v>90</v>
       </c>
-      <c r="G24" s="15" t="s">
+      <c r="G24" s="62" t="s">
         <v>90</v>
       </c>
-      <c r="H24" s="1" t="s">
+      <c r="H24" s="49" t="s">
         <v>66</v>
       </c>
-      <c r="J24" s="1" t="s">
+      <c r="J24" s="49" t="s">
         <v>43</v>
       </c>
-      <c r="L24" s="15" t="s">
+      <c r="L24" s="62" t="s">
         <v>85</v>
       </c>
-      <c r="M24" s="1" t="s">
+      <c r="M24" s="49" t="s">
         <v>56</v>
       </c>
-      <c r="N24" s="16" t="s">
+      <c r="N24" s="63" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="25" s="1" customFormat="1" spans="2:14">
-      <c r="B25" s="14">
+    <row r="25" spans="2:14" s="49" customFormat="1">
+      <c r="B25" s="61" t="n">
         <v>10021</v>
       </c>
-      <c r="C25" s="15" t="s">
+      <c r="C25" s="62" t="s">
         <v>94</v>
       </c>
-      <c r="D25" s="15" t="s">
+      <c r="D25" s="62" t="s">
         <v>89</v>
       </c>
-      <c r="E25" s="14">
+      <c r="E25" s="61" t="n">
         <v>10005</v>
       </c>
-      <c r="F25" s="1" t="s">
+      <c r="F25" s="49" t="s">
         <v>90</v>
       </c>
-      <c r="G25" s="15" t="s">
+      <c r="G25" s="62" t="s">
         <v>90</v>
       </c>
-      <c r="H25" s="1" t="s">
+      <c r="H25" s="49" t="s">
         <v>95</v>
       </c>
-      <c r="J25" s="1" t="s">
+      <c r="J25" s="49" t="s">
         <v>43</v>
       </c>
-      <c r="L25" s="15" t="s">
+      <c r="L25" s="62" t="s">
         <v>85</v>
       </c>
-      <c r="M25" s="1" t="s">
+      <c r="M25" s="49" t="s">
         <v>47</v>
       </c>
-      <c r="N25" s="16" t="s">
+      <c r="N25" s="63" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="26" s="1" customFormat="1" spans="2:14">
-      <c r="B26" s="14">
+    <row r="26" spans="2:14" s="49" customFormat="1">
+      <c r="B26" s="61" t="n">
         <v>10022</v>
       </c>
-      <c r="C26" s="15" t="s">
+      <c r="C26" s="62" t="s">
         <v>96</v>
       </c>
-      <c r="D26" s="15" t="s">
+      <c r="D26" s="62" t="s">
         <v>97</v>
       </c>
-      <c r="E26" s="14">
+      <c r="E26" s="61" t="n">
         <v>10006</v>
       </c>
-      <c r="F26" s="1" t="s">
+      <c r="F26" s="49" t="s">
         <v>98</v>
       </c>
-      <c r="G26" s="15" t="s">
+      <c r="G26" s="62" t="s">
         <v>99</v>
       </c>
-      <c r="H26" s="1" t="s">
+      <c r="H26" s="49" t="s">
         <v>100</v>
       </c>
-      <c r="J26" s="1" t="s">
+      <c r="J26" s="49" t="s">
         <v>43</v>
       </c>
-      <c r="L26" s="15" t="s">
+      <c r="L26" s="62" t="s">
         <v>44</v>
       </c>
-      <c r="M26" s="1" t="s">
+      <c r="M26" s="49" t="s">
         <v>101</v>
       </c>
-      <c r="N26" s="16" t="s">
+      <c r="N26" s="63" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="27" s="1" customFormat="1" spans="2:14">
-      <c r="B27" s="14">
+    <row r="27" spans="2:14" s="49" customFormat="1">
+      <c r="B27" s="61" t="n">
         <v>10023</v>
       </c>
-      <c r="C27" s="15" t="s">
+      <c r="C27" s="62" t="s">
         <v>102</v>
       </c>
-      <c r="D27" s="15" t="s">
+      <c r="D27" s="62" t="s">
         <v>97</v>
       </c>
-      <c r="E27" s="14">
+      <c r="E27" s="61" t="n">
         <v>10006</v>
       </c>
-      <c r="F27" s="1" t="s">
+      <c r="F27" s="49" t="s">
         <v>98</v>
       </c>
-      <c r="G27" s="15" t="s">
+      <c r="G27" s="62" t="s">
         <v>99</v>
       </c>
-      <c r="H27" s="1" t="s">
+      <c r="H27" s="49" t="s">
         <v>103</v>
       </c>
-      <c r="J27" s="1" t="s">
+      <c r="J27" s="49" t="s">
         <v>43</v>
       </c>
-      <c r="L27" s="15" t="s">
+      <c r="L27" s="62" t="s">
         <v>44</v>
       </c>
-      <c r="M27" s="1" t="s">
+      <c r="M27" s="49" t="s">
         <v>101</v>
       </c>
-      <c r="N27" s="16" t="s">
+      <c r="N27" s="63" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="28" s="1" customFormat="1" spans="2:14">
-      <c r="B28" s="14">
+    <row r="28" spans="2:14" s="49" customFormat="1">
+      <c r="B28" s="61" t="n">
         <v>10024</v>
       </c>
-      <c r="C28" s="15" t="s">
+      <c r="C28" s="62" t="s">
         <v>105</v>
       </c>
-      <c r="D28" s="15" t="s">
+      <c r="D28" s="62" t="s">
         <v>106</v>
       </c>
-      <c r="E28" s="15">
+      <c r="E28" s="62" t="n">
         <v>10007</v>
       </c>
-      <c r="F28" s="1" t="s">
+      <c r="F28" s="49" t="s">
         <v>107</v>
       </c>
-      <c r="G28" s="15" t="s">
+      <c r="G28" s="62" t="s">
         <v>108</v>
       </c>
-      <c r="H28" s="1" t="s">
+      <c r="H28" s="49" t="s">
         <v>109</v>
       </c>
-      <c r="J28" s="1" t="s">
+      <c r="J28" s="49" t="s">
         <v>43</v>
       </c>
-      <c r="L28" s="15" t="s">
+      <c r="L28" s="62" t="s">
         <v>44</v>
       </c>
-      <c r="M28" s="1" t="s">
+      <c r="M28" s="49" t="s">
         <v>92</v>
       </c>
-      <c r="N28" s="16" t="s">
+      <c r="N28" s="63" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="29" s="1" customFormat="1" spans="2:14">
-      <c r="B29" s="14">
+    <row r="29" spans="2:14" s="49" customFormat="1">
+      <c r="B29" s="61" t="n">
         <v>10025</v>
       </c>
-      <c r="C29" s="15" t="s">
+      <c r="C29" s="62" t="s">
         <v>110</v>
       </c>
-      <c r="D29" s="15" t="s">
+      <c r="D29" s="62" t="s">
         <v>111</v>
       </c>
-      <c r="E29" s="14">
+      <c r="E29" s="61" t="n">
         <v>10008</v>
       </c>
-      <c r="F29" s="1" t="s">
+      <c r="F29" s="49" t="s">
         <v>112</v>
       </c>
-      <c r="G29" s="15" t="s">
+      <c r="G29" s="62" t="s">
         <v>113</v>
       </c>
-      <c r="H29" s="1" t="s">
+      <c r="H29" s="49" t="s">
         <v>114</v>
       </c>
-      <c r="J29" s="1" t="s">
+      <c r="J29" s="49" t="s">
         <v>43</v>
       </c>
-      <c r="L29" s="15" t="s">
+      <c r="L29" s="62" t="s">
         <v>44</v>
       </c>
-      <c r="M29" s="1" t="s">
+      <c r="M29" s="49" t="s">
         <v>92</v>
       </c>
-      <c r="N29" s="16" t="s">
+      <c r="N29" s="63" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="30" s="1" customFormat="1" spans="2:14">
-      <c r="B30" s="14">
+    <row r="30" spans="2:14" s="49" customFormat="1">
+      <c r="B30" s="61" t="n">
         <v>10026</v>
       </c>
-      <c r="C30" s="15" t="s">
+      <c r="C30" s="62" t="s">
         <v>115</v>
       </c>
-      <c r="D30" s="15" t="s">
+      <c r="D30" s="62" t="s">
         <v>116</v>
       </c>
-      <c r="E30" s="14">
+      <c r="E30" s="61" t="n">
         <v>10009</v>
       </c>
-      <c r="F30" s="1" t="s">
+      <c r="F30" s="49" t="s">
         <v>117</v>
       </c>
-      <c r="G30" s="15" t="s">
+      <c r="G30" s="62" t="s">
         <v>118</v>
       </c>
-      <c r="H30" s="1" t="s">
+      <c r="H30" s="49" t="s">
         <v>119</v>
       </c>
-      <c r="J30" s="1" t="s">
+      <c r="J30" s="49" t="s">
         <v>43</v>
       </c>
-      <c r="L30" s="15" t="s">
+      <c r="L30" s="62" t="s">
         <v>80</v>
       </c>
-      <c r="M30" s="1" t="s">
+      <c r="M30" s="49" t="s">
         <v>92</v>
       </c>
-      <c r="N30" s="16" t="s">
+      <c r="N30" s="63" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="31" s="1" customFormat="1" spans="2:14">
-      <c r="B31" s="14">
+    <row r="31" spans="2:14" s="49" customFormat="1">
+      <c r="B31" s="61" t="n">
         <v>10027</v>
       </c>
-      <c r="C31" s="15" t="s">
+      <c r="C31" s="62" t="s">
         <v>120</v>
       </c>
-      <c r="D31" s="15" t="s">
+      <c r="D31" s="62" t="s">
         <v>121</v>
       </c>
-      <c r="E31" s="14">
+      <c r="E31" s="61" t="n">
         <v>10010</v>
       </c>
-      <c r="F31" s="1" t="s">
+      <c r="F31" s="49" t="s">
         <v>122</v>
       </c>
-      <c r="G31" s="15" t="s">
+      <c r="G31" s="62" t="s">
         <v>123</v>
       </c>
-      <c r="H31" s="1" t="s">
+      <c r="H31" s="49" t="s">
         <v>124</v>
       </c>
-      <c r="J31" s="1" t="s">
+      <c r="J31" s="49" t="s">
         <v>43</v>
       </c>
-      <c r="L31" s="15" t="s">
+      <c r="L31" s="62" t="s">
         <v>44</v>
       </c>
-      <c r="M31" s="1" t="s">
+      <c r="M31" s="49" t="s">
         <v>92</v>
       </c>
-      <c r="N31" s="16" t="s">
+      <c r="N31" s="63" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="32" s="1" customFormat="1" spans="2:14">
-      <c r="B32" s="14">
+    <row r="32" spans="2:14" s="49" customFormat="1">
+      <c r="B32" s="61" t="n">
         <v>10028</v>
       </c>
-      <c r="C32" s="15" t="s">
+      <c r="C32" s="62" t="s">
         <v>125</v>
       </c>
-      <c r="D32" s="15" t="s">
+      <c r="D32" s="62" t="s">
         <v>126</v>
       </c>
-      <c r="E32" s="15">
+      <c r="E32" s="62" t="n">
         <v>10011</v>
       </c>
-      <c r="F32" s="1" t="s">
+      <c r="F32" s="49" t="s">
         <v>127</v>
       </c>
-      <c r="G32" s="15" t="s">
+      <c r="G32" s="62" t="s">
+        <v>127</v>
+      </c>
+      <c r="H32" s="49" t="s">
         <v>128</v>
       </c>
-      <c r="H32" s="1" t="s">
+      <c r="J32" s="49" t="s">
+        <v>43</v>
+      </c>
+      <c r="L32" s="62" t="s">
+        <v>80</v>
+      </c>
+      <c r="M32" s="49" t="s">
+        <v>47</v>
+      </c>
+      <c r="N32" s="63" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="33" spans="2:14" s="50" customFormat="1">
+      <c r="B33" s="64" t="n">
+        <v>10029</v>
+      </c>
+      <c r="C33" s="50" t="s">
         <v>129</v>
       </c>
-      <c r="J32" s="1" t="s">
+      <c r="D33" s="65" t="s">
+        <v>130</v>
+      </c>
+      <c r="E33" s="65" t="n">
+        <v>10012</v>
+      </c>
+      <c r="F33" s="49" t="s">
+        <v>98</v>
+      </c>
+      <c r="G33" s="62" t="s">
+        <v>99</v>
+      </c>
+      <c r="H33" s="50" t="s">
+        <v>131</v>
+      </c>
+      <c r="J33" s="50" t="s">
         <v>43</v>
       </c>
-      <c r="L32" s="15" t="s">
-        <v>80</v>
-      </c>
-      <c r="M32" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="N32" s="16" t="s">
-        <v>39</v>
+      <c r="L33" s="65" t="s">
+        <v>44</v>
+      </c>
+      <c r="M33" s="65" t="s">
+        <v>44</v>
+      </c>
+      <c r="N33" s="63" t="s">
+        <v>132</v>
       </c>
     </row>
-    <row r="33" s="2" customFormat="1" spans="2:14">
-      <c r="B33" s="17">
-        <v>10029</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D33" s="18" t="s">
-        <v>131</v>
-      </c>
-      <c r="E33" s="18">
-        <v>10012</v>
-      </c>
-      <c r="F33" s="1" t="s">
+    <row r="34" spans="2:14" s="50" customFormat="1">
+      <c r="B34" s="64" t="n">
+        <v>10030</v>
+      </c>
+      <c r="C34" s="50" t="s">
+        <v>133</v>
+      </c>
+      <c r="D34" s="65" t="s">
+        <v>134</v>
+      </c>
+      <c r="E34" s="65" t="n">
+        <v>10013</v>
+      </c>
+      <c r="F34" s="49" t="s">
         <v>98</v>
       </c>
-      <c r="G33" s="15" t="s">
+      <c r="G34" s="62" t="s">
         <v>99</v>
       </c>
-      <c r="H33" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="I33" s="2"/>
-      <c r="J33" s="2" t="s">
+      <c r="H34" s="50" t="s">
+        <v>135</v>
+      </c>
+      <c r="J34" s="50" t="s">
         <v>43</v>
       </c>
-      <c r="K33" s="2"/>
-      <c r="L33" s="18" t="s">
+      <c r="L34" s="65" t="s">
         <v>44</v>
       </c>
-      <c r="M33" s="18" t="s">
+      <c r="M34" s="65" t="s">
         <v>44</v>
       </c>
-      <c r="N33" s="16" t="s">
-        <v>133</v>
+      <c r="N34" s="66" t="s">
+        <v>136</v>
       </c>
     </row>
-    <row r="34" s="2" customFormat="1" spans="2:14">
-      <c r="B34" s="17">
-        <v>10030</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="D34" s="18" t="s">
-        <v>135</v>
-      </c>
-      <c r="E34" s="18">
-        <v>10013</v>
-      </c>
-      <c r="F34" s="1" t="s">
+    <row r="35" spans="2:14" s="50" customFormat="1">
+      <c r="B35" s="64" t="n">
+        <v>10031</v>
+      </c>
+      <c r="C35" s="50" t="s">
+        <v>137</v>
+      </c>
+      <c r="D35" s="65" t="s">
+        <v>138</v>
+      </c>
+      <c r="E35" s="65" t="n">
+        <v>10014</v>
+      </c>
+      <c r="F35" s="49" t="s">
         <v>98</v>
       </c>
-      <c r="G34" s="15" t="s">
+      <c r="G35" s="62" t="s">
         <v>99</v>
       </c>
-      <c r="H34" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="I34" s="2"/>
-      <c r="J34" s="2" t="s">
+      <c r="H35" s="50" t="s">
+        <v>139</v>
+      </c>
+      <c r="J35" s="50" t="s">
         <v>43</v>
       </c>
-      <c r="K34" s="2"/>
-      <c r="L34" s="18" t="s">
+      <c r="L35" s="65" t="s">
         <v>44</v>
       </c>
-      <c r="M34" s="18" t="s">
+      <c r="M35" s="65" t="s">
         <v>44</v>
       </c>
-      <c r="N34" s="19" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="35" s="2" customFormat="1" spans="2:14">
-      <c r="B35" s="17">
-        <v>10031</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="D35" s="18" t="s">
-        <v>139</v>
-      </c>
-      <c r="E35" s="18">
-        <v>10014</v>
-      </c>
-      <c r="F35" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="G35" s="15" t="s">
-        <v>99</v>
-      </c>
-      <c r="H35" s="2" t="s">
+      <c r="N35" s="66" t="s">
         <v>140</v>
-      </c>
-      <c r="I35" s="2"/>
-      <c r="J35" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K35" s="2"/>
-      <c r="L35" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="M35" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="N35" s="19" t="s">
-        <v>141</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
+  <printOptions>
+    <extLst>
+      <ext uri="smNativeData">
+        <pm:pageFlags xmlns:pm="smNativeData" id="1784688383" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+      </ext>
+    </extLst>
+  </printOptions>
+  <pageMargins left="0.700000" right="0.700000" top="0.750000" bottom="0.750000" header="0.300000" footer="0.300000"/>
+  <pageSetup paperSize="9" fitToWidth="0" fitToHeight="1" pageOrder="overThenDown"/>
+  <headerFooter>
+    <extLst>
+      <ext uri="smNativeData">
+        <pm:header xmlns:pm="smNativeData" id="1784688383" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1784688383" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1784688383" Id="0" type="0" value="0"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1784688383" Id="1" type="0" value="0"/>
+      </ext>
+    </extLst>
+  </headerFooter>
+  <extLst>
+    <ext uri="smNativeData">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1784688383" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+        <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
+        <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
+      </pm:sheetPrefs>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
--- a/ExcelTool/LubanTools/DataTables/Datas/NpcData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/NpcData.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64D0E18C-847B-4A4E-B0AB-7BA974F41D0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowHeight="17680" tabRatio="500"/>
+    <workbookView xWindow="0" yWindow="2310" windowWidth="37160" windowHeight="18570" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="角色表" sheetId="1" r:id="rId1"/>
@@ -27,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="135">
   <si>
     <t>##var</t>
   </si>
@@ -44,9 +50,6 @@
     <t>CharacterData</t>
   </si>
   <si>
-    <t>SceneSpinePath</t>
-  </si>
-  <si>
     <t>MiniImg</t>
   </si>
   <si>
@@ -209,9 +212,6 @@
     <t>CharacterNames+Character_NPC_03</t>
   </si>
   <si>
-    <t>单人_女二@2x</t>
-  </si>
-  <si>
     <t>女二@2x</t>
   </si>
   <si>
@@ -245,9 +245,6 @@
     <t>CharacterNames+Character_NPC_04</t>
   </si>
   <si>
-    <t>单人_女仆@2x</t>
-  </si>
-  <si>
     <t>女三女仆@2x</t>
   </si>
   <si>
@@ -266,9 +263,6 @@
     <t>CharacterNames+Character_NPC_05</t>
   </si>
   <si>
-    <t>单人_女四@2x</t>
-  </si>
-  <si>
     <t>女四@2x</t>
   </si>
   <si>
@@ -326,9 +320,6 @@
     <t>CharacterNames+Character_NPC_07</t>
   </si>
   <si>
-    <t>单人_酒保@2x</t>
-  </si>
-  <si>
     <t>酒保@2x</t>
   </si>
   <si>
@@ -353,9 +344,6 @@
     <t>CharacterNames+Character_NPC_08</t>
   </si>
   <si>
-    <t>单人_经理@2x</t>
-  </si>
-  <si>
     <t>PlantManager</t>
   </si>
   <si>
@@ -368,9 +356,6 @@
     <t>CharacterNames+Character_NPC_09</t>
   </si>
   <si>
-    <t>单人_布料店@2x</t>
-  </si>
-  <si>
     <t>布料店@2x</t>
   </si>
   <si>
@@ -383,9 +368,6 @@
     <t>CharacterNames+Character_NPC_10</t>
   </si>
   <si>
-    <t>单人_摄影小妹@2x</t>
-  </si>
-  <si>
     <t>摄影小妹@2x</t>
   </si>
   <si>
@@ -398,9 +380,6 @@
     <t>CharacterNames+Character_NPC_11</t>
   </si>
   <si>
-    <t>单人_果蔬大叔@2x</t>
-  </si>
-  <si>
     <t>果蔬店大叔@2x</t>
   </si>
   <si>
@@ -453,19 +432,20 @@
   </si>
   <si>
     <t>-6.5,-2.0</t>
+  </si>
+  <si>
+    <t>illustPath</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Prefabs/DramaActor/01/char003703_SkeletonData.asset</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="21">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -476,135 +456,22 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="微软雅黑"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF1F2329"/>
       <name val="微软雅黑"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <sz val="9"/>
       <name val="等线"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color rgb="FF44546A"/>
-      <name val="等线"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color rgb="FF44546A"/>
-      <name val="等线"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color rgb="FF44546A"/>
-      <name val="等线"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF44546A"/>
-      <name val="等线"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="等线"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -641,170 +508,8 @@
         <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5B9BD5"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDEBF7"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9BC2E6"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED7D31"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBE3D5"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8CAAB"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4AF82"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEBEBEB"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD9D9D9"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC7C7C7"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CA"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFE697"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFD964"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4472C4"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD9E1F2"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB4C6E7"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8EA9DB"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF70AD47"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE1EFD8"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="10">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -827,258 +532,16 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color rgb="FF5B9BD5"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color rgb="FFACCCEA"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FF5B9BD5"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF5B9BD5"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1102,89 +565,54 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1437,30 +865,31 @@
       </a:style>
     </a:spDef>
   </a:objectDefaults>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N35"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="2" width="8.66666666666667" style="3" customWidth="1"/>
-    <col min="3" max="3" width="25.8333333333333" style="3" customWidth="1"/>
-    <col min="4" max="6" width="35.5833333333333" style="3" customWidth="1"/>
-    <col min="7" max="7" width="23" style="4" customWidth="1"/>
-    <col min="8" max="8" width="33.5833333333333" style="3" customWidth="1"/>
+    <col min="1" max="2" width="8.6640625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="25.83203125" style="3" customWidth="1"/>
+    <col min="4" max="5" width="35.58203125" style="3" customWidth="1"/>
+    <col min="6" max="6" width="85.75" style="19" customWidth="1"/>
+    <col min="7" max="7" width="49.33203125" style="4" customWidth="1"/>
+    <col min="8" max="8" width="33.58203125" style="3" customWidth="1"/>
     <col min="9" max="9" width="23.25" style="3" customWidth="1"/>
-    <col min="10" max="10" width="21.4166666666667" style="3" customWidth="1"/>
-    <col min="11" max="11" width="16.5833333333333" style="3" customWidth="1"/>
+    <col min="10" max="10" width="21.4140625" style="3" customWidth="1"/>
+    <col min="11" max="11" width="16.58203125" style="3" customWidth="1"/>
     <col min="12" max="12" width="28" style="4" customWidth="1"/>
     <col min="13" max="13" width="17.75" style="3" customWidth="1"/>
-    <col min="14" max="14" width="17.3333333333333" style="5" customWidth="1"/>
+    <col min="14" max="14" width="17.33203125" style="5" customWidth="1"/>
     <col min="15" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1476,1228 +905,1231 @@
       <c r="E1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="20" t="s">
+        <v>133</v>
+      </c>
+      <c r="G1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="H1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="J1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="K1" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="L1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="M1" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="N1" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="9" t="s">
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A2" s="3" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
-      <c r="A2" s="3" t="s">
+      <c r="B2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="C2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="E2" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="E2" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="H2" s="10" t="s">
+      <c r="I2" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="I2" s="8" t="s">
+      <c r="J2" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="K2" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="J2" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="K2" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="L2" s="11" t="s">
+      <c r="M2" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="M2" s="12" t="s">
+      <c r="N2" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="N2" s="5" t="s">
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A3" s="3" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="3" spans="1:14">
-      <c r="A3" s="3" t="s">
+      <c r="B3" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="C3" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="D3" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="E3" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="F3" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="G3" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="H3" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="I3" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="J3" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="K3" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="L3" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="L3" s="4" t="s">
+      <c r="M3" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="M3" s="3" t="s">
+      <c r="N3" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="N3" s="5" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="4" s="1" customFormat="1" spans="1:14">
+    </row>
+    <row r="4" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B4" s="13">
         <v>10000</v>
       </c>
       <c r="C4" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="D4" s="14" t="s">
         <v>37</v>
-      </c>
-      <c r="D4" s="14" t="s">
-        <v>38</v>
       </c>
       <c r="E4" s="13">
         <v>10000</v>
       </c>
+      <c r="F4" s="21" t="s">
+        <v>134</v>
+      </c>
       <c r="G4" s="14"/>
       <c r="N4" s="15" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="5" s="1" customFormat="1" spans="1:14">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B5" s="13">
         <v>10001</v>
       </c>
       <c r="C5" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="D5" s="14" t="s">
         <v>40</v>
-      </c>
-      <c r="D5" s="14" t="s">
-        <v>41</v>
       </c>
       <c r="E5" s="13">
         <v>10001</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="F5" s="21" t="s">
+        <v>134</v>
+      </c>
+      <c r="G5" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="H5" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G5" s="14" t="s">
-        <v>42</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="J5" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="L5" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="L5" s="14" t="s">
+      <c r="M5" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="M5" s="1" t="s">
-        <v>46</v>
-      </c>
       <c r="N5" s="15" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="6" s="1" customFormat="1" spans="1:14">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B6" s="13">
         <v>10002</v>
       </c>
       <c r="C6" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="D6" s="14" t="s">
         <v>40</v>
-      </c>
-      <c r="D6" s="14" t="s">
-        <v>41</v>
       </c>
       <c r="E6" s="13">
         <v>10001</v>
       </c>
-      <c r="F6" s="1" t="s">
-        <v>42</v>
+      <c r="F6" s="21" t="s">
+        <v>134</v>
       </c>
       <c r="G6" s="14" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H6" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="L6" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="M6" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="J6" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="L6" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="M6" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="N6" s="15" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="7" s="1" customFormat="1" spans="1:14">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B7" s="13">
         <v>10003</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E7" s="13">
         <v>10001</v>
       </c>
-      <c r="F7" s="1" t="s">
-        <v>42</v>
+      <c r="F7" s="21" t="s">
+        <v>134</v>
       </c>
       <c r="G7" s="14" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H7" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="L7" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="J7" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="L7" s="14" t="s">
+      <c r="M7" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="M7" s="1" t="s">
-        <v>52</v>
-      </c>
       <c r="N7" s="15" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="8" s="1" customFormat="1" spans="1:14">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B8" s="13">
         <v>10004</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E8" s="13">
         <v>10001</v>
       </c>
-      <c r="F8" s="1" t="s">
-        <v>42</v>
+      <c r="F8" s="21" t="s">
+        <v>134</v>
       </c>
       <c r="G8" s="14" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="L8" s="14" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="N8" s="15" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="9" s="1" customFormat="1" spans="1:14">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B9" s="13">
         <v>10005</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E9" s="13">
         <v>10001</v>
       </c>
-      <c r="F9" s="1" t="s">
-        <v>42</v>
+      <c r="F9" s="21" t="s">
+        <v>134</v>
       </c>
       <c r="G9" s="14" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H9" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="L9" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="M9" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="J9" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="L9" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="M9" s="1" t="s">
-        <v>57</v>
-      </c>
       <c r="N9" s="15" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="10" s="1" customFormat="1" spans="1:14">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B10" s="13">
         <v>10006</v>
       </c>
       <c r="C10" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="D10" s="14" t="s">
         <v>58</v>
-      </c>
-      <c r="D10" s="14" t="s">
-        <v>59</v>
       </c>
       <c r="E10" s="13">
         <v>10002</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="F10" s="21" t="s">
+        <v>134</v>
+      </c>
+      <c r="G10" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="H10" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="G10" s="14" t="s">
+      <c r="J10" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="L10" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="H10" s="1" t="s">
+      <c r="M10" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="J10" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="L10" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="M10" s="1" t="s">
-        <v>64</v>
-      </c>
       <c r="N10" s="15" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="11" s="1" customFormat="1" spans="1:14">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B11" s="13">
         <v>10007</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E11" s="13">
         <v>10002</v>
       </c>
-      <c r="F11" s="1" t="s">
+      <c r="F11" s="21" t="s">
+        <v>134</v>
+      </c>
+      <c r="G11" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="H11" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="G11" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>62</v>
-      </c>
       <c r="J11" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="L11" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="L11" s="14" t="s">
-        <v>45</v>
-      </c>
       <c r="M11" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N11" s="15" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="12" s="1" customFormat="1" spans="1:14">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B12" s="13">
         <v>10008</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E12" s="13">
         <v>10002</v>
       </c>
-      <c r="F12" s="1" t="s">
+      <c r="F12" s="21" t="s">
+        <v>134</v>
+      </c>
+      <c r="G12" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="H12" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="G12" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>62</v>
-      </c>
       <c r="J12" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="L12" s="14" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="N12" s="15" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="13" s="1" customFormat="1" spans="1:14">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B13" s="13">
         <v>10009</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E13" s="13">
         <v>10002</v>
       </c>
-      <c r="F13" s="1" t="s">
-        <v>60</v>
+      <c r="F13" s="21" t="s">
+        <v>134</v>
       </c>
       <c r="G13" s="14" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J13" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="L13" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="L13" s="14" t="s">
-        <v>45</v>
-      </c>
       <c r="M13" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="N13" s="15" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="14" s="1" customFormat="1" spans="1:14">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B14" s="13">
         <v>10010</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E14" s="13">
         <v>10002</v>
       </c>
-      <c r="F14" s="1" t="s">
-        <v>60</v>
+      <c r="F14" s="21" t="s">
+        <v>134</v>
       </c>
       <c r="G14" s="14" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J14" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="L14" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="L14" s="14" t="s">
+      <c r="M14" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="M14" s="1" t="s">
-        <v>46</v>
-      </c>
       <c r="N14" s="15" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="15" s="1" customFormat="1" spans="1:14">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B15" s="13">
         <v>10011</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E15" s="14">
         <v>10003</v>
       </c>
-      <c r="F15" s="1" t="s">
-        <v>72</v>
+      <c r="F15" s="21" t="s">
+        <v>134</v>
       </c>
       <c r="G15" s="14" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="L15" s="14" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="N15" s="15" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="16" s="1" customFormat="1" spans="1:14">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B16" s="13">
         <v>10012</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E16" s="14">
         <v>10003</v>
       </c>
-      <c r="F16" s="1" t="s">
-        <v>72</v>
+      <c r="F16" s="21" t="s">
+        <v>134</v>
       </c>
       <c r="G16" s="14" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="L16" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="M16" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="M16" s="1" t="s">
-        <v>52</v>
-      </c>
       <c r="N16" s="15" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="17" s="1" customFormat="1" spans="2:14">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="17" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B17" s="13">
         <v>10013</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E17" s="14">
         <v>10003</v>
       </c>
-      <c r="F17" s="1" t="s">
-        <v>72</v>
+      <c r="F17" s="21" t="s">
+        <v>134</v>
       </c>
       <c r="G17" s="14" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="L17" s="14" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="N17" s="15" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="18" s="1" customFormat="1" spans="2:14">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="18" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B18" s="13">
         <v>10014</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E18" s="14">
         <v>10003</v>
       </c>
-      <c r="F18" s="1" t="s">
-        <v>72</v>
+      <c r="F18" s="21" t="s">
+        <v>134</v>
       </c>
       <c r="G18" s="14" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="L18" s="14" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="N18" s="15" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="19" s="1" customFormat="1" spans="2:14">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="19" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B19" s="13">
         <v>10015</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D19" s="14" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E19" s="13">
         <v>10004</v>
       </c>
-      <c r="F19" s="1" t="s">
+      <c r="F19" s="21" t="s">
+        <v>134</v>
+      </c>
+      <c r="G19" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="L19" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="M19" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="G19" s="14" t="s">
-        <v>80</v>
-      </c>
-      <c r="H19" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="J19" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="L19" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="M19" s="1" t="s">
-        <v>83</v>
-      </c>
       <c r="N19" s="15" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="20" s="1" customFormat="1" spans="2:14">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="20" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B20" s="13">
         <v>10016</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E20" s="13">
         <v>10004</v>
       </c>
-      <c r="F20" s="1" t="s">
-        <v>79</v>
+      <c r="F20" s="21" t="s">
+        <v>134</v>
       </c>
       <c r="G20" s="14" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="L20" s="14" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N20" s="15" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="21" s="1" customFormat="1" spans="2:14">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="21" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B21" s="13">
         <v>10017</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D21" s="14" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E21" s="13">
         <v>10004</v>
       </c>
-      <c r="F21" s="1" t="s">
-        <v>79</v>
+      <c r="F21" s="21" t="s">
+        <v>134</v>
       </c>
       <c r="G21" s="14" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="L21" s="14" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N21" s="15" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="22" s="1" customFormat="1" spans="2:14">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="22" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B22" s="13">
         <v>10018</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D22" s="14" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E22" s="13">
         <v>10004</v>
       </c>
-      <c r="F22" s="1" t="s">
-        <v>79</v>
+      <c r="F22" s="21" t="s">
+        <v>134</v>
       </c>
       <c r="G22" s="14" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="L22" s="14" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="N22" s="15" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="23" s="1" customFormat="1" spans="2:14">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="23" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B23" s="13">
         <v>10019</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D23" s="14" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="E23" s="13">
         <v>10005</v>
       </c>
-      <c r="F23" s="1" t="s">
-        <v>92</v>
+      <c r="F23" s="21" t="s">
+        <v>134</v>
       </c>
       <c r="G23" s="14" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="J23" s="1">
         <v>10100</v>
       </c>
       <c r="L23" s="14" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="N23" s="15" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="24" s="1" customFormat="1" spans="2:14">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="24" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B24" s="13">
         <v>10020</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D24" s="14" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="E24" s="13">
         <v>10005</v>
       </c>
-      <c r="F24" s="1" t="s">
-        <v>92</v>
+      <c r="F24" s="21" t="s">
+        <v>134</v>
       </c>
       <c r="G24" s="14" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="L24" s="14" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="N24" s="15" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="25" s="1" customFormat="1" spans="2:14">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="25" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B25" s="13">
         <v>10021</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="D25" s="14" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="E25" s="13">
         <v>10005</v>
       </c>
-      <c r="F25" s="1" t="s">
+      <c r="F25" s="21" t="s">
+        <v>134</v>
+      </c>
+      <c r="G25" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="H25" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="G25" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="H25" s="1" t="s">
-        <v>96</v>
-      </c>
       <c r="J25" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="L25" s="14" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M25" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N25" s="15" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="26" s="1" customFormat="1" spans="2:14">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="26" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B26" s="13">
         <v>10022</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D26" s="14" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="E26" s="13">
         <v>10006</v>
       </c>
-      <c r="F26" s="1" t="s">
-        <v>99</v>
+      <c r="F26" s="21" t="s">
+        <v>134</v>
       </c>
       <c r="G26" s="14" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="J26" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="L26" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="L26" s="14" t="s">
-        <v>45</v>
-      </c>
       <c r="M26" s="1" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="N26" s="15" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="27" s="1" customFormat="1" spans="2:14">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="27" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B27" s="13">
         <v>10023</v>
       </c>
       <c r="C27" s="14" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="D27" s="14" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="E27" s="13">
         <v>10006</v>
       </c>
-      <c r="F27" s="1" t="s">
+      <c r="F27" s="21" t="s">
+        <v>134</v>
+      </c>
+      <c r="G27" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="H27" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="G27" s="14" t="s">
+      <c r="J27" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="L27" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="M27" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="N27" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="H27" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="J27" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="L27" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="M27" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="N27" s="15" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="28" s="1" customFormat="1" spans="2:14">
+    </row>
+    <row r="28" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B28" s="13">
         <v>10024</v>
       </c>
       <c r="C28" s="14" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="D28" s="14" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="E28" s="14">
         <v>10007</v>
       </c>
-      <c r="F28" s="1" t="s">
-        <v>108</v>
+      <c r="F28" s="21" t="s">
+        <v>134</v>
       </c>
       <c r="G28" s="14" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="J28" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="L28" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="L28" s="14" t="s">
-        <v>45</v>
-      </c>
       <c r="M28" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="N28" s="15" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="29" s="1" customFormat="1" spans="2:14">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="29" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B29" s="13">
         <v>10025</v>
       </c>
       <c r="C29" s="14" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="D29" s="14" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="E29" s="13">
         <v>10008</v>
       </c>
-      <c r="F29" s="1" t="s">
-        <v>113</v>
+      <c r="F29" s="21" t="s">
+        <v>134</v>
       </c>
       <c r="G29" s="14" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="J29" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="L29" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="L29" s="14" t="s">
-        <v>45</v>
-      </c>
       <c r="M29" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="N29" s="15" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="30" s="1" customFormat="1" spans="2:14">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="30" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B30" s="13">
         <v>10026</v>
       </c>
       <c r="C30" s="14" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="D30" s="14" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="E30" s="13">
         <v>10009</v>
       </c>
-      <c r="F30" s="1" t="s">
-        <v>118</v>
+      <c r="F30" s="21" t="s">
+        <v>134</v>
       </c>
       <c r="G30" s="14" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="L30" s="14" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="M30" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="N30" s="15" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="31" s="1" customFormat="1" spans="2:14">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="31" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B31" s="13">
         <v>10027</v>
       </c>
       <c r="C31" s="14" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="D31" s="14" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="E31" s="13">
         <v>10010</v>
       </c>
-      <c r="F31" s="1" t="s">
-        <v>123</v>
+      <c r="F31" s="21" t="s">
+        <v>134</v>
       </c>
       <c r="G31" s="14" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="J31" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="L31" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="L31" s="14" t="s">
-        <v>45</v>
-      </c>
       <c r="M31" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="N31" s="15" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="32" s="1" customFormat="1" spans="2:14">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="32" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B32" s="13">
         <v>10028</v>
       </c>
       <c r="C32" s="14" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="D32" s="14" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="E32" s="14">
         <v>10011</v>
       </c>
-      <c r="F32" s="1" t="s">
-        <v>128</v>
+      <c r="F32" s="21" t="s">
+        <v>134</v>
       </c>
       <c r="G32" s="14" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="L32" s="14" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="M32" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N32" s="15" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="33" s="2" customFormat="1" spans="2:14">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="33" spans="2:14" s="2" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B33" s="16">
         <v>10029</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="D33" s="17" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="E33" s="17">
         <v>10012</v>
       </c>
-      <c r="F33" s="1" t="s">
-        <v>99</v>
+      <c r="F33" s="21" t="s">
+        <v>134</v>
       </c>
       <c r="G33" s="14" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="J33" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L33" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="L33" s="17" t="s">
-        <v>45</v>
-      </c>
       <c r="M33" s="17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N33" s="15" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="34" s="2" customFormat="1" spans="2:14">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="34" spans="2:14" s="2" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B34" s="16">
         <v>10030</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="D34" s="17" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="E34" s="17">
         <v>10013</v>
       </c>
-      <c r="F34" s="1" t="s">
-        <v>99</v>
+      <c r="F34" s="21" t="s">
+        <v>134</v>
       </c>
       <c r="G34" s="14" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="J34" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L34" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="L34" s="17" t="s">
-        <v>45</v>
-      </c>
       <c r="M34" s="17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N34" s="18" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="35" s="2" customFormat="1" spans="2:14">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="35" spans="2:14" s="2" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B35" s="16">
         <v>10031</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="D35" s="17" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="E35" s="17">
         <v>10014</v>
       </c>
-      <c r="F35" s="1" t="s">
-        <v>99</v>
+      <c r="F35" s="21" t="s">
+        <v>134</v>
       </c>
       <c r="G35" s="14" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="J35" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L35" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="L35" s="17" t="s">
-        <v>45</v>
-      </c>
       <c r="M35" s="17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N35" s="18" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" fitToWidth="0" pageOrder="overThenDown" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/ExcelTool/LubanTools/DataTables/Datas/NpcData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/NpcData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64D0E18C-847B-4A4E-B0AB-7BA974F41D0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B679710-1D18-4B52-AD00-4D970B5DD986}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2310" windowWidth="37160" windowHeight="18570" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-9940" yWindow="2230" windowWidth="44100" windowHeight="18570" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="角色表" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="173">
   <si>
     <t>##var</t>
   </si>
@@ -116,9 +116,6 @@
     <t>绑定真实ID</t>
   </si>
   <si>
-    <t>立绘(后期换为Spine)</t>
-  </si>
-  <si>
     <t>立绘</t>
   </si>
   <si>
@@ -434,11 +431,134 @@
     <t>-6.5,-2.0</t>
   </si>
   <si>
-    <t>illustPath</t>
+    <t>Assets/AddressableAssets/Remote/Prefabs/DramaActor/01/char003703_SkeletonData.asset</t>
+  </si>
+  <si>
+    <t>CusbimPath</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>Assets/AddressableAssets/Remote/Prefabs/DramaActor/01/char003703_SkeletonData.asset</t>
+    <t>TexturePath</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Live2D路径</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>DramaSpinePaht</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>剧情Spine路径</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>立绘图路径</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Cusbim/Char_01/Prefabs/Chat_01.prefab</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Prefabs/DramaActor/01/char003704_SkeletonData.asset</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Prefabs/DramaActor/01/char003705_SkeletonData.asset</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Prefabs/DramaActor/01/char003706_SkeletonData.asset</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Prefabs/DramaActor/01/char003707_SkeletonData.asset</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Prefabs/DramaActor/01/char003708_SkeletonData.asset</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Prefabs/DramaActor/01/char003709_SkeletonData.asset</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Prefabs/DramaActor/01/char003710_SkeletonData.asset</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Prefabs/DramaActor/01/char003711_SkeletonData.asset</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Prefabs/DramaActor/01/char003712_SkeletonData.asset</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Prefabs/DramaActor/01/char003713_SkeletonData.asset</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Prefabs/DramaActor/01/char003714_SkeletonData.asset</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Prefabs/DramaActor/01/char003715_SkeletonData.asset</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Prefabs/DramaActor/01/char003716_SkeletonData.asset</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Prefabs/DramaActor/01/char003717_SkeletonData.asset</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Prefabs/DramaActor/01/char003718_SkeletonData.asset</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Prefabs/DramaActor/01/char003719_SkeletonData.asset</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Prefabs/DramaActor/01/char003720_SkeletonData.asset</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Prefabs/DramaActor/01/char003721_SkeletonData.asset</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Prefabs/DramaActor/01/char003722_SkeletonData.asset</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Prefabs/DramaActor/01/char003723_SkeletonData.asset</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Prefabs/DramaActor/01/char003724_SkeletonData.asset</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Prefabs/DramaActor/01/char003725_SkeletonData.asset</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Prefabs/DramaActor/01/char003726_SkeletonData.asset</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Prefabs/DramaActor/01/char003727_SkeletonData.asset</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Prefabs/DramaActor/01/char003728_SkeletonData.asset</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Prefabs/DramaActor/01/char003729_SkeletonData.asset</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Prefabs/DramaActor/01/char003730_SkeletonData.asset</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Prefabs/DramaActor/01/char003731_SkeletonData.asset</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Prefabs/DramaActor/01/char003732_SkeletonData.asset</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Prefabs/DramaActor/01/char003733_SkeletonData.asset</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Prefabs/DramaActor/01/char003734_SkeletonData.asset</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Texture2D/Characters/DialogueTexture2D/Machi.png</t>
   </si>
 </sst>
 </file>
@@ -536,7 +656,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -596,10 +716,13 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -871,25 +994,27 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N35"/>
+  <dimension ref="A1:P35"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="2" width="8.6640625" style="3" customWidth="1"/>
     <col min="3" max="3" width="25.83203125" style="3" customWidth="1"/>
     <col min="4" max="5" width="35.58203125" style="3" customWidth="1"/>
-    <col min="6" max="6" width="85.75" style="19" customWidth="1"/>
-    <col min="7" max="7" width="49.33203125" style="4" customWidth="1"/>
-    <col min="8" max="8" width="33.58203125" style="3" customWidth="1"/>
-    <col min="9" max="9" width="23.25" style="3" customWidth="1"/>
-    <col min="10" max="10" width="21.4140625" style="3" customWidth="1"/>
-    <col min="11" max="11" width="16.58203125" style="3" customWidth="1"/>
-    <col min="12" max="12" width="28" style="4" customWidth="1"/>
-    <col min="13" max="13" width="17.75" style="3" customWidth="1"/>
-    <col min="14" max="14" width="17.33203125" style="5" customWidth="1"/>
-    <col min="15" max="16384" width="9" style="3"/>
+    <col min="6" max="6" width="73.1640625" style="22" customWidth="1"/>
+    <col min="7" max="7" width="82.4140625" style="22" customWidth="1"/>
+    <col min="8" max="8" width="95.33203125" style="22" customWidth="1"/>
+    <col min="9" max="9" width="49.33203125" style="4" customWidth="1"/>
+    <col min="10" max="10" width="33.58203125" style="3" customWidth="1"/>
+    <col min="11" max="11" width="23.25" style="3" customWidth="1"/>
+    <col min="12" max="12" width="21.4140625" style="3" customWidth="1"/>
+    <col min="13" max="13" width="16.58203125" style="3" customWidth="1"/>
+    <col min="14" max="14" width="28" style="4" customWidth="1"/>
+    <col min="15" max="15" width="17.75" style="3" customWidth="1"/>
+    <col min="16" max="16" width="17.33203125" style="5" customWidth="1"/>
+    <col min="17" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -908,32 +1033,38 @@
       <c r="F1" s="20" t="s">
         <v>133</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="H1" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="I1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="K1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="L1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="M1" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="N1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="O1" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="9" t="s">
+      <c r="P1" s="9" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A2" s="3" t="s">
         <v>13</v>
       </c>
@@ -950,34 +1081,40 @@
         <v>14</v>
       </c>
       <c r="F2" s="19" t="s">
+        <v>135</v>
+      </c>
+      <c r="G2" s="19" t="s">
+        <v>135</v>
+      </c>
+      <c r="H2" s="19" t="s">
+        <v>135</v>
+      </c>
+      <c r="I2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="H2" s="10" t="s">
+      <c r="J2" s="10" t="s">
         <v>17</v>
-      </c>
-      <c r="I2" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="J2" s="8" t="s">
-        <v>18</v>
       </c>
       <c r="K2" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="L2" s="11" t="s">
+      <c r="L2" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="M2" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="N2" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="M2" s="12" t="s">
+      <c r="O2" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="N2" s="5" t="s">
+      <c r="P2" s="5" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A3" s="3" t="s">
         <v>22</v>
       </c>
@@ -994,1137 +1131,1335 @@
         <v>26</v>
       </c>
       <c r="F3" s="20" t="s">
+        <v>136</v>
+      </c>
+      <c r="G3" s="20" t="s">
+        <v>138</v>
+      </c>
+      <c r="H3" s="20" t="s">
+        <v>139</v>
+      </c>
+      <c r="I3" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="J3" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="K3" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="L3" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="M3" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="N3" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="L3" s="4" t="s">
+      <c r="O3" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M3" s="3" t="s">
+      <c r="P3" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="N3" s="5" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
+    </row>
+    <row r="4" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B4" s="13">
         <v>10000</v>
       </c>
       <c r="C4" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" s="14" t="s">
         <v>36</v>
-      </c>
-      <c r="D4" s="14" t="s">
-        <v>37</v>
       </c>
       <c r="E4" s="13">
         <v>10000</v>
       </c>
       <c r="F4" s="21" t="s">
-        <v>134</v>
-      </c>
-      <c r="G4" s="14"/>
-      <c r="N4" s="15" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
+        <v>140</v>
+      </c>
+      <c r="G4" s="21" t="s">
+        <v>132</v>
+      </c>
+      <c r="H4" s="21" t="s">
+        <v>172</v>
+      </c>
+      <c r="I4" s="14"/>
+      <c r="P4" s="15" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B5" s="13">
         <v>10001</v>
       </c>
       <c r="C5" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="D5" s="14" t="s">
         <v>39</v>
-      </c>
-      <c r="D5" s="14" t="s">
-        <v>40</v>
       </c>
       <c r="E5" s="13">
         <v>10001</v>
       </c>
       <c r="F5" s="21" t="s">
-        <v>134</v>
-      </c>
-      <c r="G5" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="G5" s="21" t="s">
+        <v>141</v>
+      </c>
+      <c r="H5" s="21" t="s">
+        <v>172</v>
+      </c>
+      <c r="I5" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="J5" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="H5" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="J5" s="1" t="s">
+      <c r="L5" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N5" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="L5" s="14" t="s">
+      <c r="O5" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="M5" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="N5" s="15" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="P5" s="15" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B6" s="13">
         <v>10002</v>
       </c>
       <c r="C6" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="D6" s="14" t="s">
         <v>39</v>
-      </c>
-      <c r="D6" s="14" t="s">
-        <v>40</v>
       </c>
       <c r="E6" s="13">
         <v>10001</v>
       </c>
       <c r="F6" s="21" t="s">
-        <v>134</v>
-      </c>
-      <c r="G6" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="H6" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="G6" s="21" t="s">
+        <v>142</v>
+      </c>
+      <c r="H6" s="21" t="s">
+        <v>172</v>
+      </c>
+      <c r="I6" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N6" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="O6" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="J6" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="L6" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="M6" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="N6" s="15" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="P6" s="15" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B7" s="13">
         <v>10003</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E7" s="13">
         <v>10001</v>
       </c>
       <c r="F7" s="21" t="s">
-        <v>134</v>
-      </c>
-      <c r="G7" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="H7" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="G7" s="21" t="s">
+        <v>143</v>
+      </c>
+      <c r="H7" s="21" t="s">
+        <v>172</v>
+      </c>
+      <c r="I7" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N7" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="J7" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="L7" s="14" t="s">
+      <c r="O7" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="M7" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="N7" s="15" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="P7" s="15" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B8" s="13">
         <v>10004</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E8" s="13">
         <v>10001</v>
       </c>
       <c r="F8" s="21" t="s">
-        <v>134</v>
-      </c>
-      <c r="G8" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>49</v>
+        <v>140</v>
+      </c>
+      <c r="G8" s="21" t="s">
+        <v>144</v>
+      </c>
+      <c r="H8" s="21" t="s">
+        <v>172</v>
+      </c>
+      <c r="I8" s="14" t="s">
+        <v>40</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="L8" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="M8" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="N8" s="15" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
+        <v>48</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N8" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="O8" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="P8" s="15" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B9" s="13">
         <v>10005</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E9" s="13">
         <v>10001</v>
       </c>
       <c r="F9" s="21" t="s">
-        <v>134</v>
-      </c>
-      <c r="G9" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="H9" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="G9" s="21" t="s">
+        <v>145</v>
+      </c>
+      <c r="H9" s="21" t="s">
+        <v>172</v>
+      </c>
+      <c r="I9" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N9" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="O9" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="J9" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="L9" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="M9" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="N9" s="15" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="P9" s="15" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B10" s="13">
         <v>10006</v>
       </c>
       <c r="C10" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="D10" s="14" t="s">
         <v>57</v>
-      </c>
-      <c r="D10" s="14" t="s">
-        <v>58</v>
       </c>
       <c r="E10" s="13">
         <v>10002</v>
       </c>
       <c r="F10" s="21" t="s">
-        <v>134</v>
-      </c>
-      <c r="G10" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="G10" s="21" t="s">
+        <v>146</v>
+      </c>
+      <c r="H10" s="21" t="s">
+        <v>172</v>
+      </c>
+      <c r="I10" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="J10" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="H10" s="1" t="s">
+      <c r="L10" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N10" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="J10" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="L10" s="14" t="s">
+      <c r="O10" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="M10" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="N10" s="15" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="P10" s="15" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B11" s="13">
         <v>10007</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E11" s="13">
         <v>10002</v>
       </c>
       <c r="F11" s="21" t="s">
-        <v>134</v>
-      </c>
-      <c r="G11" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="G11" s="21" t="s">
+        <v>147</v>
+      </c>
+      <c r="H11" s="21" t="s">
+        <v>172</v>
+      </c>
+      <c r="I11" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="J11" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="H11" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="J11" s="1" t="s">
+      <c r="L11" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N11" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="L11" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="M11" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="N11" s="15" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="O11" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="P11" s="15" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B12" s="13">
         <v>10008</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E12" s="13">
         <v>10002</v>
       </c>
       <c r="F12" s="21" t="s">
-        <v>134</v>
-      </c>
-      <c r="G12" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="G12" s="21" t="s">
+        <v>148</v>
+      </c>
+      <c r="H12" s="21" t="s">
+        <v>172</v>
+      </c>
+      <c r="I12" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="J12" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="H12" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="J12" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="L12" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="M12" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="N12" s="15" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="L12" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N12" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="O12" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="P12" s="15" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B13" s="13">
         <v>10009</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E13" s="13">
         <v>10002</v>
       </c>
       <c r="F13" s="21" t="s">
-        <v>134</v>
-      </c>
-      <c r="G13" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="H13" s="1" t="s">
-        <v>42</v>
+        <v>140</v>
+      </c>
+      <c r="G13" s="21" t="s">
+        <v>149</v>
+      </c>
+      <c r="H13" s="21" t="s">
+        <v>172</v>
+      </c>
+      <c r="I13" s="14" t="s">
+        <v>58</v>
       </c>
       <c r="J13" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N13" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="L13" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="M13" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="N13" s="15" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="O13" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="P13" s="15" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B14" s="13">
         <v>10010</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E14" s="13">
         <v>10002</v>
       </c>
       <c r="F14" s="21" t="s">
-        <v>134</v>
-      </c>
-      <c r="G14" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="H14" s="1" t="s">
-        <v>42</v>
+        <v>140</v>
+      </c>
+      <c r="G14" s="21" t="s">
+        <v>150</v>
+      </c>
+      <c r="H14" s="21" t="s">
+        <v>172</v>
+      </c>
+      <c r="I14" s="14" t="s">
+        <v>58</v>
       </c>
       <c r="J14" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="L14" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N14" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="L14" s="14" t="s">
+      <c r="O14" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="M14" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="N14" s="15" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="P14" s="15" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B15" s="13">
         <v>10011</v>
       </c>
       <c r="C15" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="D15" s="14" t="s">
         <v>68</v>
-      </c>
-      <c r="D15" s="14" t="s">
-        <v>69</v>
       </c>
       <c r="E15" s="14">
         <v>10003</v>
       </c>
       <c r="F15" s="21" t="s">
-        <v>134</v>
-      </c>
-      <c r="G15" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="G15" s="21" t="s">
+        <v>151</v>
+      </c>
+      <c r="H15" s="21" t="s">
+        <v>172</v>
+      </c>
+      <c r="I15" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N15" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="O15" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="H15" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="J15" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="L15" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="M15" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="N15" s="15" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="P15" s="15" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B16" s="13">
         <v>10012</v>
       </c>
       <c r="C16" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="D16" s="14" t="s">
         <v>68</v>
-      </c>
-      <c r="D16" s="14" t="s">
-        <v>69</v>
       </c>
       <c r="E16" s="14">
         <v>10003</v>
       </c>
       <c r="F16" s="21" t="s">
-        <v>134</v>
-      </c>
-      <c r="G16" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="H16" s="1" t="s">
-        <v>42</v>
+        <v>140</v>
+      </c>
+      <c r="G16" s="21" t="s">
+        <v>152</v>
+      </c>
+      <c r="H16" s="21" t="s">
+        <v>172</v>
+      </c>
+      <c r="I16" s="14" t="s">
+        <v>69</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="L16" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="L16" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N16" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="O16" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="M16" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="N16" s="15" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="17" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="P16" s="15" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="17" spans="2:16" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B17" s="13">
         <v>10013</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E17" s="14">
         <v>10003</v>
       </c>
       <c r="F17" s="21" t="s">
-        <v>134</v>
-      </c>
-      <c r="G17" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="H17" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="G17" s="21" t="s">
+        <v>153</v>
+      </c>
+      <c r="H17" s="21" t="s">
+        <v>172</v>
+      </c>
+      <c r="I17" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="L17" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N17" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="J17" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="L17" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="M17" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="N17" s="15" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="18" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="O17" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="P17" s="15" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="18" spans="2:16" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B18" s="13">
         <v>10014</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E18" s="14">
         <v>10003</v>
       </c>
       <c r="F18" s="21" t="s">
-        <v>134</v>
-      </c>
-      <c r="G18" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="H18" s="1" t="s">
-        <v>42</v>
+        <v>140</v>
+      </c>
+      <c r="G18" s="21" t="s">
+        <v>154</v>
+      </c>
+      <c r="H18" s="21" t="s">
+        <v>172</v>
+      </c>
+      <c r="I18" s="14" t="s">
+        <v>69</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="L18" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="M18" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="N18" s="15" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="19" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
+        <v>41</v>
+      </c>
+      <c r="L18" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N18" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="O18" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="P18" s="15" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="19" spans="2:16" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B19" s="13">
         <v>10015</v>
       </c>
       <c r="C19" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="D19" s="14" t="s">
         <v>74</v>
-      </c>
-      <c r="D19" s="14" t="s">
-        <v>75</v>
       </c>
       <c r="E19" s="13">
         <v>10004</v>
       </c>
       <c r="F19" s="21" t="s">
-        <v>134</v>
-      </c>
-      <c r="G19" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="G19" s="21" t="s">
+        <v>155</v>
+      </c>
+      <c r="H19" s="21" t="s">
+        <v>172</v>
+      </c>
+      <c r="I19" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="J19" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="H19" s="1" t="s">
+      <c r="L19" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N19" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="J19" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="L19" s="14" t="s">
+      <c r="O19" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="M19" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="N19" s="15" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="20" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="P19" s="15" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="20" spans="2:16" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B20" s="13">
         <v>10016</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E20" s="13">
         <v>10004</v>
       </c>
       <c r="F20" s="21" t="s">
-        <v>134</v>
-      </c>
-      <c r="G20" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="H20" s="1" t="s">
-        <v>81</v>
+        <v>140</v>
+      </c>
+      <c r="G20" s="21" t="s">
+        <v>156</v>
+      </c>
+      <c r="H20" s="21" t="s">
+        <v>172</v>
+      </c>
+      <c r="I20" s="14" t="s">
+        <v>75</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="L20" s="14" t="s">
-        <v>78</v>
-      </c>
-      <c r="M20" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="N20" s="15" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="21" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
+        <v>80</v>
+      </c>
+      <c r="L20" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N20" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="O20" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="P20" s="15" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="21" spans="2:16" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B21" s="13">
         <v>10017</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D21" s="14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E21" s="13">
         <v>10004</v>
       </c>
       <c r="F21" s="21" t="s">
-        <v>134</v>
-      </c>
-      <c r="G21" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="H21" s="1" t="s">
-        <v>60</v>
+        <v>140</v>
+      </c>
+      <c r="G21" s="21" t="s">
+        <v>157</v>
+      </c>
+      <c r="H21" s="21" t="s">
+        <v>172</v>
+      </c>
+      <c r="I21" s="14" t="s">
+        <v>75</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="L21" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="M21" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="N21" s="15" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="22" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
+        <v>59</v>
+      </c>
+      <c r="L21" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N21" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="O21" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="P21" s="15" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="22" spans="2:16" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B22" s="13">
         <v>10018</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D22" s="14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E22" s="13">
         <v>10004</v>
       </c>
       <c r="F22" s="21" t="s">
-        <v>134</v>
-      </c>
-      <c r="G22" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="H22" s="1" t="s">
-        <v>60</v>
+        <v>140</v>
+      </c>
+      <c r="G22" s="21" t="s">
+        <v>158</v>
+      </c>
+      <c r="H22" s="21" t="s">
+        <v>172</v>
+      </c>
+      <c r="I22" s="14" t="s">
+        <v>75</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="L22" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="M22" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="N22" s="15" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="23" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
+        <v>59</v>
+      </c>
+      <c r="L22" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N22" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="O22" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="P22" s="15" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="23" spans="2:16" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B23" s="13">
         <v>10019</v>
       </c>
       <c r="C23" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="D23" s="14" t="s">
         <v>86</v>
-      </c>
-      <c r="D23" s="14" t="s">
-        <v>87</v>
       </c>
       <c r="E23" s="13">
         <v>10005</v>
       </c>
       <c r="F23" s="21" t="s">
-        <v>134</v>
-      </c>
-      <c r="G23" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="G23" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="H23" s="21" t="s">
+        <v>172</v>
+      </c>
+      <c r="I23" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="J23" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="H23" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="J23" s="1">
+      <c r="L23" s="1">
         <v>10100</v>
       </c>
-      <c r="L23" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="M23" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="N23" s="15" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="24" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="N23" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="O23" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="P23" s="15" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="24" spans="2:16" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B24" s="13">
         <v>10020</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D24" s="14" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E24" s="13">
         <v>10005</v>
       </c>
       <c r="F24" s="21" t="s">
-        <v>134</v>
-      </c>
-      <c r="G24" s="14" t="s">
-        <v>88</v>
-      </c>
-      <c r="H24" s="1" t="s">
-        <v>42</v>
+        <v>140</v>
+      </c>
+      <c r="G24" s="21" t="s">
+        <v>160</v>
+      </c>
+      <c r="H24" s="21" t="s">
+        <v>172</v>
+      </c>
+      <c r="I24" s="14" t="s">
+        <v>87</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="L24" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="M24" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="N24" s="15" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="25" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
+        <v>41</v>
+      </c>
+      <c r="L24" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N24" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="O24" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="P24" s="15" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="25" spans="2:16" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B25" s="13">
         <v>10021</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D25" s="14" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E25" s="13">
         <v>10005</v>
       </c>
       <c r="F25" s="21" t="s">
-        <v>134</v>
-      </c>
-      <c r="G25" s="14" t="s">
-        <v>88</v>
-      </c>
-      <c r="H25" s="1" t="s">
-        <v>92</v>
+        <v>140</v>
+      </c>
+      <c r="G25" s="21" t="s">
+        <v>161</v>
+      </c>
+      <c r="H25" s="21" t="s">
+        <v>172</v>
+      </c>
+      <c r="I25" s="14" t="s">
+        <v>87</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="L25" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="M25" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="N25" s="15" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="26" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
+        <v>91</v>
+      </c>
+      <c r="L25" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N25" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="O25" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="P25" s="15" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="26" spans="2:16" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B26" s="13">
         <v>10022</v>
       </c>
       <c r="C26" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="D26" s="14" t="s">
         <v>93</v>
-      </c>
-      <c r="D26" s="14" t="s">
-        <v>94</v>
       </c>
       <c r="E26" s="13">
         <v>10006</v>
       </c>
       <c r="F26" s="21" t="s">
-        <v>134</v>
-      </c>
-      <c r="G26" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="G26" s="21" t="s">
+        <v>162</v>
+      </c>
+      <c r="H26" s="21" t="s">
+        <v>172</v>
+      </c>
+      <c r="I26" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="J26" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="H26" s="1" t="s">
+      <c r="L26" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N26" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="O26" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="J26" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="L26" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="M26" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="N26" s="15" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="27" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="P26" s="15" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="27" spans="2:16" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B27" s="13">
         <v>10023</v>
       </c>
       <c r="C27" s="14" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D27" s="14" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E27" s="13">
         <v>10006</v>
       </c>
       <c r="F27" s="21" t="s">
-        <v>134</v>
-      </c>
-      <c r="G27" s="14" t="s">
-        <v>95</v>
-      </c>
-      <c r="H27" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="G27" s="21" t="s">
+        <v>163</v>
+      </c>
+      <c r="H27" s="21" t="s">
+        <v>172</v>
+      </c>
+      <c r="I27" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="J27" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="L27" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N27" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="O27" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="P27" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="J27" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="L27" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="M27" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="N27" s="15" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="28" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
+    </row>
+    <row r="28" spans="2:16" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B28" s="13">
         <v>10024</v>
       </c>
       <c r="C28" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="D28" s="14" t="s">
         <v>101</v>
-      </c>
-      <c r="D28" s="14" t="s">
-        <v>102</v>
       </c>
       <c r="E28" s="14">
         <v>10007</v>
       </c>
       <c r="F28" s="21" t="s">
-        <v>134</v>
-      </c>
-      <c r="G28" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="G28" s="21" t="s">
+        <v>164</v>
+      </c>
+      <c r="H28" s="21" t="s">
+        <v>172</v>
+      </c>
+      <c r="I28" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="J28" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="H28" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="J28" s="1" t="s">
+      <c r="L28" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N28" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="L28" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="M28" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="N28" s="15" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="29" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="O28" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="P28" s="15" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="29" spans="2:16" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B29" s="13">
         <v>10025</v>
       </c>
       <c r="C29" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="D29" s="14" t="s">
         <v>105</v>
-      </c>
-      <c r="D29" s="14" t="s">
-        <v>106</v>
       </c>
       <c r="E29" s="13">
         <v>10008</v>
       </c>
       <c r="F29" s="21" t="s">
-        <v>134</v>
-      </c>
-      <c r="G29" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="G29" s="21" t="s">
+        <v>165</v>
+      </c>
+      <c r="H29" s="21" t="s">
+        <v>172</v>
+      </c>
+      <c r="I29" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="J29" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="H29" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="J29" s="1" t="s">
+      <c r="L29" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N29" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="L29" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="M29" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="N29" s="15" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="30" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="O29" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="P29" s="15" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="30" spans="2:16" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B30" s="13">
         <v>10026</v>
       </c>
       <c r="C30" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="D30" s="14" t="s">
         <v>109</v>
-      </c>
-      <c r="D30" s="14" t="s">
-        <v>110</v>
       </c>
       <c r="E30" s="13">
         <v>10009</v>
       </c>
       <c r="F30" s="21" t="s">
-        <v>134</v>
-      </c>
-      <c r="G30" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="G30" s="21" t="s">
+        <v>166</v>
+      </c>
+      <c r="H30" s="21" t="s">
+        <v>172</v>
+      </c>
+      <c r="I30" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="J30" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="H30" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="J30" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="L30" s="14" t="s">
-        <v>78</v>
-      </c>
-      <c r="M30" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="N30" s="15" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="31" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="L30" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N30" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="O30" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="P30" s="15" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="31" spans="2:16" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B31" s="13">
         <v>10027</v>
       </c>
       <c r="C31" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="D31" s="14" t="s">
         <v>113</v>
-      </c>
-      <c r="D31" s="14" t="s">
-        <v>114</v>
       </c>
       <c r="E31" s="13">
         <v>10010</v>
       </c>
       <c r="F31" s="21" t="s">
-        <v>134</v>
-      </c>
-      <c r="G31" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="G31" s="21" t="s">
+        <v>167</v>
+      </c>
+      <c r="H31" s="21" t="s">
+        <v>172</v>
+      </c>
+      <c r="I31" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="J31" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="H31" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="J31" s="1" t="s">
+      <c r="L31" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N31" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="L31" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="M31" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="N31" s="15" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="32" spans="2:14" s="1" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="O31" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="P31" s="15" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="32" spans="2:16" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B32" s="13">
         <v>10028</v>
       </c>
       <c r="C32" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="D32" s="14" t="s">
         <v>117</v>
-      </c>
-      <c r="D32" s="14" t="s">
-        <v>118</v>
       </c>
       <c r="E32" s="14">
         <v>10011</v>
       </c>
       <c r="F32" s="21" t="s">
-        <v>134</v>
-      </c>
-      <c r="G32" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="G32" s="21" t="s">
+        <v>168</v>
+      </c>
+      <c r="H32" s="21" t="s">
+        <v>172</v>
+      </c>
+      <c r="I32" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="J32" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="H32" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="J32" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="L32" s="14" t="s">
-        <v>78</v>
-      </c>
-      <c r="M32" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="N32" s="15" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="33" spans="2:14" s="2" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="L32" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N32" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="O32" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="P32" s="15" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="33" spans="2:16" s="2" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B33" s="16">
         <v>10029</v>
       </c>
       <c r="C33" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D33" s="17" t="s">
         <v>121</v>
-      </c>
-      <c r="D33" s="17" t="s">
-        <v>122</v>
       </c>
       <c r="E33" s="17">
         <v>10012</v>
       </c>
       <c r="F33" s="21" t="s">
-        <v>134</v>
-      </c>
-      <c r="G33" s="14" t="s">
-        <v>95</v>
-      </c>
-      <c r="H33" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="G33" s="21" t="s">
+        <v>169</v>
+      </c>
+      <c r="H33" s="21" t="s">
+        <v>172</v>
+      </c>
+      <c r="I33" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="J33" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="L33" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="N33" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="O33" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="P33" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="J33" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="L33" s="17" t="s">
-        <v>44</v>
-      </c>
-      <c r="M33" s="17" t="s">
-        <v>44</v>
-      </c>
-      <c r="N33" s="15" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="34" spans="2:14" s="2" customFormat="1" x14ac:dyDescent="0.45">
+    </row>
+    <row r="34" spans="2:16" s="2" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B34" s="16">
         <v>10030</v>
       </c>
       <c r="C34" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="D34" s="17" t="s">
         <v>125</v>
-      </c>
-      <c r="D34" s="17" t="s">
-        <v>126</v>
       </c>
       <c r="E34" s="17">
         <v>10013</v>
       </c>
       <c r="F34" s="21" t="s">
-        <v>134</v>
-      </c>
-      <c r="G34" s="14" t="s">
-        <v>95</v>
-      </c>
-      <c r="H34" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="G34" s="21" t="s">
+        <v>170</v>
+      </c>
+      <c r="H34" s="21" t="s">
+        <v>172</v>
+      </c>
+      <c r="I34" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="J34" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="L34" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="N34" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="O34" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="P34" s="18" t="s">
         <v>127</v>
       </c>
-      <c r="J34" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="L34" s="17" t="s">
-        <v>44</v>
-      </c>
-      <c r="M34" s="17" t="s">
-        <v>44</v>
-      </c>
-      <c r="N34" s="18" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="35" spans="2:14" s="2" customFormat="1" x14ac:dyDescent="0.45">
+    </row>
+    <row r="35" spans="2:16" s="2" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B35" s="16">
         <v>10031</v>
       </c>
       <c r="C35" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="D35" s="17" t="s">
         <v>129</v>
-      </c>
-      <c r="D35" s="17" t="s">
-        <v>130</v>
       </c>
       <c r="E35" s="17">
         <v>10014</v>
       </c>
       <c r="F35" s="21" t="s">
-        <v>134</v>
-      </c>
-      <c r="G35" s="14" t="s">
-        <v>95</v>
-      </c>
-      <c r="H35" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="G35" s="21" t="s">
+        <v>171</v>
+      </c>
+      <c r="H35" s="21" t="s">
+        <v>172</v>
+      </c>
+      <c r="I35" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="J35" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="L35" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="N35" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="O35" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="P35" s="18" t="s">
         <v>131</v>
-      </c>
-      <c r="J35" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="L35" s="17" t="s">
-        <v>44</v>
-      </c>
-      <c r="M35" s="17" t="s">
-        <v>44</v>
-      </c>
-      <c r="N35" s="18" t="s">
-        <v>132</v>
       </c>
     </row>
   </sheetData>

--- a/ExcelTool/LubanTools/DataTables/Datas/NpcData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/NpcData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B679710-1D18-4B52-AD00-4D970B5DD986}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41EB3132-5953-49B4-95B8-6B2F064673E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-9940" yWindow="2230" windowWidth="44100" windowHeight="18570" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-14440" yWindow="2710" windowWidth="44100" windowHeight="18570" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="角色表" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="176">
   <si>
     <t>##var</t>
   </si>
@@ -559,6 +559,17 @@
   </si>
   <si>
     <t>Assets/AddressableAssets/Remote/Texture2D/Characters/DialogueTexture2D/Machi.png</t>
+  </si>
+  <si>
+    <t>ScreenSpienPath</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>场景Spine</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Skeleton/Machi/sp漫展小人_SkeletonData.asset</t>
   </si>
 </sst>
 </file>
@@ -718,7 +729,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -994,7 +1005,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P35"/>
+  <dimension ref="A1:Q35"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="2" width="8.6640625" style="3" customWidth="1"/>
@@ -1002,19 +1013,19 @@
     <col min="4" max="5" width="35.58203125" style="3" customWidth="1"/>
     <col min="6" max="6" width="73.1640625" style="22" customWidth="1"/>
     <col min="7" max="7" width="82.4140625" style="22" customWidth="1"/>
-    <col min="8" max="8" width="95.33203125" style="22" customWidth="1"/>
-    <col min="9" max="9" width="49.33203125" style="4" customWidth="1"/>
-    <col min="10" max="10" width="33.58203125" style="3" customWidth="1"/>
-    <col min="11" max="11" width="23.25" style="3" customWidth="1"/>
-    <col min="12" max="12" width="21.4140625" style="3" customWidth="1"/>
-    <col min="13" max="13" width="16.58203125" style="3" customWidth="1"/>
-    <col min="14" max="14" width="28" style="4" customWidth="1"/>
-    <col min="15" max="15" width="17.75" style="3" customWidth="1"/>
-    <col min="16" max="16" width="17.33203125" style="5" customWidth="1"/>
-    <col min="17" max="16384" width="9" style="3"/>
+    <col min="8" max="9" width="95.33203125" style="22" customWidth="1"/>
+    <col min="10" max="10" width="49.33203125" style="4" customWidth="1"/>
+    <col min="11" max="11" width="33.58203125" style="3" customWidth="1"/>
+    <col min="12" max="12" width="23.25" style="3" customWidth="1"/>
+    <col min="13" max="13" width="21.4140625" style="3" customWidth="1"/>
+    <col min="14" max="14" width="16.58203125" style="3" customWidth="1"/>
+    <col min="15" max="15" width="28" style="4" customWidth="1"/>
+    <col min="16" max="16" width="17.75" style="3" customWidth="1"/>
+    <col min="17" max="17" width="17.33203125" style="5" customWidth="1"/>
+    <col min="18" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1039,32 +1050,35 @@
       <c r="H1" s="20" t="s">
         <v>134</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="20" t="s">
+        <v>173</v>
+      </c>
+      <c r="J1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="L1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="M1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="N1" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="O1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="O1" s="6" t="s">
+      <c r="P1" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="P1" s="9" t="s">
+      <c r="Q1" s="9" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A2" s="3" t="s">
         <v>13</v>
       </c>
@@ -1089,14 +1103,14 @@
       <c r="H2" s="19" t="s">
         <v>135</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="19" t="s">
+        <v>135</v>
+      </c>
+      <c r="J2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J2" s="10" t="s">
+      <c r="K2" s="10" t="s">
         <v>17</v>
-      </c>
-      <c r="K2" s="8" t="s">
-        <v>18</v>
       </c>
       <c r="L2" s="8" t="s">
         <v>18</v>
@@ -1104,17 +1118,20 @@
       <c r="M2" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="N2" s="11" t="s">
+      <c r="N2" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="O2" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="O2" s="12" t="s">
+      <c r="P2" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="P2" s="5" t="s">
+      <c r="Q2" s="5" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A3" s="3" t="s">
         <v>22</v>
       </c>
@@ -1139,32 +1156,35 @@
       <c r="H3" s="20" t="s">
         <v>139</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="I3" s="20" t="s">
+        <v>174</v>
+      </c>
+      <c r="J3" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="K3" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="L3" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="M3" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="M3" s="3" t="s">
+      <c r="N3" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="N3" s="4" t="s">
+      <c r="O3" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="O3" s="3" t="s">
+      <c r="P3" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="P3" s="5" t="s">
+      <c r="Q3" s="5" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="4" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B4" s="13">
         <v>10000</v>
       </c>
@@ -1186,12 +1206,15 @@
       <c r="H4" s="21" t="s">
         <v>172</v>
       </c>
-      <c r="I4" s="14"/>
-      <c r="P4" s="15" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="I4" s="21" t="s">
+        <v>175</v>
+      </c>
+      <c r="J4" s="14"/>
+      <c r="Q4" s="15" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B5" s="13">
         <v>10001</v>
       </c>
@@ -1213,26 +1236,29 @@
       <c r="H5" s="21" t="s">
         <v>172</v>
       </c>
-      <c r="I5" s="14" t="s">
+      <c r="I5" s="21" t="s">
+        <v>175</v>
+      </c>
+      <c r="J5" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="J5" s="1" t="s">
+      <c r="K5" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="L5" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="N5" s="14" t="s">
+      <c r="M5" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="O5" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="O5" s="1" t="s">
+      <c r="P5" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="P5" s="15" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="Q5" s="15" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B6" s="13">
         <v>10002</v>
       </c>
@@ -1254,26 +1280,29 @@
       <c r="H6" s="21" t="s">
         <v>172</v>
       </c>
-      <c r="I6" s="14" t="s">
+      <c r="I6" s="21" t="s">
+        <v>175</v>
+      </c>
+      <c r="J6" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="J6" s="1" t="s">
+      <c r="K6" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="L6" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="N6" s="14" t="s">
+      <c r="M6" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="O6" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="O6" s="1" t="s">
+      <c r="P6" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="P6" s="15" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="Q6" s="15" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B7" s="13">
         <v>10003</v>
       </c>
@@ -1295,26 +1324,29 @@
       <c r="H7" s="21" t="s">
         <v>172</v>
       </c>
-      <c r="I7" s="14" t="s">
+      <c r="I7" s="21" t="s">
+        <v>175</v>
+      </c>
+      <c r="J7" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="J7" s="1" t="s">
+      <c r="K7" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="L7" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="N7" s="14" t="s">
+      <c r="M7" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="O7" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="O7" s="1" t="s">
+      <c r="P7" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="P7" s="15" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="Q7" s="15" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B8" s="13">
         <v>10004</v>
       </c>
@@ -1336,26 +1368,29 @@
       <c r="H8" s="21" t="s">
         <v>172</v>
       </c>
-      <c r="I8" s="14" t="s">
+      <c r="I8" s="21" t="s">
+        <v>175</v>
+      </c>
+      <c r="J8" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="J8" s="1" t="s">
+      <c r="K8" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="L8" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="N8" s="14" t="s">
+      <c r="M8" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="O8" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="O8" s="1" t="s">
+      <c r="P8" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="P8" s="15" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="Q8" s="15" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B9" s="13">
         <v>10005</v>
       </c>
@@ -1377,26 +1412,29 @@
       <c r="H9" s="21" t="s">
         <v>172</v>
       </c>
-      <c r="I9" s="14" t="s">
+      <c r="I9" s="21" t="s">
+        <v>175</v>
+      </c>
+      <c r="J9" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="J9" s="1" t="s">
+      <c r="K9" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="L9" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="N9" s="14" t="s">
+      <c r="M9" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="O9" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="O9" s="1" t="s">
+      <c r="P9" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="P9" s="15" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="Q9" s="15" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B10" s="13">
         <v>10006</v>
       </c>
@@ -1418,26 +1456,29 @@
       <c r="H10" s="21" t="s">
         <v>172</v>
       </c>
-      <c r="I10" s="14" t="s">
+      <c r="I10" s="21" t="s">
+        <v>175</v>
+      </c>
+      <c r="J10" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="J10" s="1" t="s">
+      <c r="K10" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="L10" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="N10" s="14" t="s">
+      <c r="M10" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="O10" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="O10" s="1" t="s">
+      <c r="P10" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="P10" s="15" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="Q10" s="15" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B11" s="13">
         <v>10007</v>
       </c>
@@ -1459,26 +1500,29 @@
       <c r="H11" s="21" t="s">
         <v>172</v>
       </c>
-      <c r="I11" s="14" t="s">
+      <c r="I11" s="21" t="s">
+        <v>175</v>
+      </c>
+      <c r="J11" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="J11" s="1" t="s">
+      <c r="K11" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="L11" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="N11" s="14" t="s">
+      <c r="M11" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="O11" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="O11" s="1" t="s">
+      <c r="P11" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="P11" s="15" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="Q11" s="15" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B12" s="13">
         <v>10008</v>
       </c>
@@ -1500,26 +1544,29 @@
       <c r="H12" s="21" t="s">
         <v>172</v>
       </c>
-      <c r="I12" s="14" t="s">
+      <c r="I12" s="21" t="s">
+        <v>175</v>
+      </c>
+      <c r="J12" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="J12" s="1" t="s">
+      <c r="K12" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="L12" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="N12" s="14" t="s">
+      <c r="M12" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="O12" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="O12" s="1" t="s">
+      <c r="P12" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="P12" s="15" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="Q12" s="15" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B13" s="13">
         <v>10009</v>
       </c>
@@ -1541,26 +1588,29 @@
       <c r="H13" s="21" t="s">
         <v>172</v>
       </c>
-      <c r="I13" s="14" t="s">
+      <c r="I13" s="21" t="s">
+        <v>175</v>
+      </c>
+      <c r="J13" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="J13" s="1" t="s">
+      <c r="K13" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="L13" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="N13" s="14" t="s">
+      <c r="M13" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="O13" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="O13" s="1" t="s">
+      <c r="P13" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="P13" s="15" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="Q13" s="15" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B14" s="13">
         <v>10010</v>
       </c>
@@ -1582,26 +1632,29 @@
       <c r="H14" s="21" t="s">
         <v>172</v>
       </c>
-      <c r="I14" s="14" t="s">
+      <c r="I14" s="21" t="s">
+        <v>175</v>
+      </c>
+      <c r="J14" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="J14" s="1" t="s">
+      <c r="K14" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="L14" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="N14" s="14" t="s">
+      <c r="M14" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="O14" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="O14" s="1" t="s">
+      <c r="P14" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="P14" s="15" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="Q14" s="15" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B15" s="13">
         <v>10011</v>
       </c>
@@ -1623,26 +1676,29 @@
       <c r="H15" s="21" t="s">
         <v>172</v>
       </c>
-      <c r="I15" s="14" t="s">
+      <c r="I15" s="21" t="s">
+        <v>175</v>
+      </c>
+      <c r="J15" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="J15" s="1" t="s">
+      <c r="K15" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="L15" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="N15" s="14" t="s">
+      <c r="M15" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="O15" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="O15" s="1" t="s">
+      <c r="P15" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="P15" s="15" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="Q15" s="15" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B16" s="13">
         <v>10012</v>
       </c>
@@ -1664,26 +1720,29 @@
       <c r="H16" s="21" t="s">
         <v>172</v>
       </c>
-      <c r="I16" s="14" t="s">
+      <c r="I16" s="21" t="s">
+        <v>175</v>
+      </c>
+      <c r="J16" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="J16" s="1" t="s">
+      <c r="K16" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="L16" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="N16" s="14" t="s">
+      <c r="M16" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="O16" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="O16" s="1" t="s">
+      <c r="P16" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="P16" s="15" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="17" spans="2:16" s="1" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="Q16" s="15" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="17" spans="2:17" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B17" s="13">
         <v>10013</v>
       </c>
@@ -1705,26 +1764,29 @@
       <c r="H17" s="21" t="s">
         <v>172</v>
       </c>
-      <c r="I17" s="14" t="s">
+      <c r="I17" s="21" t="s">
+        <v>175</v>
+      </c>
+      <c r="J17" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="J17" s="1" t="s">
+      <c r="K17" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="L17" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="N17" s="14" t="s">
+      <c r="M17" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="O17" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="O17" s="1" t="s">
+      <c r="P17" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="P17" s="15" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="18" spans="2:16" s="1" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="Q17" s="15" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="18" spans="2:17" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B18" s="13">
         <v>10014</v>
       </c>
@@ -1746,26 +1808,29 @@
       <c r="H18" s="21" t="s">
         <v>172</v>
       </c>
-      <c r="I18" s="14" t="s">
+      <c r="I18" s="21" t="s">
+        <v>175</v>
+      </c>
+      <c r="J18" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="J18" s="1" t="s">
+      <c r="K18" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="L18" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="N18" s="14" t="s">
+      <c r="M18" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="O18" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="O18" s="1" t="s">
+      <c r="P18" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="P18" s="15" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="19" spans="2:16" s="1" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="Q18" s="15" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="19" spans="2:17" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B19" s="13">
         <v>10015</v>
       </c>
@@ -1787,26 +1852,29 @@
       <c r="H19" s="21" t="s">
         <v>172</v>
       </c>
-      <c r="I19" s="14" t="s">
+      <c r="I19" s="21" t="s">
+        <v>175</v>
+      </c>
+      <c r="J19" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="J19" s="1" t="s">
+      <c r="K19" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="L19" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="N19" s="14" t="s">
+      <c r="M19" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="O19" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="O19" s="1" t="s">
+      <c r="P19" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="P19" s="15" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="20" spans="2:16" s="1" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="Q19" s="15" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="20" spans="2:17" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B20" s="13">
         <v>10016</v>
       </c>
@@ -1828,26 +1896,29 @@
       <c r="H20" s="21" t="s">
         <v>172</v>
       </c>
-      <c r="I20" s="14" t="s">
+      <c r="I20" s="21" t="s">
+        <v>175</v>
+      </c>
+      <c r="J20" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="J20" s="1" t="s">
+      <c r="K20" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="L20" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="N20" s="14" t="s">
+      <c r="M20" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="O20" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="O20" s="1" t="s">
+      <c r="P20" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="P20" s="15" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="21" spans="2:16" s="1" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="Q20" s="15" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="21" spans="2:17" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B21" s="13">
         <v>10017</v>
       </c>
@@ -1869,26 +1940,29 @@
       <c r="H21" s="21" t="s">
         <v>172</v>
       </c>
-      <c r="I21" s="14" t="s">
+      <c r="I21" s="21" t="s">
+        <v>175</v>
+      </c>
+      <c r="J21" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="J21" s="1" t="s">
+      <c r="K21" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="L21" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="N21" s="14" t="s">
+      <c r="M21" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="O21" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="O21" s="1" t="s">
+      <c r="P21" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="P21" s="15" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="22" spans="2:16" s="1" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="Q21" s="15" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="22" spans="2:17" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B22" s="13">
         <v>10018</v>
       </c>
@@ -1910,26 +1984,29 @@
       <c r="H22" s="21" t="s">
         <v>172</v>
       </c>
-      <c r="I22" s="14" t="s">
+      <c r="I22" s="21" t="s">
+        <v>175</v>
+      </c>
+      <c r="J22" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="J22" s="1" t="s">
+      <c r="K22" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="L22" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="N22" s="14" t="s">
+      <c r="M22" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="O22" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="O22" s="1" t="s">
+      <c r="P22" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="P22" s="15" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="23" spans="2:16" s="1" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="Q22" s="15" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="23" spans="2:17" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B23" s="13">
         <v>10019</v>
       </c>
@@ -1951,26 +2028,29 @@
       <c r="H23" s="21" t="s">
         <v>172</v>
       </c>
-      <c r="I23" s="14" t="s">
+      <c r="I23" s="21" t="s">
+        <v>175</v>
+      </c>
+      <c r="J23" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="J23" s="1" t="s">
+      <c r="K23" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="L23" s="1">
+      <c r="M23" s="1">
         <v>10100</v>
       </c>
-      <c r="N23" s="14" t="s">
+      <c r="O23" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="O23" s="1" t="s">
+      <c r="P23" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="P23" s="15" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="24" spans="2:16" s="1" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="Q23" s="15" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="24" spans="2:17" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B24" s="13">
         <v>10020</v>
       </c>
@@ -1992,26 +2072,29 @@
       <c r="H24" s="21" t="s">
         <v>172</v>
       </c>
-      <c r="I24" s="14" t="s">
+      <c r="I24" s="21" t="s">
+        <v>175</v>
+      </c>
+      <c r="J24" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="J24" s="1" t="s">
+      <c r="K24" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="L24" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="N24" s="14" t="s">
+      <c r="M24" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="O24" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="O24" s="1" t="s">
+      <c r="P24" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="P24" s="15" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="25" spans="2:16" s="1" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="Q24" s="15" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="25" spans="2:17" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B25" s="13">
         <v>10021</v>
       </c>
@@ -2033,26 +2116,29 @@
       <c r="H25" s="21" t="s">
         <v>172</v>
       </c>
-      <c r="I25" s="14" t="s">
+      <c r="I25" s="21" t="s">
+        <v>175</v>
+      </c>
+      <c r="J25" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="J25" s="1" t="s">
+      <c r="K25" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="L25" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="N25" s="14" t="s">
+      <c r="M25" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="O25" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="O25" s="1" t="s">
+      <c r="P25" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="P25" s="15" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="26" spans="2:16" s="1" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="Q25" s="15" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="26" spans="2:17" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B26" s="13">
         <v>10022</v>
       </c>
@@ -2074,26 +2160,29 @@
       <c r="H26" s="21" t="s">
         <v>172</v>
       </c>
-      <c r="I26" s="14" t="s">
+      <c r="I26" s="21" t="s">
+        <v>175</v>
+      </c>
+      <c r="J26" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="J26" s="1" t="s">
+      <c r="K26" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="L26" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="N26" s="14" t="s">
+      <c r="M26" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="O26" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="O26" s="1" t="s">
+      <c r="P26" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="P26" s="15" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="27" spans="2:16" s="1" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="Q26" s="15" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="27" spans="2:17" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B27" s="13">
         <v>10023</v>
       </c>
@@ -2115,26 +2204,29 @@
       <c r="H27" s="21" t="s">
         <v>172</v>
       </c>
-      <c r="I27" s="14" t="s">
+      <c r="I27" s="21" t="s">
+        <v>175</v>
+      </c>
+      <c r="J27" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="J27" s="1" t="s">
+      <c r="K27" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="L27" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="N27" s="14" t="s">
+      <c r="M27" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="O27" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="O27" s="1" t="s">
+      <c r="P27" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="P27" s="15" t="s">
+      <c r="Q27" s="15" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="28" spans="2:16" s="1" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="2:17" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B28" s="13">
         <v>10024</v>
       </c>
@@ -2156,26 +2248,29 @@
       <c r="H28" s="21" t="s">
         <v>172</v>
       </c>
-      <c r="I28" s="14" t="s">
+      <c r="I28" s="21" t="s">
+        <v>175</v>
+      </c>
+      <c r="J28" s="14" t="s">
         <v>102</v>
       </c>
-      <c r="J28" s="1" t="s">
+      <c r="K28" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="L28" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="N28" s="14" t="s">
+      <c r="M28" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="O28" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="O28" s="1" t="s">
+      <c r="P28" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="P28" s="15" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="29" spans="2:16" s="1" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="Q28" s="15" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="29" spans="2:17" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B29" s="13">
         <v>10025</v>
       </c>
@@ -2197,26 +2292,29 @@
       <c r="H29" s="21" t="s">
         <v>172</v>
       </c>
-      <c r="I29" s="14" t="s">
+      <c r="I29" s="21" t="s">
+        <v>175</v>
+      </c>
+      <c r="J29" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="J29" s="1" t="s">
+      <c r="K29" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="L29" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="N29" s="14" t="s">
+      <c r="M29" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="O29" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="O29" s="1" t="s">
+      <c r="P29" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="P29" s="15" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="30" spans="2:16" s="1" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="Q29" s="15" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="30" spans="2:17" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B30" s="13">
         <v>10026</v>
       </c>
@@ -2238,26 +2336,29 @@
       <c r="H30" s="21" t="s">
         <v>172</v>
       </c>
-      <c r="I30" s="14" t="s">
+      <c r="I30" s="21" t="s">
+        <v>175</v>
+      </c>
+      <c r="J30" s="14" t="s">
         <v>110</v>
       </c>
-      <c r="J30" s="1" t="s">
+      <c r="K30" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="L30" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="N30" s="14" t="s">
+      <c r="M30" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="O30" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="O30" s="1" t="s">
+      <c r="P30" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="P30" s="15" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="31" spans="2:16" s="1" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="Q30" s="15" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="31" spans="2:17" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B31" s="13">
         <v>10027</v>
       </c>
@@ -2279,26 +2380,29 @@
       <c r="H31" s="21" t="s">
         <v>172</v>
       </c>
-      <c r="I31" s="14" t="s">
+      <c r="I31" s="21" t="s">
+        <v>175</v>
+      </c>
+      <c r="J31" s="14" t="s">
         <v>114</v>
       </c>
-      <c r="J31" s="1" t="s">
+      <c r="K31" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="L31" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="N31" s="14" t="s">
+      <c r="M31" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="O31" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="O31" s="1" t="s">
+      <c r="P31" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="P31" s="15" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="32" spans="2:16" s="1" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="Q31" s="15" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="32" spans="2:17" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B32" s="13">
         <v>10028</v>
       </c>
@@ -2320,26 +2424,29 @@
       <c r="H32" s="21" t="s">
         <v>172</v>
       </c>
-      <c r="I32" s="14" t="s">
+      <c r="I32" s="21" t="s">
+        <v>175</v>
+      </c>
+      <c r="J32" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="J32" s="1" t="s">
+      <c r="K32" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="L32" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="N32" s="14" t="s">
+      <c r="M32" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="O32" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="O32" s="1" t="s">
+      <c r="P32" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="P32" s="15" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="33" spans="2:16" s="2" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="Q32" s="15" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="33" spans="2:17" s="2" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B33" s="16">
         <v>10029</v>
       </c>
@@ -2361,26 +2468,29 @@
       <c r="H33" s="21" t="s">
         <v>172</v>
       </c>
-      <c r="I33" s="14" t="s">
+      <c r="I33" s="21" t="s">
+        <v>175</v>
+      </c>
+      <c r="J33" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="J33" s="2" t="s">
+      <c r="K33" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="L33" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="N33" s="17" t="s">
-        <v>43</v>
+      <c r="M33" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="O33" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="P33" s="15" t="s">
+      <c r="P33" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q33" s="15" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="34" spans="2:16" s="2" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="34" spans="2:17" s="2" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B34" s="16">
         <v>10030</v>
       </c>
@@ -2402,26 +2512,29 @@
       <c r="H34" s="21" t="s">
         <v>172</v>
       </c>
-      <c r="I34" s="14" t="s">
+      <c r="I34" s="21" t="s">
+        <v>175</v>
+      </c>
+      <c r="J34" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="J34" s="2" t="s">
+      <c r="K34" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="L34" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="N34" s="17" t="s">
-        <v>43</v>
+      <c r="M34" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="O34" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="P34" s="18" t="s">
+      <c r="P34" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q34" s="18" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="35" spans="2:16" s="2" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="35" spans="2:17" s="2" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B35" s="16">
         <v>10031</v>
       </c>
@@ -2443,22 +2556,25 @@
       <c r="H35" s="21" t="s">
         <v>172</v>
       </c>
-      <c r="I35" s="14" t="s">
+      <c r="I35" s="21" t="s">
+        <v>175</v>
+      </c>
+      <c r="J35" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="J35" s="2" t="s">
+      <c r="K35" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="L35" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="N35" s="17" t="s">
-        <v>43</v>
+      <c r="M35" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="O35" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="P35" s="18" t="s">
+      <c r="P35" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q35" s="18" t="s">
         <v>131</v>
       </c>
     </row>

--- a/ExcelTool/LubanTools/DataTables/Datas/NpcData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/NpcData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41EB3132-5953-49B4-95B8-6B2F064673E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2292E329-AE59-4576-9A93-A9F9974A92F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-14440" yWindow="2710" windowWidth="44100" windowHeight="18570" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-4720" yWindow="3090" windowWidth="44100" windowHeight="18570" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="角色表" sheetId="1" r:id="rId1"/>
